--- a/OffSeason.xlsx
+++ b/OffSeason.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Rosters" sheetId="1" state="visible" r:id="rId2"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="621">
   <si>
     <t xml:space="preserve">No Chubb – John Olson</t>
   </si>
@@ -71,6 +71,9 @@
     <t xml:space="preserve">Spencer Rattler</t>
   </si>
   <si>
+    <t xml:space="preserve">Joe Burrow</t>
+  </si>
+  <si>
     <t xml:space="preserve">Baker Mayfield</t>
   </si>
   <si>
@@ -89,12 +92,12 @@
     <t xml:space="preserve">Calvin Austin</t>
   </si>
   <si>
-    <t xml:space="preserve">Joe Burrow</t>
-  </si>
-  <si>
     <t xml:space="preserve">RB</t>
   </si>
   <si>
+    <t xml:space="preserve">Nick Chubb</t>
+  </si>
+  <si>
     <t xml:space="preserve">Taysom Hill (QB/TE</t>
   </si>
   <si>
@@ -110,7 +113,10 @@
     <t xml:space="preserve">Michael Penix Jr</t>
   </si>
   <si>
-    <t xml:space="preserve">Nick Chubb</t>
+    <t xml:space="preserve">Derrek Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Taylor</t>
   </si>
   <si>
     <t xml:space="preserve">Chubba Hubbard</t>
@@ -119,7 +125,7 @@
     <t xml:space="preserve">Travis Etienne Jr</t>
   </si>
   <si>
-    <t xml:space="preserve">Derrek Carr</t>
+    <t xml:space="preserve">Joe Mixon</t>
   </si>
   <si>
     <t xml:space="preserve">Derrick Henry</t>
@@ -128,7 +134,10 @@
     <t xml:space="preserve">Mac Jones</t>
   </si>
   <si>
-    <t xml:space="preserve">Jonathan Taylor</t>
+    <t xml:space="preserve">Jonathan Owens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bijan Robinson</t>
   </si>
   <si>
     <t xml:space="preserve">James Conner</t>
@@ -137,7 +146,7 @@
     <t xml:space="preserve">Jahmyr Gibbs</t>
   </si>
   <si>
-    <t xml:space="preserve">Joe Mixon</t>
+    <t xml:space="preserve">Tony Pollard</t>
   </si>
   <si>
     <t xml:space="preserve">Jaylen Warren</t>
@@ -146,7 +155,10 @@
     <t xml:space="preserve">Devon Achane</t>
   </si>
   <si>
-    <t xml:space="preserve">Bijan Robinson</t>
+    <t xml:space="preserve">Kris Jenkins Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breece Hall</t>
   </si>
   <si>
     <t xml:space="preserve">Rico Dowdle</t>
@@ -155,7 +167,7 @@
     <t xml:space="preserve">D’Andre Swift</t>
   </si>
   <si>
-    <t xml:space="preserve">Tony Pollard</t>
+    <t xml:space="preserve">Rhamondre Stevenson</t>
   </si>
   <si>
     <t xml:space="preserve">     </t>
@@ -167,7 +179,10 @@
     <t xml:space="preserve">Roschon Johnson</t>
   </si>
   <si>
-    <t xml:space="preserve">Breece Hall</t>
+    <t xml:space="preserve">Trevin Wallace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saquon Barkley</t>
   </si>
   <si>
     <t xml:space="preserve">Raheem Blackshear</t>
@@ -176,7 +191,7 @@
     <t xml:space="preserve">Kenneth Walker III</t>
   </si>
   <si>
-    <t xml:space="preserve">Rhamondre Stevenson</t>
+    <t xml:space="preserve">Isiah Pacheco</t>
   </si>
   <si>
     <t xml:space="preserve">Jaleel Mclaughlin</t>
@@ -185,7 +200,13 @@
     <t xml:space="preserve">Tyler Allgeier</t>
   </si>
   <si>
-    <t xml:space="preserve">Saquon Barkley</t>
+    <t xml:space="preserve">Payton Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Jefferson</t>
   </si>
   <si>
     <t xml:space="preserve">Ameer Abdullah</t>
@@ -194,7 +215,7 @@
     <t xml:space="preserve">Emmanuel Wilson</t>
   </si>
   <si>
-    <t xml:space="preserve">Isiah Pacheco</t>
+    <t xml:space="preserve">J.K. Dobbins</t>
   </si>
   <si>
     <t xml:space="preserve">Tyrone Tracy Jr</t>
@@ -203,10 +224,7 @@
     <t xml:space="preserve">Isaiah Davis</t>
   </si>
   <si>
-    <t xml:space="preserve">WR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Jefferson</t>
+    <t xml:space="preserve">Ja’Marr Chase</t>
   </si>
   <si>
     <t xml:space="preserve">Raheem Mostert</t>
@@ -215,7 +233,7 @@
     <t xml:space="preserve">Chris Brooks</t>
   </si>
   <si>
-    <t xml:space="preserve">J.K. Dobbins</t>
+    <t xml:space="preserve">Stefon Diggs</t>
   </si>
   <si>
     <t xml:space="preserve">Kareem Hunt</t>
@@ -224,7 +242,7 @@
     <t xml:space="preserve">Ray Davis</t>
   </si>
   <si>
-    <t xml:space="preserve">Ja’Marr Chase</t>
+    <t xml:space="preserve">CeeDee Lamb</t>
   </si>
   <si>
     <t xml:space="preserve">Trey Sermon</t>
@@ -233,7 +251,7 @@
     <t xml:space="preserve">Alexander Mattison</t>
   </si>
   <si>
-    <t xml:space="preserve">Stefon Diggs</t>
+    <t xml:space="preserve">Drake London</t>
   </si>
   <si>
     <t xml:space="preserve">Jordan Mason</t>
@@ -242,7 +260,7 @@
     <t xml:space="preserve">Isreal Abanikanda</t>
   </si>
   <si>
-    <t xml:space="preserve">CeeDee Lamb</t>
+    <t xml:space="preserve">Brian Thomas Jr.</t>
   </si>
   <si>
     <t xml:space="preserve">Puka Nacua</t>
@@ -251,7 +269,7 @@
     <t xml:space="preserve">Craig Reynolds</t>
   </si>
   <si>
-    <t xml:space="preserve">Drake London</t>
+    <t xml:space="preserve">Davonte Adams</t>
   </si>
   <si>
     <t xml:space="preserve">Deebo Samel</t>
@@ -260,7 +278,7 @@
     <t xml:space="preserve">Trey Benson</t>
   </si>
   <si>
-    <t xml:space="preserve">Brian Thomas Jr.</t>
+    <t xml:space="preserve">Ladd McConkey</t>
   </si>
   <si>
     <t xml:space="preserve">Mike Evans</t>
@@ -269,7 +287,7 @@
     <t xml:space="preserve">Amon-Ra St. Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Davonte Adams</t>
+    <t xml:space="preserve">DK Metcalf</t>
   </si>
   <si>
     <t xml:space="preserve">Tee Higgins</t>
@@ -278,7 +296,7 @@
     <t xml:space="preserve">Khalil Herbert</t>
   </si>
   <si>
-    <t xml:space="preserve">Ladd McConkey</t>
+    <t xml:space="preserve">Xavier Worthy</t>
   </si>
   <si>
     <t xml:space="preserve">Adam Thielen</t>
@@ -287,7 +305,7 @@
     <t xml:space="preserve">Jaxon Smith-Njigba</t>
   </si>
   <si>
-    <t xml:space="preserve">DK Metcalf</t>
+    <t xml:space="preserve">Jaylen Waddle</t>
   </si>
   <si>
     <t xml:space="preserve">George Pickens</t>
@@ -296,7 +314,7 @@
     <t xml:space="preserve">Chris Godwin</t>
   </si>
   <si>
-    <t xml:space="preserve">Xavier Worthy</t>
+    <t xml:space="preserve">Jermaine Burton</t>
   </si>
   <si>
     <t xml:space="preserve">Sterling Shepard</t>
@@ -305,7 +323,7 @@
     <t xml:space="preserve">Nico Collins</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaylen Waddle</t>
+    <t xml:space="preserve">Cooper Kupp</t>
   </si>
   <si>
     <t xml:space="preserve">Jakobi Meyers</t>
@@ -314,7 +332,10 @@
     <t xml:space="preserve">DJ Moore</t>
   </si>
   <si>
-    <t xml:space="preserve">Jermaine Burton</t>
+    <t xml:space="preserve">TE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.J. Hockenson</t>
   </si>
   <si>
     <t xml:space="preserve">Jalen Tolbert</t>
@@ -323,7 +344,7 @@
     <t xml:space="preserve">Calvin Ridley</t>
   </si>
   <si>
-    <t xml:space="preserve">Cooper Kupp</t>
+    <t xml:space="preserve">Zay Flowers</t>
   </si>
   <si>
     <t xml:space="preserve">Rondale Moore</t>
@@ -332,13 +353,16 @@
     <t xml:space="preserve">Rashod Bateman</t>
   </si>
   <si>
+    <t xml:space="preserve">Trey McBride</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marquez Valdes-Scantling</t>
   </si>
   <si>
     <t xml:space="preserve">Xavier Legette</t>
   </si>
   <si>
-    <t xml:space="preserve">Zay Flowers</t>
+    <t xml:space="preserve">Sam LaPorta</t>
   </si>
   <si>
     <t xml:space="preserve">Wan’Dale Robinson</t>
@@ -347,10 +371,7 @@
     <t xml:space="preserve">Darnell Mooney</t>
   </si>
   <si>
-    <t xml:space="preserve">TE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T.J. Hockenson</t>
+    <t xml:space="preserve">Dalton Kincaid</t>
   </si>
   <si>
     <t xml:space="preserve">Ray Ray McCloud</t>
@@ -359,7 +380,7 @@
     <t xml:space="preserve">Rome Odunze</t>
   </si>
   <si>
-    <t xml:space="preserve">Sam LaPorta</t>
+    <t xml:space="preserve">Jake Furgeson</t>
   </si>
   <si>
     <t xml:space="preserve">Troy Franklin</t>
@@ -368,7 +389,10 @@
     <t xml:space="preserve">Kayshon Boutte</t>
   </si>
   <si>
-    <t xml:space="preserve">Trey McBride</t>
+    <t xml:space="preserve">DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antoine Winfield Jr.</t>
   </si>
   <si>
     <t xml:space="preserve">Tyler Lockett</t>
@@ -377,7 +401,7 @@
     <t xml:space="preserve">Malik Washington</t>
   </si>
   <si>
-    <t xml:space="preserve">Jake Furgeson</t>
+    <t xml:space="preserve">Chigoziem Okonkwo</t>
   </si>
   <si>
     <t xml:space="preserve">Jordan Whittington</t>
@@ -386,7 +410,7 @@
     <t xml:space="preserve">Brandin Cooks</t>
   </si>
   <si>
-    <t xml:space="preserve">Dalton Kincaid</t>
+    <t xml:space="preserve">Budda Baker</t>
   </si>
   <si>
     <t xml:space="preserve">Lil’Joran Humphrey</t>
@@ -395,7 +419,7 @@
     <t xml:space="preserve">Dyami Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Chigoziem Okonkwo</t>
+    <t xml:space="preserve">Derwin James Jr</t>
   </si>
   <si>
     <t xml:space="preserve">Tim Patrick</t>
@@ -404,10 +428,7 @@
     <t xml:space="preserve">Andrei Iosivias</t>
   </si>
   <si>
-    <t xml:space="preserve">DB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antoine Winfield Jr.</t>
+    <t xml:space="preserve">Tyler Nubin</t>
   </si>
   <si>
     <t xml:space="preserve">Adonai Mitchell</t>
@@ -416,7 +437,7 @@
     <t xml:space="preserve">Noah Brown</t>
   </si>
   <si>
-    <t xml:space="preserve">Derwin James Jr</t>
+    <t xml:space="preserve">Kevin Byard</t>
   </si>
   <si>
     <t xml:space="preserve">Dalton Shultz</t>
@@ -425,7 +446,10 @@
     <t xml:space="preserve">Ja’Lynn Polk</t>
   </si>
   <si>
-    <t xml:space="preserve">Budda Baker</t>
+    <t xml:space="preserve">DL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwity Paye</t>
   </si>
   <si>
     <t xml:space="preserve">Javon Baker</t>
@@ -434,279 +458,255 @@
     <t xml:space="preserve">Rashee Rice</t>
   </si>
   <si>
-    <t xml:space="preserve">Kevin Byard</t>
+    <t xml:space="preserve">Kyle Dugger</t>
   </si>
   <si>
     <t xml:space="preserve">Isaiah Likely</t>
   </si>
   <si>
+    <t xml:space="preserve">Myles Garrett</t>
+  </si>
+  <si>
     <t xml:space="preserve">George Kittle</t>
   </si>
   <si>
-    <t xml:space="preserve">Tyler Nubin</t>
+    <t xml:space="preserve">Josh Downs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Hubbard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucker Kraft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat Freiermuth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick bosa</t>
   </si>
   <si>
     <t xml:space="preserve">Juwan Johnson</t>
   </si>
   <si>
-    <t xml:space="preserve">Josh Downs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Dugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucker Kraft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pat Freiermuth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Owens</t>
+    <t xml:space="preserve">Mark Andrews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montez Sweat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erick all Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cade Otten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maxxx Crosby</t>
   </si>
   <si>
     <t xml:space="preserve">Noah Gray</t>
   </si>
   <si>
-    <t xml:space="preserve">Mark Andrews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Hubbard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erick all Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cade Otten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwity Paye</t>
+    <t xml:space="preserve">Hunter Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carl Granderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jessie Bates III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Mayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Anderson</t>
   </si>
   <si>
     <t xml:space="preserve">Noah Fant</t>
   </si>
   <si>
-    <t xml:space="preserve">Hunter Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montez Sweat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jessie Bates III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Mayer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kris Jenkins Jr</t>
+    <t xml:space="preserve">Brenton Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Woods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zack Baun</t>
   </si>
   <si>
     <t xml:space="preserve">Kerby Jospeh</t>
   </si>
   <si>
-    <t xml:space="preserve">Brenton Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carl Granderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Woods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myles Garrett</t>
+    <t xml:space="preserve">Julian Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calijah Kancey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alontea Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tre’von Moehrig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roquan Smith</t>
   </si>
   <si>
     <t xml:space="preserve">Ar’Darius Washington</t>
   </si>
   <si>
-    <t xml:space="preserve">Julian Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danielle Hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alontea Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tre’von Moehrig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick bosa</t>
+    <t xml:space="preserve">Quintin Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quay Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devon Witherspoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damar Hamlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ernest Jones</t>
   </si>
   <si>
     <t xml:space="preserve">Harrison ‘Hitman’ Smith</t>
   </si>
   <si>
-    <t xml:space="preserve">Quintin Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calijah Kancey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devon Witherspoon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damar Hamlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maxxx Crosby</t>
+    <t xml:space="preserve">Jared Verse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foyesade Oluokun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micah Parsons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeShon Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azeez Al-Shaair</t>
   </si>
   <si>
     <t xml:space="preserve">Rashan Gary</t>
   </si>
   <si>
-    <t xml:space="preserve">Jared Verse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quay Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micah Parsons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeShon Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Anderson</t>
+    <t xml:space="preserve">Greg Rousseau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dante Fowler Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byron Murphy II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Pace Jr.</t>
   </si>
   <si>
     <t xml:space="preserve">Adam Butler</t>
   </si>
   <si>
-    <t xml:space="preserve">Greg Rousseau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foyesade Oluokun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dante Fowler Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byron Murphy II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zack Baun</t>
+    <t xml:space="preserve">A’Shawn Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joryn Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.J. Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Carter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Barton</t>
   </si>
   <si>
     <t xml:space="preserve">Daron Payne</t>
   </si>
   <si>
-    <t xml:space="preserve">A’Shawn Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.J. Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Carter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Barton</t>
+    <t xml:space="preserve">Trey Hendrickson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyzir White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nik Bonitto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Za’Darius Smith</t>
   </si>
   <si>
     <t xml:space="preserve">Alim McNeil</t>
   </si>
   <si>
-    <t xml:space="preserve">Trey Hendrickson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joryn Brooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nik Bonitto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Za’Darius Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roquan Smith</t>
+    <t xml:space="preserve">Fred Warner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Smith Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micah McFadden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamien Sherwood</t>
   </si>
   <si>
     <t xml:space="preserve">Akeem Davis-Gaither</t>
   </si>
   <si>
-    <t xml:space="preserve">Fred Warner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyzir White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micah McFadden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamien Sherwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ernest Jones</t>
+    <t xml:space="preserve">Henry To’oTo’o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorian Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiyan Henley</t>
   </si>
   <si>
     <t xml:space="preserve">Drue Tranquill</t>
   </si>
   <si>
-    <t xml:space="preserve">Henry To’oTo’o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Smith Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dorian Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daiyan Henley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payton Wilson</t>
+    <t xml:space="preserve">Kaden Ellis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lavonte David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Queen</t>
   </si>
   <si>
     <t xml:space="preserve">Tryrice Knight</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaden Ellis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lavonte David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patrick Queen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azeez Al-Shaair</t>
+    <t xml:space="preserve">Junior Colson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Anzalone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas Turner</t>
   </si>
   <si>
     <t xml:space="preserve">Bobby Okereke</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior Colson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Anzalone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas Turner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivan Pace Jr.</t>
+    <t xml:space="preserve">DeMavion Overshown</t>
   </si>
   <si>
     <t xml:space="preserve">Jonathoan Greenard</t>
   </si>
   <si>
-    <t xml:space="preserve">DeMavion Overshown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevin Wallace</t>
-  </si>
-  <si>
     <t xml:space="preserve">Go Pack Go – Josh L</t>
   </si>
   <si>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">Magik Skol Bus – Brandon Hurd</t>
   </si>
   <si>
-    <t xml:space="preserve">Folding Table Repair Man - </t>
+    <t xml:space="preserve">Folding Table Repair Man -  CJ perry</t>
   </si>
   <si>
     <t xml:space="preserve">Bryce Young</t>
@@ -1319,33 +1319,33 @@
     <t xml:space="preserve">Matt Milano</t>
   </si>
   <si>
+    <t xml:space="preserve">Jack Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omar Speights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.J. Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.J.Watt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Owusu-Koramoah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dre Greenlaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quincy Williams</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nakobe Dean</t>
   </si>
   <si>
-    <t xml:space="preserve">Omar Speights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T.J. Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T.J.Watt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dre Greenlaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quincy Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Owusu-Koramoah</t>
-  </si>
-  <si>
     <t xml:space="preserve">C.J. Mosley</t>
   </si>
   <si>
@@ -1370,6 +1370,9 @@
     <t xml:space="preserve">Folding Table</t>
   </si>
   <si>
+    <t xml:space="preserve">cjperry1284@yahoo.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Benjamin Luther</t>
   </si>
   <si>
@@ -1460,174 +1463,174 @@
     <t xml:space="preserve">2026 1 John O</t>
   </si>
   <si>
+    <t xml:space="preserve">2025 3 3.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 John O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Matt H</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 1 1.12</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 1 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 John O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Matt H</t>
+    <t xml:space="preserve">2026 3 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Matt H</t>
   </si>
   <si>
     <t xml:space="preserve">2025 3 3.09</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 3 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Matt H</t>
+    <t xml:space="preserve">2026 4 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 John O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Matt H</t>
   </si>
   <si>
     <t xml:space="preserve">2025 3 3.06</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 4 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 John O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Matt H</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 5 Alan</t>
   </si>
   <si>
     <t xml:space="preserve">2026 4 John O</t>
   </si>
   <si>
+    <t xml:space="preserve">2025 5 5.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 John O</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 4 4.11</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 5 John O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.12</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025 4 4.07</t>
   </si>
   <si>
@@ -1649,7 +1652,7 @@
     <t xml:space="preserve">Brandon</t>
   </si>
   <si>
-    <t xml:space="preserve">Steve</t>
+    <t xml:space="preserve">CJ</t>
   </si>
   <si>
     <t xml:space="preserve">2025 1 1.06</t>
@@ -1661,28 +1664,28 @@
     <t xml:space="preserve">2026 1 Vanja</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 Rhode</t>
+    <t xml:space="preserve">2025 1.4</t>
   </si>
   <si>
     <t xml:space="preserve">2026 1 Rhode</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 Joe Luke</t>
+    <t xml:space="preserve">2025 1.3</t>
   </si>
   <si>
     <t xml:space="preserve">2026 1 Joe Luke</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 Brandon</t>
+    <t xml:space="preserve">2025 1.2</t>
   </si>
   <si>
     <t xml:space="preserve">2026 1 Brandon</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 Steve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Steve</t>
+    <t xml:space="preserve">2025 1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 CJ Perry</t>
   </si>
   <si>
     <t xml:space="preserve">2025 2 2.05</t>
@@ -1694,28 +1697,28 @@
     <t xml:space="preserve">2026 2 Vanja</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 2 Rhode</t>
+    <t xml:space="preserve">2025 2.4</t>
   </si>
   <si>
     <t xml:space="preserve">2026 2 Rhode</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 2 Joe Luke</t>
+    <t xml:space="preserve">2025 2.3</t>
   </si>
   <si>
     <t xml:space="preserve">2026 2 Joe Luke</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 2 Brandon</t>
+    <t xml:space="preserve">2025 2.2</t>
   </si>
   <si>
     <t xml:space="preserve">2026 2 Brandon</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 2 Steve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Steve</t>
+    <t xml:space="preserve">2025 2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 CJ Perry</t>
   </si>
   <si>
     <t xml:space="preserve">2025 2 2.06</t>
@@ -1727,28 +1730,28 @@
     <t xml:space="preserve">2026 3 Vanja</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 Rhode</t>
+    <t xml:space="preserve">2025 3.4</t>
   </si>
   <si>
     <t xml:space="preserve">2026 3 Rhode</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 Joe Luke</t>
+    <t xml:space="preserve">2025 3.3</t>
   </si>
   <si>
     <t xml:space="preserve">2026 3 Joe Luke</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 Brandon</t>
+    <t xml:space="preserve">2025 3.2</t>
   </si>
   <si>
     <t xml:space="preserve">2026 3 Brandon</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 Steve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Steve</t>
+    <t xml:space="preserve">2025 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 CJ Perry</t>
   </si>
   <si>
     <t xml:space="preserve">2025 2 2.09</t>
@@ -1760,28 +1763,28 @@
     <t xml:space="preserve">2026 4 Vanja</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 4 Rhode</t>
+    <t xml:space="preserve">2025 4.4</t>
   </si>
   <si>
     <t xml:space="preserve">2026 4 Rhode</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 4 Joe Luke</t>
+    <t xml:space="preserve">2025 4.3</t>
   </si>
   <si>
     <t xml:space="preserve">2026 4 Joe Luke</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 4 Brandon</t>
+    <t xml:space="preserve">2025 4.2</t>
   </si>
   <si>
     <t xml:space="preserve">2026 4 Brandon</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 4 Steve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Steve</t>
+    <t xml:space="preserve">2025 4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 CJ Perry</t>
   </si>
   <si>
     <t xml:space="preserve">2025 2 2.11</t>
@@ -1793,28 +1796,28 @@
     <t xml:space="preserve">2026 5 Vanja</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 5 Rhode</t>
+    <t xml:space="preserve">2025 5.4</t>
   </si>
   <si>
     <t xml:space="preserve">2026 5 Rhode</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 5 Joe Luke</t>
+    <t xml:space="preserve">2025 5.3</t>
   </si>
   <si>
     <t xml:space="preserve">2026 5 Joe Luke</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 5 Brandon</t>
+    <t xml:space="preserve">2025 5.2</t>
   </si>
   <si>
     <t xml:space="preserve">2026 5 Brandon</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 5 Steve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Steve</t>
+    <t xml:space="preserve">2025 5.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 CJ Perry</t>
   </si>
   <si>
     <t xml:space="preserve">2025 3 3.11</t>
@@ -1835,7 +1838,7 @@
     <t xml:space="preserve">Draft order</t>
   </si>
   <si>
-    <t xml:space="preserve">Steve cohen</t>
+    <t xml:space="preserve">CJ Perry</t>
   </si>
   <si>
     <t xml:space="preserve">Joe Burres Luke Longly</t>
@@ -1878,6 +1881,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jonathan Greenard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.09</t>
   </si>
   <si>
     <t xml:space="preserve">2026 pick trades</t>
@@ -1898,6 +1904,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1920,6 +1927,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1929,6 +1937,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u val="single"/>
@@ -1936,12 +1945,14 @@
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFC9211E"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1950,12 +1961,14 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="32"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -2114,7 +2127,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2159,12 +2172,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2228,6 +2241,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2317,7 +2338,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB118"/>
+  <dimension ref="B1:AB118"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8.21"/>
@@ -2418,974 +2439,968 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="4"/>
+      <c r="C3" s="0" t="s">
+        <v>15</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N3" s="4"/>
       <c r="O3" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V3" s="4"/>
       <c r="W3" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="0" t="s">
-        <v>21</v>
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N4" s="4"/>
       <c r="O4" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="S4" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V4" s="4"/>
       <c r="W4" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="AB4" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="B5" s="6"/>
       <c r="C5" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="O5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R5" s="6"/>
       <c r="S5" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V5" s="4"/>
       <c r="W5" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="AB5" s="0" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6"/>
       <c r="C6" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>22</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="N6" s="6"/>
       <c r="O6" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="R6" s="6"/>
       <c r="S6" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="V6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="W6" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
+      </c>
+      <c r="AB6" s="0" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6"/>
       <c r="C7" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R7" s="6"/>
       <c r="S7" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="V7" s="6"/>
       <c r="W7" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
+      </c>
+      <c r="AB7" s="0" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6"/>
       <c r="C8" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="R8" s="6"/>
       <c r="S8" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="V8" s="6"/>
       <c r="W8" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
+      </c>
+      <c r="AB8" s="0" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6"/>
+      <c r="B9" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="C9" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="5" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="R9" s="6"/>
       <c r="S9" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="V9" s="6"/>
       <c r="W9" s="0" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="B10" s="7"/>
       <c r="C10" s="5" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="N10" s="6"/>
+        <v>68</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>59</v>
+      </c>
       <c r="O10" s="5" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="R10" s="6"/>
       <c r="S10" s="0" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="V10" s="6"/>
       <c r="W10" s="0" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7"/>
       <c r="C11" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="5" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="N11" s="7"/>
       <c r="O11" s="5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="R11" s="6"/>
       <c r="S11" s="0" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="V11" s="6"/>
       <c r="W11" s="0" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="7"/>
       <c r="C12" s="5" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>59</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="0" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="5" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="R12" s="7" t="s">
         <v>59</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="V12" s="6"/>
       <c r="W12" s="0" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="7"/>
-      <c r="C13" s="5" t="s">
-        <v>78</v>
+      <c r="C13" s="0" t="s">
+        <v>84</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>59</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="5" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="V13" s="6"/>
       <c r="W13" s="5" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="7"/>
       <c r="C14" s="0" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="5" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="5" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="V14" s="7" t="s">
         <v>59</v>
       </c>
       <c r="W14" s="5" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="7"/>
       <c r="C15" s="0" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="V15" s="7"/>
       <c r="W15" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7"/>
-      <c r="C16" s="0" t="s">
-        <v>96</v>
+      <c r="B16" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="5" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="N16" s="7"/>
-      <c r="O16" s="5" t="s">
-        <v>99</v>
+      <c r="O16" s="0" t="s">
+        <v>106</v>
       </c>
       <c r="R16" s="7"/>
       <c r="S16" s="5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="V16" s="7"/>
       <c r="W16" s="5" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="8"/>
+      <c r="C17" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="F17" s="7"/>
       <c r="G17" s="5" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="N17" s="7"/>
-      <c r="O17" s="0" t="s">
-        <v>104</v>
+        <v>111</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="R17" s="7"/>
       <c r="S17" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="V17" s="7"/>
       <c r="W17" s="5" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8" t="s">
-        <v>107</v>
-      </c>
+      <c r="B18" s="8"/>
       <c r="C18" s="5" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="J18" s="7"/>
       <c r="K18" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>107</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="N18" s="8"/>
       <c r="O18" s="5" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="R18" s="7"/>
       <c r="S18" s="0" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="V18" s="7"/>
       <c r="W18" s="0" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="8"/>
+      <c r="B19" s="9" t="s">
+        <v>121</v>
+      </c>
       <c r="C19" s="5" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="5" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="J19" s="7"/>
       <c r="K19" s="5" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="N19" s="8"/>
       <c r="O19" s="5" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="0" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="V19" s="7"/>
       <c r="W19" s="0" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="8"/>
+      <c r="B20" s="9"/>
       <c r="C20" s="5" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="5" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="J20" s="7"/>
       <c r="K20" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="N20" s="8"/>
+        <v>130</v>
+      </c>
+      <c r="N20" s="9" t="s">
+        <v>121</v>
+      </c>
       <c r="O20" s="5" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="R20" s="7"/>
       <c r="S20" s="0" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="V20" s="7"/>
       <c r="W20" s="0" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>127</v>
+      <c r="B21" s="9"/>
+      <c r="C21" s="0" t="s">
+        <v>134</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="0" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="J21" s="7"/>
       <c r="K21" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>126</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N21" s="9"/>
       <c r="O21" s="5" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="R21" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="V21" s="7"/>
       <c r="W21" s="0" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="9"/>
-      <c r="C22" s="5" t="s">
-        <v>133</v>
+      <c r="B22" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>141</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="0" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="N22" s="9"/>
       <c r="O22" s="5" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="R22" s="8"/>
       <c r="S22" s="5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="V22" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="W22" s="5" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="9"/>
-      <c r="C23" s="0" t="s">
-        <v>139</v>
+      <c r="B23" s="10"/>
+      <c r="C23" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="N23" s="9"/>
+        <v>148</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="O23" s="5" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="R23" s="8"/>
       <c r="S23" s="0" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="V23" s="8"/>
       <c r="W23" s="5" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9"/>
-      <c r="C24" s="0" t="s">
-        <v>145</v>
+      <c r="B24" s="10"/>
+      <c r="C24" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="F24" s="8"/>
-      <c r="G24" s="0" t="s">
-        <v>146</v>
+      <c r="G24" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>147</v>
-      </c>
-      <c r="N24" s="10" t="s">
-        <v>148</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N24" s="10"/>
       <c r="O24" s="5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="R24" s="8"/>
       <c r="S24" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="V24" s="8"/>
       <c r="W24" s="5" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>152</v>
+      <c r="B25" s="10"/>
+      <c r="C25" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="0" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="0" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="N25" s="10"/>
       <c r="O25" s="5" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="R25" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="V25" s="8"/>
       <c r="W25" s="0" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="10"/>
-      <c r="C26" s="0" t="s">
-        <v>158</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>126</v>
-      </c>
+      <c r="C26" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F26" s="8"/>
       <c r="G26" s="0" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J26" s="8"/>
       <c r="K26" s="0" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="N26" s="10"/>
-      <c r="O26" s="5" t="s">
-        <v>161</v>
+      <c r="O26" s="0" t="s">
+        <v>167</v>
       </c>
       <c r="R26" s="9"/>
       <c r="S26" s="0" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="V26" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="W26" s="5" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10"/>
+      <c r="B27" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="C27" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="11" t="s">
-        <v>165</v>
+        <v>171</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27" s="0" t="s">
+        <v>172</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="N27" s="10"/>
       <c r="O27" s="0" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="R27" s="9"/>
       <c r="S27" s="5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="5" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="10"/>
+      <c r="B28" s="11"/>
       <c r="C28" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F28" s="9"/>
-      <c r="G28" s="0" t="s">
-        <v>171</v>
+      <c r="G28" s="12" t="s">
+        <v>178</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="N28" s="10"/>
+        <v>179</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="O28" s="0" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="R28" s="9"/>
       <c r="S28" s="5" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="V28" s="9"/>
       <c r="W28" s="5" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10"/>
+      <c r="B29" s="11"/>
       <c r="C29" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>148</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="F29" s="9"/>
       <c r="G29" s="0" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="N29" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="O29" s="0" t="s">
-        <v>180</v>
+        <v>185</v>
+      </c>
+      <c r="N29" s="11"/>
+      <c r="O29" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="R29" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="V29" s="9"/>
       <c r="W29" s="0" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="10"/>
-      <c r="C30" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>140</v>
+      </c>
       <c r="G30" s="0" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="J30" s="10"/>
       <c r="K30" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="N30" s="12"/>
+        <v>191</v>
+      </c>
+      <c r="N30" s="11"/>
       <c r="O30" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="R30" s="10"/>
       <c r="S30" s="5" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="V30" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="W30" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AB30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>189</v>
+      <c r="B31" s="11"/>
+      <c r="C31" s="0" t="s">
+        <v>195</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="0" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="J31" s="10"/>
       <c r="K31" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="N31" s="12"/>
+        <v>197</v>
+      </c>
+      <c r="N31" s="11"/>
       <c r="O31" s="5" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="R31" s="10"/>
       <c r="S31" s="5" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="V31" s="10"/>
       <c r="W31" s="5" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="AB31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="12"/>
+      <c r="B32" s="11"/>
       <c r="C32" s="5" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="0" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="J32" s="10"/>
-      <c r="K32" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="N32" s="12"/>
-      <c r="O32" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="R32" s="12" t="s">
-        <v>179</v>
+      <c r="K32" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="N32" s="11"/>
+      <c r="O32" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="R32" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="S32" s="0" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="V32" s="10"/>
       <c r="W32" s="0" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="AB32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="12"/>
-      <c r="C33" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>179</v>
-      </c>
+      <c r="F33" s="10"/>
       <c r="G33" s="0" t="s">
-        <v>202</v>
-      </c>
-      <c r="J33" s="12" t="s">
-        <v>179</v>
+        <v>207</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="N33" s="12"/>
+        <v>208</v>
+      </c>
+      <c r="N33" s="11"/>
       <c r="O33" s="0" t="s">
-        <v>204</v>
-      </c>
-      <c r="R33" s="12"/>
+        <v>209</v>
+      </c>
+      <c r="R33" s="11"/>
       <c r="S33" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="V33" s="12" t="s">
-        <v>179</v>
+        <v>210</v>
+      </c>
+      <c r="V33" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="W33" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="12"/>
-      <c r="C34" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="F34" s="12"/>
+      <c r="F34" s="11" t="s">
+        <v>170</v>
+      </c>
       <c r="G34" s="0" t="s">
-        <v>208</v>
-      </c>
-      <c r="J34" s="12"/>
+        <v>212</v>
+      </c>
+      <c r="J34" s="11"/>
       <c r="K34" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="N34" s="12"/>
-      <c r="O34" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="R34" s="12"/>
+        <v>213</v>
+      </c>
+      <c r="R34" s="11"/>
       <c r="S34" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="V34" s="12"/>
+        <v>214</v>
+      </c>
+      <c r="V34" s="11"/>
       <c r="W34" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="12"/>
-      <c r="C35" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="F35" s="12"/>
+      <c r="F35" s="11"/>
       <c r="G35" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="J35" s="12"/>
+        <v>216</v>
+      </c>
+      <c r="J35" s="11"/>
       <c r="K35" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="R35" s="12"/>
+        <v>217</v>
+      </c>
+      <c r="R35" s="11"/>
       <c r="S35" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="V35" s="12"/>
+        <v>218</v>
+      </c>
+      <c r="V35" s="11"/>
       <c r="W35" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="12"/>
-      <c r="C36" s="0" t="s">
-        <v>218</v>
-      </c>
-      <c r="F36" s="12"/>
+      <c r="F36" s="11"/>
       <c r="G36" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="J36" s="12"/>
+        <v>220</v>
+      </c>
+      <c r="J36" s="11"/>
       <c r="K36" s="0" t="s">
-        <v>220</v>
-      </c>
-      <c r="R36" s="12"/>
+        <v>221</v>
+      </c>
+      <c r="R36" s="11"/>
       <c r="S36" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="V36" s="12"/>
+        <v>222</v>
+      </c>
+      <c r="V36" s="11"/>
       <c r="W36" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="12"/>
-      <c r="C37" s="0" t="s">
-        <v>223</v>
-      </c>
-      <c r="F37" s="12"/>
-      <c r="G37" s="5" t="s">
+      <c r="F37" s="11"/>
+      <c r="G37" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="V37" s="12"/>
+      <c r="V37" s="11"/>
       <c r="W37" s="0" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="12"/>
-      <c r="C38" s="0" t="s">
+      <c r="F38" s="11"/>
+      <c r="G38" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="G38" s="5"/>
       <c r="S38" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3422,9 +3437,6 @@
       <c r="W45" s="1"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
-        <v>1</v>
-      </c>
       <c r="B46" s="4" t="s">
         <v>7</v>
       </c>
@@ -3463,9 +3475,6 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
-        <v>2</v>
-      </c>
       <c r="B47" s="4"/>
       <c r="C47" s="5" t="s">
         <v>239</v>
@@ -3493,9 +3502,6 @@
       <c r="AB47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
-        <v>3</v>
-      </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
         <v>245</v>
@@ -3524,9 +3530,6 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
-        <v>4</v>
-      </c>
       <c r="B49" s="6" t="s">
         <v>22</v>
       </c>
@@ -3560,9 +3563,6 @@
       <c r="Y49" s="15"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
-        <v>5</v>
-      </c>
       <c r="B50" s="6"/>
       <c r="C50" s="5" t="s">
         <v>257</v>
@@ -3591,9 +3591,6 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
-        <v>6</v>
-      </c>
       <c r="B51" s="6"/>
       <c r="C51" s="0" t="s">
         <v>263</v>
@@ -3622,9 +3619,6 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
-        <v>7</v>
-      </c>
       <c r="B52" s="6"/>
       <c r="C52" s="5" t="s">
         <v>269</v>
@@ -3651,9 +3645,6 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
-        <v>8</v>
-      </c>
       <c r="B53" s="6"/>
       <c r="C53" s="5" t="s">
         <v>275</v>
@@ -3680,9 +3671,6 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
-        <v>9</v>
-      </c>
       <c r="B54" s="6"/>
       <c r="C54" s="5" t="s">
         <v>281</v>
@@ -3709,9 +3697,6 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
-        <v>10</v>
-      </c>
       <c r="B55" s="6"/>
       <c r="C55" s="5" t="s">
         <v>287</v>
@@ -3740,9 +3725,6 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
-        <v>11</v>
-      </c>
       <c r="B56" s="7" t="s">
         <v>59</v>
       </c>
@@ -3775,9 +3757,6 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
-        <v>12</v>
-      </c>
       <c r="B57" s="7"/>
       <c r="C57" s="5" t="s">
         <v>299</v>
@@ -3806,9 +3785,6 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="n">
-        <v>13</v>
-      </c>
       <c r="B58" s="7"/>
       <c r="C58" s="5" t="s">
         <v>305</v>
@@ -3837,9 +3813,6 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="n">
-        <v>14</v>
-      </c>
       <c r="B59" s="7"/>
       <c r="C59" s="5" t="s">
         <v>311</v>
@@ -3866,9 +3839,6 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="n">
-        <v>15</v>
-      </c>
       <c r="B60" s="7"/>
       <c r="C60" s="5" t="s">
         <v>317</v>
@@ -3895,9 +3865,6 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="n">
-        <v>16</v>
-      </c>
       <c r="B61" s="7"/>
       <c r="C61" s="5" t="s">
         <v>323</v>
@@ -3924,9 +3891,6 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="n">
-        <v>17</v>
-      </c>
       <c r="B62" s="7"/>
       <c r="C62" s="5" t="s">
         <v>329</v>
@@ -3953,9 +3917,6 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="n">
-        <v>18</v>
-      </c>
       <c r="B63" s="7"/>
       <c r="C63" s="0" t="s">
         <v>335</v>
@@ -3965,7 +3926,7 @@
         <v>336</v>
       </c>
       <c r="J63" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K63" s="5" t="s">
         <v>337</v>
@@ -3984,9 +3945,6 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="n">
-        <v>19</v>
-      </c>
       <c r="B64" s="7"/>
       <c r="C64" s="5" t="s">
         <v>341</v>
@@ -4000,7 +3958,7 @@
         <v>343</v>
       </c>
       <c r="N64" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="O64" s="5" t="s">
         <v>344</v>
@@ -4015,11 +3973,8 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="n">
-        <v>20</v>
-      </c>
       <c r="B65" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C65" s="5" t="s">
         <v>347</v>
@@ -4046,27 +4001,24 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="n">
-        <v>21</v>
-      </c>
       <c r="B66" s="8"/>
       <c r="C66" s="5" t="s">
         <v>353</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>354</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K66" s="5" t="s">
         <v>355</v>
       </c>
       <c r="N66" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="O66" s="5" t="s">
         <v>356</v>
@@ -4081,9 +4033,6 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="n">
-        <v>22</v>
-      </c>
       <c r="B67" s="8"/>
       <c r="C67" s="0" t="s">
         <v>359</v>
@@ -4101,7 +4050,7 @@
         <v>362</v>
       </c>
       <c r="R67" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="S67" s="5" t="s">
         <v>363</v>
@@ -4112,11 +4061,8 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="n">
-        <v>23</v>
-      </c>
       <c r="B68" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C68" s="0" t="s">
         <v>365</v>
@@ -4138,34 +4084,31 @@
         <v>369</v>
       </c>
       <c r="V68" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="W68" s="0" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="n">
-        <v>24</v>
-      </c>
       <c r="B69" s="9"/>
       <c r="C69" s="5" t="s">
         <v>371</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G69" s="5" t="s">
         <v>372</v>
       </c>
       <c r="J69" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K69" s="5" t="s">
         <v>373</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="O69" s="0" t="s">
         <v>374</v>
@@ -4180,9 +4123,6 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="n">
-        <v>25</v>
-      </c>
       <c r="B70" s="9"/>
       <c r="C70" s="0" t="s">
         <v>377</v>
@@ -4200,7 +4140,7 @@
         <v>380</v>
       </c>
       <c r="R70" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="S70" s="5" t="s">
         <v>381</v>
@@ -4211,9 +4151,6 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="n">
-        <v>26</v>
-      </c>
       <c r="B71" s="9"/>
       <c r="C71" s="0" t="s">
         <v>383</v>
@@ -4235,16 +4172,13 @@
         <v>387</v>
       </c>
       <c r="V71" s="9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="W71" s="0" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="n">
-        <v>27</v>
-      </c>
       <c r="B72" s="9"/>
       <c r="C72" s="0" t="s">
         <v>389</v>
@@ -4271,17 +4205,14 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="n">
-        <v>28</v>
-      </c>
       <c r="B73" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="C73" s="0" t="s">
         <v>395</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="G73" s="5" t="s">
         <v>396</v>
@@ -4295,7 +4226,7 @@
         <v>398</v>
       </c>
       <c r="R73" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="S73" s="0" t="s">
         <v>399</v>
@@ -4306,9 +4237,6 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="n">
-        <v>29</v>
-      </c>
       <c r="B74" s="10"/>
       <c r="C74" s="0" t="s">
         <v>401</v>
@@ -4321,8 +4249,8 @@
       <c r="K74" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="N74" s="12" t="s">
-        <v>179</v>
+      <c r="N74" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="O74" s="0" t="s">
         <v>404</v>
@@ -4332,7 +4260,7 @@
         <v>405</v>
       </c>
       <c r="V74" s="10" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="W74" s="0" t="s">
         <v>406</v>
@@ -4340,9 +4268,6 @@
       <c r="AB74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="n">
-        <v>30</v>
-      </c>
       <c r="B75" s="10"/>
       <c r="C75" s="0" t="s">
         <v>407</v>
@@ -4355,7 +4280,7 @@
       <c r="K75" s="0" t="s">
         <v>409</v>
       </c>
-      <c r="N75" s="12"/>
+      <c r="N75" s="11"/>
       <c r="O75" s="0" t="s">
         <v>410</v>
       </c>
@@ -4370,9 +4295,6 @@
       <c r="AB75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="n">
-        <v>31</v>
-      </c>
       <c r="B76" s="10"/>
       <c r="C76" s="0" t="s">
         <v>413</v>
@@ -4381,13 +4303,13 @@
       <c r="G76" s="0" t="s">
         <v>414</v>
       </c>
-      <c r="J76" s="12" t="s">
-        <v>179</v>
+      <c r="J76" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="K76" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="N76" s="12"/>
+      <c r="N76" s="11"/>
       <c r="O76" s="0" t="s">
         <v>416</v>
       </c>
@@ -4402,26 +4324,23 @@
       <c r="AB76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="n">
-        <v>32</v>
-      </c>
       <c r="B77" s="16" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="F77" s="12" t="s">
-        <v>179</v>
+      <c r="F77" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="J77" s="12"/>
+      <c r="J77" s="11"/>
       <c r="K77" s="5" t="s">
         <v>421</v>
       </c>
-      <c r="N77" s="12"/>
+      <c r="N77" s="11"/>
       <c r="O77" s="0" t="s">
         <v>422</v>
       </c>
@@ -4435,105 +4354,96 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="n">
-        <v>33</v>
-      </c>
       <c r="B78" s="16"/>
       <c r="C78" s="0" t="s">
         <v>425</v>
       </c>
-      <c r="F78" s="12"/>
+      <c r="F78" s="11"/>
       <c r="G78" s="5" t="s">
         <v>426</v>
       </c>
-      <c r="J78" s="12"/>
+      <c r="J78" s="11"/>
       <c r="K78" s="0" t="s">
         <v>427</v>
       </c>
-      <c r="N78" s="12"/>
+      <c r="N78" s="11"/>
       <c r="O78" s="0" t="s">
         <v>428</v>
       </c>
-      <c r="R78" s="12" t="s">
-        <v>179</v>
+      <c r="R78" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="S78" s="0" t="s">
         <v>429</v>
       </c>
-      <c r="V78" s="12" t="s">
-        <v>179</v>
+      <c r="V78" s="11" t="s">
+        <v>170</v>
       </c>
       <c r="W78" s="0" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="n">
-        <v>34</v>
-      </c>
       <c r="B79" s="16"/>
       <c r="C79" s="0" t="s">
         <v>431</v>
       </c>
-      <c r="F79" s="12"/>
+      <c r="F79" s="11"/>
       <c r="G79" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="R79" s="12"/>
+      <c r="R79" s="11"/>
       <c r="S79" s="0" t="s">
         <v>433</v>
       </c>
-      <c r="V79" s="12"/>
+      <c r="V79" s="11"/>
       <c r="W79" s="0" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="n">
-        <v>35</v>
-      </c>
       <c r="B80" s="16"/>
-      <c r="C80" s="0" t="s">
+      <c r="C80" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="F80" s="12"/>
+      <c r="F80" s="11"/>
       <c r="G80" s="0" t="s">
         <v>436</v>
       </c>
-      <c r="R80" s="12"/>
+      <c r="R80" s="11"/>
       <c r="S80" s="0" t="s">
         <v>437</v>
       </c>
-      <c r="V80" s="12"/>
+      <c r="V80" s="11"/>
       <c r="W80" s="0" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="16"/>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="0" t="s">
         <v>439</v>
       </c>
-      <c r="F81" s="12"/>
+      <c r="F81" s="11"/>
       <c r="G81" s="0" t="s">
         <v>440</v>
       </c>
       <c r="H81" s="13"/>
-      <c r="R81" s="12"/>
+      <c r="R81" s="11"/>
       <c r="S81" s="0" t="s">
         <v>441</v>
       </c>
-      <c r="V81" s="12"/>
+      <c r="V81" s="11"/>
       <c r="W81" s="0" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F82" s="12"/>
+      <c r="F82" s="11"/>
       <c r="G82" s="0" t="s">
         <v>443</v>
       </c>
-      <c r="V82" s="12"/>
+      <c r="V82" s="11"/>
       <c r="W82" s="0" t="s">
         <v>444</v>
       </c>
@@ -4551,55 +4461,54 @@
       <c r="AB118" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="92">
+  <mergeCells count="91">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="V1:W1"/>
-    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B2:B3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="J2:J4"/>
-    <mergeCell ref="N2:N5"/>
+    <mergeCell ref="N2:N4"/>
     <mergeCell ref="R2:R3"/>
     <mergeCell ref="V2:V5"/>
+    <mergeCell ref="B4:B8"/>
     <mergeCell ref="F4:F11"/>
     <mergeCell ref="R4:R11"/>
-    <mergeCell ref="B5:B9"/>
     <mergeCell ref="J5:J12"/>
-    <mergeCell ref="N6:N10"/>
+    <mergeCell ref="N5:N9"/>
     <mergeCell ref="V6:V13"/>
-    <mergeCell ref="B10:B16"/>
-    <mergeCell ref="N11:N17"/>
+    <mergeCell ref="B9:B15"/>
+    <mergeCell ref="N10:N16"/>
     <mergeCell ref="F12:F22"/>
     <mergeCell ref="R12:R20"/>
     <mergeCell ref="J13:J23"/>
     <mergeCell ref="V14:V21"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="N18:N20"/>
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="N21:N23"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="N17:N19"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="N20:N22"/>
     <mergeCell ref="R21:R24"/>
+    <mergeCell ref="B22:B26"/>
     <mergeCell ref="V22:V25"/>
-    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="N23:N27"/>
     <mergeCell ref="J24:J26"/>
-    <mergeCell ref="N24:N28"/>
-    <mergeCell ref="B25:B28"/>
     <mergeCell ref="R25:R28"/>
-    <mergeCell ref="F26:F28"/>
     <mergeCell ref="V26:V29"/>
+    <mergeCell ref="F27:F29"/>
     <mergeCell ref="J27:J28"/>
-    <mergeCell ref="F29:F32"/>
+    <mergeCell ref="N28:N33"/>
     <mergeCell ref="J29:J32"/>
-    <mergeCell ref="N29:N34"/>
     <mergeCell ref="R29:R31"/>
+    <mergeCell ref="F30:F33"/>
     <mergeCell ref="V30:V32"/>
-    <mergeCell ref="B31:B38"/>
     <mergeCell ref="R32:R36"/>
-    <mergeCell ref="F33:F37"/>
     <mergeCell ref="J33:J36"/>
     <mergeCell ref="V33:V37"/>
+    <mergeCell ref="F34:F38"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="F45:G45"/>
     <mergeCell ref="J45:K45"/>
@@ -4678,107 +4587,109 @@
         <v>446</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>447</v>
       </c>
-      <c r="B2" s="17"/>
+      <c r="B2" s="17" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>451</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>452</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4787,17 +4698,18 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" display="Eranievanja@gmail.com"/>
-    <hyperlink ref="B3" r:id="rId2" display="blluther7@gmail.com"/>
-    <hyperlink ref="B4" r:id="rId3" display="john.olson8734@gmail.com"/>
-    <hyperlink ref="B5" r:id="rId4" display="JoeyBures@hotmail.com"/>
-    <hyperlink ref="B6" r:id="rId5" display="lukeb55@hotmail.com"/>
-    <hyperlink ref="B7" r:id="rId6" display="FieldsJared54@gmail.com"/>
-    <hyperlink ref="B8" r:id="rId7" display="bjhurd@hotmail.com"/>
-    <hyperlink ref="B9" r:id="rId8" display="roadrunner44@gmail.com"/>
-    <hyperlink ref="B10" r:id="rId9" display="Champion.ship5690@gmail.com"/>
-    <hyperlink ref="B11" r:id="rId10" display="adamwells12@gmail.com"/>
-    <hyperlink ref="B12" r:id="rId11" display="powellap28@gmail.com"/>
-    <hyperlink ref="B13" r:id="rId12" display="king_ahab11@hotmail.com"/>
+    <hyperlink ref="B2" r:id="rId2" display="cjperry1284@yahoo.com"/>
+    <hyperlink ref="B3" r:id="rId3" display="blluther7@gmail.com"/>
+    <hyperlink ref="B4" r:id="rId4" display="john.olson8734@gmail.com"/>
+    <hyperlink ref="B5" r:id="rId5" display="JoeyBures@hotmail.com"/>
+    <hyperlink ref="B6" r:id="rId6" display="lukeb55@hotmail.com"/>
+    <hyperlink ref="B7" r:id="rId7" display="FieldsJared54@gmail.com"/>
+    <hyperlink ref="B8" r:id="rId8" display="bjhurd@hotmail.com"/>
+    <hyperlink ref="B9" r:id="rId9" display="roadrunner44@gmail.com"/>
+    <hyperlink ref="B10" r:id="rId10" display="Champion.ship5690@gmail.com"/>
+    <hyperlink ref="B11" r:id="rId11" display="adamwells12@gmail.com"/>
+    <hyperlink ref="B12" r:id="rId12" display="powellap28@gmail.com"/>
+    <hyperlink ref="B13" r:id="rId13" display="king_ahab11@hotmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4839,185 +4751,185 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="19"/>
       <c r="G1" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1" s="1"/>
       <c r="J1" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="19"/>
       <c r="M1" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>477</v>
-      </c>
-      <c r="D2" s="5" t="s">
         <v>478</v>
       </c>
+      <c r="D2" s="0" t="s">
+        <v>479</v>
+      </c>
       <c r="E2" s="5" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="BG2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="BG3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>507</v>
-      </c>
-      <c r="P4" s="0" t="s">
         <v>508</v>
       </c>
+      <c r="P4" s="5" t="s">
+        <v>509</v>
+      </c>
       <c r="Q4" s="0" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="BG4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="BG5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>522</v>
+        <v>483</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>523</v>
@@ -5038,30 +4950,27 @@
         <v>528</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="BG6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>482</v>
+        <v>532</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="BG7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>532</v>
-      </c>
-      <c r="D8" s="0" t="s">
         <v>533</v>
       </c>
       <c r="P8" s="0" t="s">
@@ -5076,6 +4985,9 @@
       <c r="BG9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P10" s="0" t="s">
+        <v>536</v>
+      </c>
       <c r="BG10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5110,216 +5022,216 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="19"/>
       <c r="G21" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="19"/>
       <c r="M21" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N21" s="1"/>
       <c r="P21" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="BG21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="BG22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N23" s="0" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="Q23" s="0" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="BG23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N24" s="0" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Q24" s="0" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="BG24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N25" s="0" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q25" s="0" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="BG25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N26" s="0" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="Q26" s="0" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="BG26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D27" s="5"/>
       <c r="G27" s="5"/>
@@ -5330,7 +5242,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="G28" s="5"/>
       <c r="M28" s="5"/>
@@ -5338,7 +5250,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G29" s="20"/>
       <c r="M29" s="5"/>
@@ -5372,7 +5284,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="BG35" s="0"/>
       <c r="BH35" s="0"/>
@@ -5384,7 +5296,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="BG36" s="0"/>
       <c r="BH36" s="0"/>
@@ -5396,13 +5308,13 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E37" s="0" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F37" s="0" t="n">
         <v>1.01</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="BG37" s="0"/>
       <c r="BH37" s="0"/>
@@ -5417,7 +5329,7 @@
         <v>1.02</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="BG38" s="0"/>
       <c r="BH38" s="0"/>
@@ -5432,7 +5344,7 @@
         <v>1.03</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="BG39" s="0"/>
       <c r="BH39" s="0"/>
@@ -5447,7 +5359,7 @@
         <v>1.04</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="BG40" s="0"/>
       <c r="BH40" s="0"/>
@@ -5477,7 +5389,7 @@
         <v>1.06</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="BG42" s="0"/>
       <c r="BH42" s="0"/>
@@ -5492,7 +5404,7 @@
         <v>1.07</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="BG43" s="0"/>
       <c r="BH43" s="0"/>
@@ -5507,7 +5419,7 @@
         <v>1.08</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="BG44" s="0"/>
       <c r="BH44" s="0"/>
@@ -5522,7 +5434,7 @@
         <v>1.09</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="BG45" s="0"/>
       <c r="BH45" s="0"/>
@@ -5537,7 +5449,7 @@
         <v>1.1</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="BG46" s="0"/>
       <c r="BH46" s="0"/>
@@ -5552,7 +5464,7 @@
         <v>1.11</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="BG47" s="0"/>
       <c r="BH47" s="0"/>
@@ -5567,7 +5479,7 @@
         <v>1.12</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="BG48" s="0"/>
       <c r="BH48" s="0"/>
@@ -7236,7 +7148,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E231"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="22" width="8.54"/>
@@ -7247,16 +7159,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25"/>
       <c r="B2" s="26" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7267,7 +7179,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>324</v>
@@ -7282,7 +7194,7 @@
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7293,22 +7205,22 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25"/>
       <c r="B10" s="26" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27"/>
       <c r="B11" s="28" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7317,7 +7229,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>293</v>
@@ -7338,12 +7250,12 @@
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27"/>
       <c r="B16" s="28" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>180</v>
@@ -7352,7 +7264,7 @@
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27"/>
       <c r="B19" s="28" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7361,22 +7273,22 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25"/>
       <c r="B22" s="26" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25"/>
       <c r="B23" s="26" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7385,22 +7297,23 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25"/>
       <c r="B26" s="26" t="s">
-        <v>128</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="G26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="27"/>
       <c r="B27" s="28" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7409,10 +7322,36 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B29" s="28" t="s">
         <v>294</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="B31" s="29" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25"/>
+      <c r="B32" s="30"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
+        <v>476</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="27"/>
+      <c r="B34" s="28" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7494,23 +7433,23 @@
       <c r="D190" s="15"/>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D216" s="29"/>
+      <c r="D216" s="31"/>
       <c r="E216" s="0"/>
     </row>
     <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D217" s="29"/>
+      <c r="D217" s="31"/>
       <c r="E217" s="0"/>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D218" s="29"/>
+      <c r="D218" s="31"/>
       <c r="E218" s="0"/>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D219" s="29"/>
+      <c r="D219" s="31"/>
       <c r="E219" s="0"/>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D220" s="29"/>
+      <c r="D220" s="31"/>
       <c r="E220" s="0"/>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7550,11 +7489,11 @@
       <c r="E229" s="0"/>
     </row>
     <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D230" s="29"/>
+      <c r="D230" s="31"/>
       <c r="E230" s="0"/>
     </row>
     <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D231" s="29"/>
+      <c r="D231" s="31"/>
       <c r="E231" s="0"/>
     </row>
   </sheetData>
@@ -7581,54 +7520,54 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="30" t="s">
-        <v>618</v>
-      </c>
-      <c r="B1" s="30"/>
+      <c r="A1" s="32" t="s">
+        <v>620</v>
+      </c>
+      <c r="B1" s="32"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="30"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="30"/>
-      <c r="B4" s="30"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="32"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="32"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="32"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="32"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5"/>

--- a/OffSeason.xlsx
+++ b/OffSeason.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="624">
   <si>
     <t xml:space="preserve">No Chubb – John Olson</t>
   </si>
@@ -464,6 +464,9 @@
     <t xml:space="preserve">Isaiah Likely</t>
   </si>
   <si>
+    <t xml:space="preserve">Pat Freiermuth</t>
+  </si>
+  <si>
     <t xml:space="preserve">Myles Garrett</t>
   </si>
   <si>
@@ -479,7 +482,7 @@
     <t xml:space="preserve">Tucker Kraft</t>
   </si>
   <si>
-    <t xml:space="preserve">Pat Freiermuth</t>
+    <t xml:space="preserve">Cade Otten</t>
   </si>
   <si>
     <t xml:space="preserve">Nick bosa</t>
@@ -497,7 +500,7 @@
     <t xml:space="preserve">Erick all Jr</t>
   </si>
   <si>
-    <t xml:space="preserve">Cade Otten</t>
+    <t xml:space="preserve">Michael Mayer</t>
   </si>
   <si>
     <t xml:space="preserve">Maxxx Crosby</t>
@@ -515,7 +518,7 @@
     <t xml:space="preserve">Jessie Bates III</t>
   </si>
   <si>
-    <t xml:space="preserve">Michael Mayer</t>
+    <t xml:space="preserve">Brian Branch</t>
   </si>
   <si>
     <t xml:space="preserve">Will Anderson</t>
@@ -533,7 +536,7 @@
     <t xml:space="preserve">Xavier Woods</t>
   </si>
   <si>
-    <t xml:space="preserve">Brian Branch</t>
+    <t xml:space="preserve">Tre’von Moehrig</t>
   </si>
   <si>
     <t xml:space="preserve">LB</t>
@@ -554,7 +557,7 @@
     <t xml:space="preserve">Alontea Taylor</t>
   </si>
   <si>
-    <t xml:space="preserve">Tre’von Moehrig</t>
+    <t xml:space="preserve">Damar Hamlin</t>
   </si>
   <si>
     <t xml:space="preserve">Roquan Smith</t>
@@ -572,7 +575,7 @@
     <t xml:space="preserve">Devon Witherspoon</t>
   </si>
   <si>
-    <t xml:space="preserve">Damar Hamlin</t>
+    <t xml:space="preserve">DeShon Elliott</t>
   </si>
   <si>
     <t xml:space="preserve">Ernest Jones</t>
@@ -590,7 +593,7 @@
     <t xml:space="preserve">Micah Parsons</t>
   </si>
   <si>
-    <t xml:space="preserve">DeShon Elliott</t>
+    <t xml:space="preserve">Byron Murphy II</t>
   </si>
   <si>
     <t xml:space="preserve">Azeez Al-Shaair</t>
@@ -608,7 +611,7 @@
     <t xml:space="preserve">Dante Fowler Jr.</t>
   </si>
   <si>
-    <t xml:space="preserve">Byron Murphy II</t>
+    <t xml:space="preserve">Jalen Carter</t>
   </si>
   <si>
     <t xml:space="preserve">Ivan Pace Jr.</t>
@@ -626,7 +629,7 @@
     <t xml:space="preserve">B.J. Hill</t>
   </si>
   <si>
-    <t xml:space="preserve">Jalen Carter</t>
+    <t xml:space="preserve">Za’Darius Smith</t>
   </si>
   <si>
     <t xml:space="preserve">Cody Barton</t>
@@ -644,7 +647,7 @@
     <t xml:space="preserve">Nik Bonitto</t>
   </si>
   <si>
-    <t xml:space="preserve">Za’Darius Smith</t>
+    <t xml:space="preserve">Jamien Sherwood</t>
   </si>
   <si>
     <t xml:space="preserve">Alim McNeil</t>
@@ -659,7 +662,7 @@
     <t xml:space="preserve">Micah McFadden</t>
   </si>
   <si>
-    <t xml:space="preserve">Jamien Sherwood</t>
+    <t xml:space="preserve">Daiyan Henley</t>
   </si>
   <si>
     <t xml:space="preserve">Akeem Davis-Gaither</t>
@@ -671,7 +674,7 @@
     <t xml:space="preserve">Dorian Williams</t>
   </si>
   <si>
-    <t xml:space="preserve">Daiyan Henley</t>
+    <t xml:space="preserve">Patrick Queen</t>
   </si>
   <si>
     <t xml:space="preserve">Drue Tranquill</t>
@@ -683,7 +686,7 @@
     <t xml:space="preserve">Lavonte David</t>
   </si>
   <si>
-    <t xml:space="preserve">Patrick Queen</t>
+    <t xml:space="preserve">Dallas Turner</t>
   </si>
   <si>
     <t xml:space="preserve">Tryrice Knight</t>
@@ -695,15 +698,12 @@
     <t xml:space="preserve">Alex Anzalone</t>
   </si>
   <si>
-    <t xml:space="preserve">Dallas Turner</t>
+    <t xml:space="preserve">DeMavion Overshown</t>
   </si>
   <si>
     <t xml:space="preserve">Bobby Okereke</t>
   </si>
   <si>
-    <t xml:space="preserve">DeMavion Overshown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jonathoan Greenard</t>
   </si>
   <si>
@@ -1463,369 +1463,369 @@
     <t xml:space="preserve">2026 1 John O</t>
   </si>
   <si>
+    <t xml:space="preserve">2025 3 3.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Josh</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 3 3.12</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 1 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Josh</t>
+    <t xml:space="preserve">2026 2 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 John O</t>
   </si>
   <si>
     <t xml:space="preserve">2025 4 4.12</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 2 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Alan</t>
+    <t xml:space="preserve">2026 3 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 John O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 John O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 John O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Brandon</t>
   </si>
   <si>
     <t xml:space="preserve">2025 2 2.07</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 2 John O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Alan</t>
+    <t xml:space="preserve">2026 3 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Brandon</t>
   </si>
   <si>
     <t xml:space="preserve">2025 3 3.05</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 2 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 John O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 John O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 John O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Brandon</t>
+    <t xml:space="preserve">2026 5 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.11</t>
   </si>
   <si>
     <t xml:space="preserve">2025 4.1</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 4 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Brandon</t>
+    <t xml:space="preserve">2025 5 5.06</t>
   </si>
   <si>
     <t xml:space="preserve">2025 5.1</t>
   </si>
   <si>
-    <t xml:space="preserve">2026 5 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.06</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025 5 5.05</t>
   </si>
   <si>
@@ -1884,6 +1884,15 @@
   </si>
   <si>
     <t xml:space="preserve">2025 3.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 JohnO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 CJ</t>
   </si>
   <si>
     <t xml:space="preserve">2026 pick trades</t>
@@ -3012,387 +3021,386 @@
       <c r="V22" s="8" t="s">
         <v>102</v>
       </c>
+      <c r="W22" s="5" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="10"/>
       <c r="C23" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>102</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J23" s="7"/>
       <c r="K23" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N23" s="10" t="s">
         <v>140</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R23" s="8"/>
       <c r="S23" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="V23" s="8"/>
       <c r="W23" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="10"/>
       <c r="C24" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F24" s="8"/>
       <c r="G24" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>102</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N24" s="10"/>
       <c r="O24" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R24" s="8"/>
       <c r="S24" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V24" s="8"/>
-      <c r="W24" s="5" t="s">
-        <v>157</v>
+      <c r="W24" s="0" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="10"/>
       <c r="C25" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F25" s="8"/>
       <c r="G25" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N25" s="10"/>
       <c r="O25" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R25" s="9" t="s">
         <v>121</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="V25" s="8"/>
-      <c r="W25" s="0" t="s">
         <v>163</v>
+      </c>
+      <c r="V25" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="W25" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="10"/>
       <c r="C26" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F26" s="8"/>
       <c r="G26" s="0" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J26" s="8"/>
       <c r="K26" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R26" s="9"/>
       <c r="S26" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>121</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="V26" s="9"/>
       <c r="W26" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>121</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>121</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N27" s="10"/>
       <c r="O27" s="0" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="R27" s="9"/>
       <c r="S27" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="V27" s="9"/>
       <c r="W27" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="11"/>
       <c r="C28" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F28" s="9"/>
       <c r="G28" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J28" s="9"/>
       <c r="K28" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R28" s="9"/>
       <c r="S28" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="V28" s="9"/>
-      <c r="W28" s="5" t="s">
-        <v>182</v>
+      <c r="W28" s="0" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="11"/>
       <c r="C29" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F29" s="9"/>
       <c r="G29" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J29" s="10" t="s">
         <v>140</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N29" s="11"/>
       <c r="O29" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="R29" s="10" t="s">
         <v>140</v>
       </c>
       <c r="S29" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="V29" s="9"/>
-      <c r="W29" s="0" t="s">
         <v>188</v>
+      </c>
+      <c r="V29" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="W29" s="5" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="11"/>
       <c r="C30" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>140</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J30" s="10"/>
       <c r="K30" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N30" s="11"/>
       <c r="O30" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R30" s="10"/>
       <c r="S30" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="V30" s="10" t="s">
-        <v>140</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="V30" s="10"/>
       <c r="W30" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AB30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="11"/>
       <c r="C31" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J31" s="10"/>
       <c r="K31" s="0" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N31" s="11"/>
       <c r="O31" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R31" s="10"/>
       <c r="S31" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="V31" s="10"/>
-      <c r="W31" s="5" t="s">
-        <v>200</v>
+      <c r="W31" s="0" t="s">
+        <v>201</v>
       </c>
       <c r="AB31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="11"/>
       <c r="C32" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J32" s="10"/>
       <c r="K32" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N32" s="11"/>
       <c r="O32" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S32" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="V32" s="10"/>
-      <c r="W32" s="0" t="s">
         <v>206</v>
+      </c>
+      <c r="V32" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="W32" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="AB32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F33" s="10"/>
       <c r="G33" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K33" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N33" s="11"/>
       <c r="O33" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R33" s="11"/>
       <c r="S33" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="V33" s="11" t="s">
-        <v>170</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="V33" s="11"/>
       <c r="W33" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F34" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R34" s="11"/>
       <c r="S34" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="V34" s="11"/>
       <c r="W34" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F35" s="11"/>
       <c r="G35" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J35" s="11"/>
       <c r="K35" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="R35" s="11"/>
       <c r="S35" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="V35" s="11"/>
-      <c r="W35" s="5" t="s">
-        <v>219</v>
+      <c r="W35" s="0" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F36" s="11"/>
       <c r="G36" s="0" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J36" s="11"/>
       <c r="K36" s="0" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R36" s="11"/>
       <c r="S36" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="V36" s="11"/>
       <c r="W36" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F37" s="11"/>
       <c r="G37" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="V37" s="11"/>
-      <c r="W37" s="0" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4250,7 +4258,7 @@
         <v>403</v>
       </c>
       <c r="N74" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O74" s="0" t="s">
         <v>404</v>
@@ -4304,7 +4312,7 @@
         <v>414</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K76" s="5" t="s">
         <v>415</v>
@@ -4325,13 +4333,13 @@
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C77" s="0" t="s">
         <v>419</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>420</v>
@@ -4371,13 +4379,13 @@
         <v>428</v>
       </c>
       <c r="R78" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S78" s="0" t="s">
         <v>429</v>
       </c>
       <c r="V78" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="W78" s="0" t="s">
         <v>430</v>
@@ -4492,22 +4500,22 @@
     <mergeCell ref="N20:N22"/>
     <mergeCell ref="R21:R24"/>
     <mergeCell ref="B22:B26"/>
-    <mergeCell ref="V22:V25"/>
+    <mergeCell ref="V22:V24"/>
     <mergeCell ref="F23:F26"/>
     <mergeCell ref="N23:N27"/>
     <mergeCell ref="J24:J26"/>
     <mergeCell ref="R25:R28"/>
-    <mergeCell ref="V26:V29"/>
+    <mergeCell ref="V25:V28"/>
     <mergeCell ref="F27:F29"/>
     <mergeCell ref="J27:J28"/>
     <mergeCell ref="N28:N33"/>
     <mergeCell ref="J29:J32"/>
     <mergeCell ref="R29:R31"/>
+    <mergeCell ref="V29:V31"/>
     <mergeCell ref="F30:F33"/>
-    <mergeCell ref="V30:V32"/>
     <mergeCell ref="R32:R36"/>
+    <mergeCell ref="V32:V36"/>
     <mergeCell ref="J33:J36"/>
-    <mergeCell ref="V33:V37"/>
     <mergeCell ref="F34:F38"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="F45:G45"/>
@@ -4853,140 +4861,134 @@
       <c r="BG3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B4" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="D4" s="0" t="s">
         <v>501</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="E4" s="0" t="s">
         <v>502</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="G4" s="0" t="s">
         <v>503</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="H4" s="0" t="s">
         <v>504</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="K4" s="0" t="s">
         <v>505</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="M4" s="0" t="s">
         <v>506</v>
       </c>
-      <c r="M4" s="0" t="s">
+      <c r="N4" s="0" t="s">
         <v>507</v>
       </c>
-      <c r="N4" s="0" t="s">
+      <c r="P4" s="5" t="s">
         <v>508</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="Q4" s="0" t="s">
         <v>509</v>
       </c>
-      <c r="Q4" s="0" t="s">
+      <c r="BG4" s="0"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
         <v>510</v>
       </c>
-      <c r="BG4" s="0"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="D5" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="E5" s="0" t="s">
         <v>512</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="G5" s="0" t="s">
         <v>513</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="H5" s="0" t="s">
         <v>514</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="K5" s="0" t="s">
         <v>515</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="M5" s="0" t="s">
         <v>516</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="N5" s="0" t="s">
         <v>517</v>
       </c>
-      <c r="M5" s="0" t="s">
+      <c r="Q5" s="0" t="s">
         <v>518</v>
-      </c>
-      <c r="N5" s="0" t="s">
-        <v>519</v>
-      </c>
-      <c r="P5" s="0" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q5" s="0" t="s">
-        <v>521</v>
       </c>
       <c r="BG5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
+        <v>519</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>521</v>
+      </c>
+      <c r="G6" s="0" t="s">
         <v>522</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>483</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="H6" s="0" t="s">
         <v>523</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="K6" s="0" t="s">
         <v>524</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="M6" s="0" t="s">
         <v>525</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="N6" s="0" t="s">
         <v>526</v>
       </c>
-      <c r="M6" s="0" t="s">
+      <c r="P6" s="0" t="s">
         <v>527</v>
       </c>
-      <c r="N6" s="0" t="s">
+      <c r="Q6" s="0" t="s">
         <v>528</v>
-      </c>
-      <c r="P6" s="0" t="s">
-        <v>529</v>
-      </c>
-      <c r="Q6" s="0" t="s">
-        <v>530</v>
       </c>
       <c r="BG6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>532</v>
+        <v>483</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="BG7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>533</v>
+        <v>530</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>531</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="BG8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P9" s="0" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="BG9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="P10" s="0" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="BG10" s="0"/>
     </row>
@@ -5022,230 +5024,235 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="19"/>
       <c r="G21" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="19"/>
       <c r="M21" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="N21" s="1"/>
       <c r="P21" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="BG21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>542</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="G22" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="H22" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="J22" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="K22" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="M22" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="N22" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="M22" s="5" t="s">
+      <c r="P22" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="N22" s="5" t="s">
+      <c r="Q22" s="5" t="s">
         <v>551</v>
-      </c>
-      <c r="P22" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>553</v>
       </c>
       <c r="BG22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
+        <v>552</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>553</v>
+      </c>
+      <c r="E23" s="0" t="s">
         <v>554</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="G23" s="0" t="s">
         <v>555</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="H23" s="0" t="s">
         <v>556</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="J23" s="0" t="s">
         <v>557</v>
       </c>
-      <c r="H23" s="0" t="s">
+      <c r="K23" s="0" t="s">
         <v>558</v>
       </c>
-      <c r="J23" s="0" t="s">
+      <c r="M23" s="0" t="s">
         <v>559</v>
       </c>
-      <c r="K23" s="0" t="s">
+      <c r="N23" s="0" t="s">
         <v>560</v>
       </c>
-      <c r="M23" s="0" t="s">
+      <c r="P23" s="0" t="s">
         <v>561</v>
       </c>
-      <c r="N23" s="0" t="s">
+      <c r="Q23" s="0" t="s">
         <v>562</v>
-      </c>
-      <c r="P23" s="0" t="s">
-        <v>563</v>
-      </c>
-      <c r="Q23" s="0" t="s">
-        <v>564</v>
       </c>
       <c r="BG23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
+        <v>563</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>564</v>
+      </c>
+      <c r="E24" s="0" t="s">
         <v>565</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="G24" s="0" t="s">
         <v>566</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="H24" s="0" t="s">
         <v>567</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="J24" s="0" t="s">
         <v>568</v>
       </c>
-      <c r="H24" s="0" t="s">
+      <c r="K24" s="0" t="s">
         <v>569</v>
       </c>
-      <c r="J24" s="0" t="s">
+      <c r="M24" s="0" t="s">
         <v>570</v>
       </c>
-      <c r="K24" s="0" t="s">
+      <c r="N24" s="0" t="s">
         <v>571</v>
       </c>
-      <c r="M24" s="0" t="s">
+      <c r="P24" s="0" t="s">
         <v>572</v>
       </c>
-      <c r="N24" s="0" t="s">
+      <c r="Q24" s="0" t="s">
         <v>573</v>
-      </c>
-      <c r="P24" s="0" t="s">
-        <v>574</v>
-      </c>
-      <c r="Q24" s="0" t="s">
-        <v>575</v>
       </c>
       <c r="BG24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>575</v>
+      </c>
+      <c r="E25" s="0" t="s">
         <v>576</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="G25" s="0" t="s">
         <v>577</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="H25" s="0" t="s">
         <v>578</v>
       </c>
-      <c r="G25" s="0" t="s">
+      <c r="J25" s="0" t="s">
         <v>579</v>
       </c>
-      <c r="H25" s="0" t="s">
+      <c r="K25" s="0" t="s">
         <v>580</v>
       </c>
-      <c r="J25" s="0" t="s">
+      <c r="M25" s="0" t="s">
         <v>581</v>
       </c>
-      <c r="K25" s="0" t="s">
+      <c r="N25" s="0" t="s">
         <v>582</v>
       </c>
-      <c r="M25" s="0" t="s">
+      <c r="P25" s="0" t="s">
         <v>583</v>
       </c>
-      <c r="N25" s="0" t="s">
+      <c r="Q25" s="0" t="s">
         <v>584</v>
-      </c>
-      <c r="P25" s="0" t="s">
-        <v>585</v>
-      </c>
-      <c r="Q25" s="0" t="s">
-        <v>586</v>
       </c>
       <c r="BG25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="E26" s="0" t="s">
         <v>587</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="G26" s="0" t="s">
         <v>588</v>
       </c>
-      <c r="E26" s="0" t="s">
+      <c r="H26" s="0" t="s">
         <v>589</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="J26" s="0" t="s">
         <v>590</v>
       </c>
-      <c r="H26" s="0" t="s">
+      <c r="K26" s="0" t="s">
         <v>591</v>
       </c>
-      <c r="J26" s="0" t="s">
+      <c r="M26" s="0" t="s">
         <v>592</v>
       </c>
-      <c r="K26" s="0" t="s">
+      <c r="N26" s="0" t="s">
         <v>593</v>
       </c>
-      <c r="M26" s="0" t="s">
+      <c r="P26" s="0" t="s">
         <v>594</v>
       </c>
-      <c r="N26" s="0" t="s">
+      <c r="Q26" s="0" t="s">
         <v>595</v>
-      </c>
-      <c r="P26" s="0" t="s">
-        <v>596</v>
-      </c>
-      <c r="Q26" s="0" t="s">
-        <v>597</v>
       </c>
       <c r="BG26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D27" s="5"/>
       <c r="G27" s="5"/>
       <c r="J27" s="5"/>
       <c r="M27" s="5"/>
-      <c r="P27" s="5"/>
+      <c r="P27" s="0" t="s">
+        <v>597</v>
+      </c>
       <c r="BG27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="G28" s="5"/>
       <c r="M28" s="5"/>
+      <c r="P28" s="0" t="s">
+        <v>599</v>
+      </c>
       <c r="BG28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7159,7 +7166,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B1" s="24" t="s">
         <v>609</v>
@@ -7179,7 +7186,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>324</v>
@@ -7205,7 +7212,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>612</v>
@@ -7220,7 +7227,7 @@
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27"/>
       <c r="B11" s="28" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7255,10 +7262,10 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7297,7 +7304,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B25" s="24" t="s">
         <v>618</v>
@@ -7345,13 +7352,45 @@
         <v>476</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="27"/>
       <c r="B34" s="28" t="s">
         <v>619</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="B36" s="29" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25"/>
+      <c r="B37" s="30" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="25"/>
+      <c r="B38" s="30" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25"/>
+      <c r="B39" s="30"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7521,7 +7560,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="32" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B1" s="32"/>
     </row>

--- a/OffSeason.xlsx
+++ b/OffSeason.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="624">
   <si>
     <t xml:space="preserve">No Chubb – John Olson</t>
   </si>
@@ -86,1281 +86,1434 @@
     <t xml:space="preserve">Drake Maye</t>
   </si>
   <si>
+    <t xml:space="preserve">Michael Penix Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calvin Austin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Chubb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chubba Hubbard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russell Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian McCaffrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devon Achane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derrek Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Conner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travis Etienne Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Mixon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derrick Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roschon Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Owens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bijan Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rico Dowdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahmyr Gibbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tony Pollard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylen Warren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kris Jenkins Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breece Hall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puka Nacua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D’Andre Swift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhamondre Stevenson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alvin Kamara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Benson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevin Wallace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saquon Barkley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenneth Walker III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isiah Pacheco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrone Tracy Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Godwin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payton Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Jefferson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Thielen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amon-Ra St. Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J.K. Dobbins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kareem Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DJ Moore</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kirk Cousins</t>
   </si>
   <si>
-    <t xml:space="preserve">Calvin Austin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Chubb</t>
+    <t xml:space="preserve">Ja’Marr Chase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adonai Mitchell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaxon Smith-Njigba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stefon Diggs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Mason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rashod Bateman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mac Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CeeDee Lamb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Tolbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nico Collins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drake London</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deebo Samel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darnell Mooney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Allgeier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Thomas Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Lockett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calvin Ridley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davonte Adams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tee Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kayshon Boutte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladd McConkey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Kittle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Legette</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DK Metcalf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Pickens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrei Iosivias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isreal Abanikanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Worthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juwan Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rome Odunze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylen Waddle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakobi Meyers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pat Freiermuth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khalil Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.J. Hockenson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Gray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malik Washington</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cooper Kupp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wan’Dale Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cade Otten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandin Cooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey McBride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kerby Jospeh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rashee Rice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zay Flowers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troy Franklin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Mayer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja’Lynn Polk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalton Kincaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison ‘Hitman’ Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Downs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine Burton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Likely</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damar Hamlin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antoine Winfield Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adam Butler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark Andrews</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam LaPorta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tucker Kraft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tre’von Moehrig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Za’Darius Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budda Baker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daron Payne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Furgeson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jessie Bates III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeShon Elliott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeMavion Overshown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyler Nubin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alim McNeil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brenton Strange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chigoziem Okonkwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Woods</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byron Murphy II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emmanuel Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwity Paye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeem Davis-Gaither</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julian Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derwin James Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devon Witherspoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Carter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myles Garrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tryrice Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jared Verse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kevin Byard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micah Parsons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamien Sherwood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexander Mattison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick bosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobby Okereke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Rousseau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Dugger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dante Fowler Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daiyan Henley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Craig Reynolds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maxxx Crosby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathoan Greenard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Hendrickson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montez Sweat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nik Bonitto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrick Queen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dyami Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fred Warner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carl Granderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micah McFadden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas Turner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zack Baun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaden Ellis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lavonte David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A’Shawn Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roquan Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calijah Kancey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Anzalone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henry To’oTo’o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ernest Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quay Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintin Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Pace Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foyesade Oluokun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Colson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.08</t>
   </si>
   <si>
     <t xml:space="preserve">Taysom Hill (QB/TE</t>
   </si>
   <si>
-    <t xml:space="preserve">Jordan Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Russell Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian McCaffrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Penix Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derrek Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chubba Hubbard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travis Etienne Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Mixon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derrick Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mac Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Owens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bijan Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Conner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahmyr Gibbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tony Pollard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylen Warren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devon Achane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kris Jenkins Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breece Hall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rico Dowdle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D’Andre Swift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhamondre Stevenson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alvin Kamara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roschon Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevin Wallace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saquon Barkley</t>
+    <t xml:space="preserve">2025 1 1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joryn Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.07</t>
   </si>
   <si>
     <t xml:space="preserve">Raheem Blackshear</t>
   </si>
   <si>
-    <t xml:space="preserve">Kenneth Walker III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isiah Pacheco</t>
+    <t xml:space="preserve">Ameer Abdullah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raheem Mostert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trey Sermon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sterling Shepard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marquez Valdes-Scantling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Ray McCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lil’Joran Humphrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Javon Baker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Fant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ar’Darius Washington</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rashan Gary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drue Tranquill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Pack Go – Josh L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Massage Envy – Vanja Dolas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young Guns – Rhode and co.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pringle Can Joe burres and Luke longly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magik Skol Bus – Brandon Hurd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Folding Table Repair Man -  CJ perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devin Singletary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bryce Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyler Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brock Purdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jared Goff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Rodgers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dak Prescott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samaje Perine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevor Lawrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Herbert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.J. Stroud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bo Nix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Levis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Darnold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Dillon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthony Richardson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deshaun Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geno Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tank “2 beers” Bigsby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J.J. McCarthy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Robinson Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demarcus Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Cook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aaron Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Najee Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chase Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caleb Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antonio Gibson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kendrick bourne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyjae Spears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austin Ekeler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachaad White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaac Guerrendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zach Charbonnet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kendre Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gave Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathon Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Jacobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerome Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucky Irving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Shipley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julian Blackmon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Javonte Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyren Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keaton Mitchell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justice Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Montgomery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keenan Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Phillips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylen Wright</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Corum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jameson Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malik Nabers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marshawn Lloyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keon Coleman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Wilkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.J. Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braelon Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garrett Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quentin Johnston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jordan Addison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry McLaurin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Rozeboom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeVonta Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeAndre Hopkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen McMillan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devaughn Vele</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerry Jeudy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Courtland Sutton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gus Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marvin Harrison Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amari Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demario Douglas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Kirk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Pittman Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hollywood Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cam Akers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Reed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyreek Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Pitts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zach Ertz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jauan Jennings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alec Pierce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zamir White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Olave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Aiyuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Hamilton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Sinnott</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romeo Doubs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joshua Palmer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tre Tucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christian Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khalil Shakir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talanoa Hufanga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camryn Bynum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dontayvion Wicks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evan Engram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brenden Rice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ricky Pearsall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dionte Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Thompson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Pitre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonnu Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike Gesicki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treylon burks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brock Bowers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marvin Mims Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Karlaftis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeffery Simmons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Dissly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Barner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja’Tavion Sanders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen Coker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travon Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Heyward</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Musgrave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brandon Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cole Kmet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Chinn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedric Tillman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Branden Fiske</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joshua Metellus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jer’Zhan Newton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cody Barton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier McKinney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rashid Shaheed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will McDonald IV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dexter Lawrence II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taylor Rapp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.J.Watt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azeez Al-Shaair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Cross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travis Kelce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chop Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zaire Franklin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kobie Turner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quincy Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Hubbard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lukas Van Ness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas Goedert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nnamdi Madubuike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frankie Luvu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zach Sieler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyzir White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Hines-Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Njoku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demario Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeForest Buckner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nolan Smith Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laiatu Latu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaquan Brisker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Van Ginkel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Robert Spillane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blake Cashman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B.J. Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edgerrin Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minkah Fitzpatrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrel Bernard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T.J. Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alontea Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devin Lloyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grant Delpit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Bolton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Burns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.11</t>
   </si>
   <si>
     <t xml:space="preserve">Jaleel Mclaughlin</t>
   </si>
   <si>
-    <t xml:space="preserve">Tyler Allgeier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payton Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Jefferson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ameer Abdullah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emmanuel Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J.K. Dobbins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrone Tracy Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja’Marr Chase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raheem Mostert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Brooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stefon Diggs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kareem Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CeeDee Lamb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Sermon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alexander Mattison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drake London</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Mason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isreal Abanikanda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Thomas Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puka Nacua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Craig Reynolds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davonte Adams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deebo Samel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Benson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ladd McConkey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mike Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amon-Ra St. Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DK Metcalf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tee Higgins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khalil Herbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Worthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Thielen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaxon Smith-Njigba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylen Waddle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">George Pickens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Godwin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine Burton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sterling Shepard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nico Collins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cooper Kupp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jakobi Meyers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DJ Moore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T.J. Hockenson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Tolbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calvin Ridley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zay Flowers</t>
+    <t xml:space="preserve">Jack Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zach Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tim Patrick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremiah Owusu-Koramoah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonard Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.05</t>
   </si>
   <si>
     <t xml:space="preserve">Rondale Moore</t>
   </si>
   <si>
-    <t xml:space="preserve">Rashod Bateman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey McBride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marquez Valdes-Scantling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Legette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam LaPorta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wan’Dale Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darnell Mooney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalton Kincaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Ray McCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rome Odunze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Furgeson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troy Franklin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayshon Boutte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antoine Winfield Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyler Lockett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malik Washington</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chigoziem Okonkwo</t>
+    <t xml:space="preserve">2025 1 1.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Sweat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.11</t>
   </si>
   <si>
     <t xml:space="preserve">Jordan Whittington</t>
   </si>
   <si>
-    <t xml:space="preserve">Brandin Cooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budda Baker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lil’Joran Humphrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dyami Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derwin James Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tim Patrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrei Iosivias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyler Nubin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adonai Mitchell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kevin Byard</t>
+    <t xml:space="preserve">2025 2 2.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omar Speights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erick all Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dre Greenlaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5.1</t>
   </si>
   <si>
     <t xml:space="preserve">Dalton Shultz</t>
   </si>
   <si>
-    <t xml:space="preserve">Ja’Lynn Polk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwity Paye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Javon Baker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rashee Rice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Dugger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Likely</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pat Freiermuth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myles Garrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">George Kittle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Downs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Hubbard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tucker Kraft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cade Otten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick bosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juwan Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mark Andrews</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montez Sweat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erick all Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Mayer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maxxx Crosby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Gray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carl Granderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jessie Bates III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Fant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brenton Strange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danielle Hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Woods</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tre’von Moehrig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zack Baun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kerby Jospeh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julian Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calijah Kancey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alontea Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damar Hamlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roquan Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ar’Darius Washington</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintin Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quay Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devon Witherspoon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeShon Elliott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ernest Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison ‘Hitman’ Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jared Verse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foyesade Oluokun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micah Parsons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Byron Murphy II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azeez Al-Shaair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rashan Gary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Rousseau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dante Fowler Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Carter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivan Pace Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Butler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A’Shawn Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joryn Brooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B.J. Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Za’Darius Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cody Barton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daron Payne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trey Hendrickson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyzir White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nik Bonitto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamien Sherwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alim McNeil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fred Warner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nolan Smith Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micah McFadden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daiyan Henley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeem Davis-Gaither</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henry To’oTo’o</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dorian Williams</t>
   </si>
   <si>
-    <t xml:space="preserve">Patrick Queen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drue Tranquill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaden Ellis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lavonte David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas Turner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tryrice Knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Colson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Anzalone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeMavion Overshown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bobby Okereke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathoan Greenard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Pack Go – Josh L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Massage Envy – Vanja Dolas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Young Guns – Rhode and co.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pringle Can Joe burres and Luke longly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magik Skol Bus – Brandon Hurd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Folding Table Repair Man -  CJ perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bryce Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyler Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brock Purdy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jared Goff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Rodgers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dak Prescott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor Lawrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justin Herbert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.J. Stroud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bo Nix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Levis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Darnold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anthony Richardson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deshaun Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geno Smith</t>
+    <t xml:space="preserve">Dylan Laube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ugo Amadi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylon Carlies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyree Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakobe Dean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jameis Winston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Audric Estime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erik Kendricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E.J. Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.J. Mosley</t>
   </si>
   <si>
     <t xml:space="preserve">Jordan Travis</t>
   </si>
   <si>
-    <t xml:space="preserve">J.J. McCarthy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Robinson Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Cook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jameis Winston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Najee Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tank “2 beers” Bigsby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daniel Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antonio Gibson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyjae Spears</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aaron Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachaad White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chase Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caleb Williams</t>
+    <t xml:space="preserve">Sean Tucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zack Moss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elijah Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Metchie III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke McCaffrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.J. Locke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cameron Jordan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Singleton</t>
   </si>
   <si>
     <t xml:space="preserve">Elijah Mitchell</t>
   </si>
   <si>
-    <t xml:space="preserve">Jonathon Brooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austin Ekeler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerome Ford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaac Guerrendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zach Charbonnet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kendre Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Javonte Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Jacobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gus Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucky Irving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devin Singletary</t>
-  </si>
-  <si>
     <t xml:space="preserve">Miles Sanders</t>
   </si>
   <si>
-    <t xml:space="preserve">Jaylen Wright</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyren Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cam Akers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sean Tucker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Montgomery</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ty Johnson</t>
   </si>
   <si>
-    <t xml:space="preserve">Dylan Laube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Corum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keaton Mitchell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Justice Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samaje Perine</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sincere McCormick</t>
   </si>
   <si>
     <t xml:space="preserve">Kimani Vidal</t>
   </si>
   <si>
-    <t xml:space="preserve">Braelon Allen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zamir White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zack Moss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Shipley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keenan Allen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A.J. Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Audric Estime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jameson Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malik Nabers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marshawn Lloyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keon Coleman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeVonta Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeAndre Hopkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garrett Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quentin Johnston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Dillon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry McLaurin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marvin Harrison Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amari Cooper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen McMillan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devaughn Vele</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jordan Addison</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Courtland Sutton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Reed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyreek Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demario Douglas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elijah Moore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerry Jeudy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hollywood Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Olave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Aiyuk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tre Tucker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Metchie III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Pittman Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alec Pierce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khalil Shakir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brenden Rice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jauan Jennings</t>
+    <t xml:space="preserve">Tutu Atwell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ainias Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tyler Boyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalin Hyatt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Hutchinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrique Stevenson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rayshawn Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrann Mathieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T’Vondre Sweat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leonard Floyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calais Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinnen Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matt Milano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobby Wagner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahlani Tavai</t>
   </si>
   <si>
     <t xml:space="preserve">Jacob Cowing</t>
   </si>
   <si>
-    <t xml:space="preserve">Ricky Pearsall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dionte Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treylon burks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke McCaffrey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romeo Doubs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joshua Palmer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rashid Shaheed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marvin Mims Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Pitts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Kirk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demarcus Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tutu Atwell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roman Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Coker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Barner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zach Ertz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dontayvion Wicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ainias Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brock Bowers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cedric Tillman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cole Kmet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Sinnott</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kendrick bourne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tyler Boyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ja’Tavion Sanders</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travis Kelce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Hamilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camryn Bynum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gave Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalin Hyatt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cade Stover</t>
   </si>
   <si>
-    <t xml:space="preserve">Dallas Goedert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talanoa Hufanga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.J. Locke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonnu Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Hutchinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ugo Amadi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Njoku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Thompson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen Pitre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will Dissly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Engram</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier McKinney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaquan Brisker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">George Karlaftis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeffery Simmons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Musgrave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mike Gesicki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Cross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minkah Fitzpatrick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travon Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Heyward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joshua Metellus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theo Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylon Carlies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grant Delpit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branden Fiske</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron Jordan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julian Blackmon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrique Stevenson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Chinn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brandon Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Will McDonald IV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taylor Rapp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rayshawn Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lukas Van Ness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zach Allen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chop Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dexter Lawrence II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Phillips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrann Mathieu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Hines-Allen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jer’Zhan Newton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nnamdi Madubuike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zaire Franklin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kobie Turner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leonard Floyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laiatu Latu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T’Vondre Sweat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frankie Luvu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zach Sieler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calais Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyree Wilson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Haason Reddick</t>
   </si>
   <si>
-    <t xml:space="preserve">Andrew Van Ginkel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demario Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeForest Buckner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leonard Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edgerrin Cooper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erik Kendricks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrel Bernard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Robert Spillane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Wilkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinnen Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devin Lloyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E.J. Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Bolton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Singleton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blake Cashman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matt Milano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Omar Speights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T.J. Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T.J.Watt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremiah Owusu-Koramoah</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dre Greenlaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Burns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quincy Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakobe Dean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.J. Mosley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Christian Rozeboom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bobby Wagner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Sweat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jahlani Tavai</t>
-  </si>
-  <si>
     <t xml:space="preserve">Vanja Dolas</t>
   </si>
   <si>
@@ -1457,160 +1610,100 @@
     <t xml:space="preserve">Alan</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 1.11</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 1 John O</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 3.09</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 1 Adam</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 1.10</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 1 Ben</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 5 5.11</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 1 Jared</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 1.08</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 1 Matt H</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 1.05</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 1 Alan</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 1.07</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 1 Josh</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 3.12</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 2 Adam</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 2 2.10</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 2 Ben</t>
   </si>
   <si>
     <t xml:space="preserve">2026 2 Jared</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 2 2.08</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 2 Matt H</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 1.09</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 2 Alan</t>
   </si>
   <si>
     <t xml:space="preserve">2026 2 John O</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 4 4.12</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 3 Adam</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 3.10</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 3 Ben</t>
   </si>
   <si>
+    <t xml:space="preserve">2026 3 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Alan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Adam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Ben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Jared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Matt H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Alan</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026 3 Jared</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 3.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Alan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Adam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Ben</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Jared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Matt H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Alan</t>
+    <t xml:space="preserve">2025 4 4.11</t>
   </si>
   <si>
     <t xml:space="preserve">2026 4 John O</t>
@@ -1619,15 +1712,6 @@
     <t xml:space="preserve">2026 5 John O</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 5 5.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.07</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025 5 5.07</t>
   </si>
   <si>
@@ -1646,250 +1730,166 @@
     <t xml:space="preserve">Brandon</t>
   </si>
   <si>
+    <t xml:space="preserve">CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 1 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 2 Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 John O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Josh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 4 Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Vanja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Rhode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Joe Luke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 Brandon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 5 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 picks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://football.fantasysports.yahoo.com/f1/215426/showtradedpicks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Draft order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joe Burres Luke Longly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhode Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Josh Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ben Luther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johnathon Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedrick Tillman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian thomas Jr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derek Carr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rasheed Shaheed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathan Greenard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026 3 JohnO</t>
+  </si>
+  <si>
     <t xml:space="preserve">CJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 1 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 2 Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 John O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 4 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Josh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Vanja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Rhode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Joe Luke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 Brandon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 5 CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 5 5.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 picks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://football.fantasysports.yahoo.com/f1/215426/showtradedpicks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Draft order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CJ Perry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joe Burres Luke Longly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhode Family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ben Luther</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johnathon Brooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cedrick Tillman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian thomas Jr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Derek Carr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rasheed Shaheed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathan Greenard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026 3 JohnO</t>
   </si>
   <si>
     <t xml:space="preserve">2026 2 CJ</t>
@@ -2136,7 +2136,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2197,12 +2197,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2259,6 +2259,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -2347,7 +2351,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:AB118"/>
+  <dimension ref="A1:AB119"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8.21"/>
@@ -2406,36 +2410,54 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
+      <c r="E2" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="F2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="I2" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="J2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="M2" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="N2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O2" s="5" t="s">
         <v>11</v>
       </c>
+      <c r="Q2" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="R2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="S2" s="5" t="s">
         <v>12</v>
       </c>
+      <c r="U2" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" s="4" t="s">
         <v>7</v>
       </c>
@@ -2447,28 +2469,46 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
       <c r="B3" s="4"/>
       <c r="C3" s="0" t="s">
         <v>15</v>
       </c>
+      <c r="E3" s="0" t="n">
+        <v>2</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="5" t="s">
         <v>16</v>
       </c>
+      <c r="I3" s="0" t="n">
+        <v>2</v>
+      </c>
       <c r="J3" s="4"/>
       <c r="K3" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="M3" s="0" t="n">
+        <v>2</v>
+      </c>
       <c r="N3" s="4"/>
       <c r="O3" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="Q3" s="0" t="n">
+        <v>2</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="5" t="s">
         <v>19</v>
       </c>
+      <c r="U3" s="0" t="n">
+        <v>2</v>
+      </c>
       <c r="V3" s="4"/>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="0" t="s">
         <v>20</v>
       </c>
       <c r="AB3" s="5" t="s">
@@ -2476,34 +2516,54 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>23</v>
       </c>
+      <c r="E4" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="F4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>24</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="M4" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="5" t="s">
         <v>26</v>
       </c>
+      <c r="Q4" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="R4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="S4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="V4" s="4"/>
-      <c r="W4" s="0" t="s">
+      <c r="U4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="W4" s="5" t="s">
         <v>28</v>
       </c>
       <c r="AB4" s="5" t="s">
@@ -2511,32 +2571,50 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
       <c r="B5" s="6"/>
       <c r="C5" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="E5" s="0" t="n">
+        <v>4</v>
+      </c>
       <c r="F5" s="6"/>
       <c r="G5" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="I5" s="0" t="n">
+        <v>4</v>
+      </c>
       <c r="J5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>32</v>
       </c>
+      <c r="M5" s="0" t="n">
+        <v>4</v>
+      </c>
       <c r="N5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="O5" s="5" t="s">
         <v>33</v>
+      </c>
+      <c r="Q5" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="R5" s="6"/>
       <c r="S5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="V5" s="4"/>
-      <c r="W5" s="0" t="s">
+      <c r="U5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" s="6"/>
+      <c r="W5" s="5" t="s">
         <v>35</v>
       </c>
       <c r="AB5" s="0" t="s">
@@ -2544,30 +2622,46 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="B6" s="6"/>
       <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
+      <c r="E6" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="F6" s="6"/>
       <c r="G6" s="5" t="s">
         <v>38</v>
       </c>
+      <c r="I6" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="J6" s="6"/>
       <c r="K6" s="5" t="s">
         <v>39</v>
       </c>
+      <c r="M6" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="N6" s="6"/>
       <c r="O6" s="5" t="s">
         <v>40</v>
       </c>
+      <c r="Q6" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="R6" s="6"/>
       <c r="S6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="W6" s="5" t="s">
+      <c r="U6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="6"/>
+      <c r="W6" s="0" t="s">
         <v>42</v>
       </c>
       <c r="AB6" s="0" t="s">
@@ -2575,1901 +2669,3004 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
       <c r="B7" s="6"/>
       <c r="C7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="E7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="G7" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="N7" s="6"/>
       <c r="O7" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="Q7" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="R7" s="6"/>
       <c r="S7" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="U7" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="V7" s="6"/>
-      <c r="W7" s="5" t="s">
-        <v>50</v>
+      <c r="W7" s="0" t="s">
+        <v>51</v>
       </c>
       <c r="AB7" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
       <c r="B8" s="6"/>
       <c r="C8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F8" s="6"/>
+        <v>53</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="7"/>
       <c r="G8" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>7</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>7</v>
       </c>
       <c r="N8" s="6"/>
       <c r="O8" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="Q8" s="0" t="n">
+        <v>7</v>
       </c>
       <c r="R8" s="6"/>
       <c r="S8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="V8" s="6"/>
+        <v>57</v>
+      </c>
+      <c r="U8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="W8" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AB8" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="B9" s="7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="E9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="7"/>
       <c r="G9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="6"/>
+      <c r="I9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="K9" s="5" t="s">
         <v>62</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>8</v>
       </c>
       <c r="N9" s="6"/>
       <c r="O9" s="5" t="s">
         <v>63</v>
       </c>
+      <c r="Q9" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="R9" s="6"/>
-      <c r="S9" s="5" t="s">
+      <c r="S9" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="V9" s="6"/>
-      <c r="W9" s="0" t="s">
+      <c r="U9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="V9" s="7"/>
+      <c r="W9" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="AB9" s="5" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
       <c r="B10" s="7"/>
       <c r="C10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="6"/>
+      <c r="E10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" s="7"/>
       <c r="K10" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="Q10" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="R10" s="6"/>
       <c r="S10" s="0" t="s">
-        <v>70</v>
-      </c>
-      <c r="V10" s="6"/>
-      <c r="W10" s="0" t="s">
         <v>71</v>
       </c>
+      <c r="U10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="V10" s="7"/>
+      <c r="W10" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB10" s="0" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
       <c r="B11" s="7"/>
       <c r="C11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F11" s="6"/>
+        <v>74</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7"/>
       <c r="G11" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="N11" s="7"/>
       <c r="O11" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="R11" s="6"/>
-      <c r="S11" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="V11" s="6"/>
-      <c r="W11" s="0" t="s">
         <v>77</v>
       </c>
+      <c r="Q11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="U11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" s="7"/>
+      <c r="W11" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AB11" s="5" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
       <c r="B12" s="7"/>
       <c r="C12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="F12" s="7"/>
       <c r="G12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="0" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="N12" s="7"/>
       <c r="O12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="Q12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" s="7"/>
       <c r="S12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="V12" s="6"/>
+        <v>85</v>
+      </c>
+      <c r="U12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="V12" s="7"/>
       <c r="W12" s="0" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="AB12" s="0" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
       <c r="B13" s="7"/>
       <c r="C13" s="0" t="s">
-        <v>84</v>
-      </c>
-      <c r="F13" s="7"/>
+        <v>88</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="G13" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="7"/>
       <c r="K13" s="5" t="s">
-        <v>86</v>
+        <v>91</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <v>12</v>
       </c>
       <c r="N13" s="7"/>
       <c r="O13" s="5" t="s">
-        <v>87</v>
+        <v>92</v>
+      </c>
+      <c r="Q13" s="0" t="n">
+        <v>12</v>
       </c>
       <c r="R13" s="7"/>
       <c r="S13" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="V13" s="6"/>
-      <c r="W13" s="5" t="s">
-        <v>89</v>
+        <v>93</v>
+      </c>
+      <c r="U13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="V13" s="7"/>
+      <c r="W13" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB13" s="0" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
       <c r="B14" s="7"/>
       <c r="C14" s="0" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" s="7"/>
+        <v>96</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="8"/>
       <c r="G14" s="5" t="s">
-        <v>91</v>
+        <v>97</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>13</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="5" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="M14" s="0" t="n">
+        <v>13</v>
       </c>
       <c r="N14" s="7"/>
       <c r="O14" s="5" t="s">
-        <v>93</v>
+        <v>99</v>
+      </c>
+      <c r="Q14" s="0" t="n">
+        <v>13</v>
       </c>
       <c r="R14" s="7"/>
       <c r="S14" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="V14" s="7" t="s">
-        <v>59</v>
+        <v>100</v>
+      </c>
+      <c r="U14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="W14" s="5" t="s">
-        <v>95</v>
+        <v>101</v>
+      </c>
+      <c r="AB14" s="5" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7"/>
-      <c r="C15" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="5" t="s">
-        <v>97</v>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="0" t="n">
+        <v>14</v>
       </c>
       <c r="J15" s="7"/>
       <c r="K15" s="5" t="s">
-        <v>98</v>
+        <v>105</v>
+      </c>
+      <c r="M15" s="0" t="n">
+        <v>14</v>
       </c>
       <c r="N15" s="7"/>
       <c r="O15" s="5" t="s">
-        <v>99</v>
+        <v>106</v>
+      </c>
+      <c r="Q15" s="0" t="n">
+        <v>14</v>
       </c>
       <c r="R15" s="7"/>
       <c r="S15" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="V15" s="7"/>
+        <v>107</v>
+      </c>
+      <c r="U15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="V15" s="8"/>
       <c r="W15" s="5" t="s">
-        <v>101</v>
+        <v>108</v>
+      </c>
+      <c r="AB15" s="0" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="8" t="s">
-        <v>102</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8"/>
       <c r="C16" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="5" t="s">
-        <v>104</v>
+        <v>110</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="I16" s="0" t="n">
+        <v>15</v>
       </c>
       <c r="J16" s="7"/>
       <c r="K16" s="5" t="s">
-        <v>105</v>
+        <v>113</v>
+      </c>
+      <c r="M16" s="0" t="n">
+        <v>15</v>
       </c>
       <c r="N16" s="7"/>
       <c r="O16" s="0" t="s">
-        <v>106</v>
+        <v>114</v>
+      </c>
+      <c r="Q16" s="0" t="n">
+        <v>15</v>
       </c>
       <c r="R16" s="7"/>
-      <c r="S16" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="V16" s="7"/>
-      <c r="W16" s="5" t="s">
-        <v>108</v>
+      <c r="S16" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="U16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="V16" s="8"/>
+      <c r="W16" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB16" s="0" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
       <c r="B17" s="8"/>
       <c r="C17" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="5" t="s">
-        <v>110</v>
+        <v>118</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" s="9"/>
+      <c r="G17" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="I17" s="0" t="n">
+        <v>16</v>
       </c>
       <c r="J17" s="7"/>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="M17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="N17" s="7"/>
+      <c r="O17" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="R17" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="S17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="U17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="V17" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="N17" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="R17" s="7"/>
-      <c r="S17" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="V17" s="7"/>
       <c r="W17" s="5" t="s">
-        <v>114</v>
+        <v>123</v>
+      </c>
+      <c r="AB17" s="5" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="8"/>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="C18" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="N18" s="8"/>
+        <v>125</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G18" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="I18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>128</v>
+      </c>
+      <c r="M18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="O18" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="R18" s="7"/>
+        <v>129</v>
+      </c>
+      <c r="Q18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="R18" s="8"/>
       <c r="S18" s="0" t="s">
-        <v>119</v>
-      </c>
-      <c r="V18" s="7"/>
-      <c r="W18" s="0" t="s">
-        <v>120</v>
+        <v>130</v>
+      </c>
+      <c r="U18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="V18" s="9"/>
+      <c r="W18" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="AB18" s="0" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="9"/>
       <c r="C19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="J19" s="7"/>
-      <c r="K19" s="5" t="s">
-        <v>124</v>
+        <v>133</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="F19" s="10"/>
+      <c r="G19" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="M19" s="0" t="n">
+        <v>18</v>
       </c>
       <c r="N19" s="8"/>
       <c r="O19" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="R19" s="7"/>
-      <c r="S19" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="R19" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="S19" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="U19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="V19" s="9"/>
+      <c r="W19" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB19" s="0" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="0" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="F20" s="10"/>
+      <c r="G20" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="M20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="N20" s="8"/>
+      <c r="O20" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="R20" s="9"/>
+      <c r="S20" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="U20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="V20" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="V19" s="7"/>
-      <c r="W19" s="0" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="9"/>
-      <c r="C20" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="N20" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="O20" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="R20" s="7"/>
-      <c r="S20" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="V20" s="7"/>
-      <c r="W20" s="0" t="s">
-        <v>133</v>
+      <c r="W20" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AB20" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="9"/>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="C21" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="F21" s="7"/>
+        <v>147</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="G21" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="N21" s="9"/>
+        <v>149</v>
+      </c>
+      <c r="I21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="K21" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="M21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N21" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="O21" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="R21" s="8" t="s">
-        <v>102</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Q21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="R21" s="9"/>
       <c r="S21" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="V21" s="7"/>
-      <c r="W21" s="0" t="s">
-        <v>139</v>
+        <v>152</v>
+      </c>
+      <c r="U21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="V21" s="10"/>
+      <c r="W21" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB21" s="5" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="F22" s="7"/>
+      <c r="A22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="F22" s="11"/>
       <c r="G22" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="J22" s="7"/>
-      <c r="K22" s="5" t="s">
-        <v>143</v>
+        <v>156</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="M22" s="0" t="n">
+        <v>21</v>
       </c>
       <c r="N22" s="9"/>
       <c r="O22" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="R22" s="8"/>
+        <v>158</v>
+      </c>
+      <c r="Q22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="R22" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="S22" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="V22" s="8" t="s">
-        <v>102</v>
+        <v>159</v>
+      </c>
+      <c r="U22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="V22" s="11" t="s">
+        <v>148</v>
       </c>
       <c r="W22" s="5" t="s">
-        <v>146</v>
+        <v>160</v>
+      </c>
+      <c r="AB22" s="0" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>22</v>
+      </c>
       <c r="B23" s="10"/>
       <c r="C23" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="J23" s="7"/>
+        <v>162</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="F23" s="11"/>
+      <c r="G23" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="J23" s="10"/>
       <c r="K23" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="N23" s="10" t="s">
-        <v>140</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="M23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="N23" s="9"/>
       <c r="O23" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="R23" s="8"/>
-      <c r="S23" s="0" t="s">
-        <v>151</v>
-      </c>
-      <c r="V23" s="8"/>
+        <v>165</v>
+      </c>
+      <c r="Q23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="R23" s="10"/>
+      <c r="S23" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="U23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="V23" s="11"/>
       <c r="W23" s="5" t="s">
-        <v>152</v>
+        <v>167</v>
+      </c>
+      <c r="AB23" s="0" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>23</v>
+      </c>
       <c r="B24" s="10"/>
       <c r="C24" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F24" s="8"/>
+        <v>169</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" s="11"/>
       <c r="G24" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="K24" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="N24" s="10"/>
+        <v>170</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="J24" s="10"/>
+      <c r="K24" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="M24" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="O24" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="R24" s="8"/>
+        <v>172</v>
+      </c>
+      <c r="Q24" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="R24" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="S24" s="0" t="s">
-        <v>157</v>
-      </c>
-      <c r="V24" s="8"/>
-      <c r="W24" s="0" t="s">
-        <v>158</v>
+        <v>173</v>
+      </c>
+      <c r="U24" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="V24" s="11"/>
+      <c r="W24" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB24" s="5" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <v>24</v>
+      </c>
       <c r="B25" s="10"/>
       <c r="C25" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="F25" s="8"/>
+        <v>176</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>24</v>
+      </c>
       <c r="G25" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="J25" s="8"/>
+        <v>177</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="K25" s="0" t="s">
-        <v>161</v>
+        <v>178</v>
+      </c>
+      <c r="M25" s="0" t="n">
+        <v>24</v>
       </c>
       <c r="N25" s="10"/>
       <c r="O25" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="R25" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="S25" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="V25" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="W25" s="5" t="s">
-        <v>164</v>
+        <v>179</v>
+      </c>
+      <c r="Q25" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="R25" s="11"/>
+      <c r="S25" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="U25" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="V25" s="11"/>
+      <c r="W25" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB25" s="5" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="10"/>
+      <c r="A26" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="C26" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="F26" s="8"/>
+        <v>183</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>25</v>
+      </c>
       <c r="G26" s="0" t="s">
-        <v>166</v>
-      </c>
-      <c r="J26" s="8"/>
+        <v>184</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J26" s="11"/>
       <c r="K26" s="0" t="s">
-        <v>167</v>
+        <v>185</v>
+      </c>
+      <c r="M26" s="0" t="n">
+        <v>25</v>
       </c>
       <c r="N26" s="10"/>
       <c r="O26" s="0" t="s">
-        <v>168</v>
-      </c>
-      <c r="R26" s="9"/>
-      <c r="S26" s="0" t="s">
-        <v>169</v>
-      </c>
-      <c r="V26" s="9"/>
+        <v>186</v>
+      </c>
+      <c r="Q26" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="R26" s="11"/>
+      <c r="S26" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="U26" s="0" t="n">
+        <v>25</v>
+      </c>
       <c r="W26" s="5" t="s">
-        <v>170</v>
+        <v>188</v>
+      </c>
+      <c r="AB26" s="0" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11" t="s">
-        <v>171</v>
-      </c>
+      <c r="A27" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11"/>
       <c r="C27" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>121</v>
+        <v>190</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>26</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="K27" s="0" t="s">
-        <v>174</v>
+        <v>191</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="M27" s="0" t="n">
+        <v>26</v>
       </c>
       <c r="N27" s="10"/>
       <c r="O27" s="0" t="s">
-        <v>175</v>
-      </c>
-      <c r="R27" s="9"/>
+        <v>193</v>
+      </c>
+      <c r="Q27" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="R27" s="11"/>
       <c r="S27" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="V27" s="9"/>
+        <v>194</v>
+      </c>
+      <c r="U27" s="0" t="n">
+        <v>26</v>
+      </c>
       <c r="W27" s="5" t="s">
-        <v>177</v>
+        <v>195</v>
+      </c>
+      <c r="AB27" s="0" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
+        <v>27</v>
+      </c>
       <c r="B28" s="11"/>
       <c r="C28" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="J28" s="9"/>
+        <v>197</v>
+      </c>
+      <c r="E28" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="G28" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="I28" s="0" t="n">
+        <v>27</v>
+      </c>
       <c r="K28" s="0" t="s">
-        <v>180</v>
+        <v>199</v>
+      </c>
+      <c r="M28" s="0" t="n">
+        <v>27</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="R28" s="9"/>
+        <v>200</v>
+      </c>
+      <c r="Q28" s="0" t="n">
+        <v>27</v>
+      </c>
       <c r="S28" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="V28" s="9"/>
-      <c r="W28" s="0" t="s">
-        <v>183</v>
+        <v>201</v>
+      </c>
+      <c r="U28" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="W28" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB28" s="0" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
+        <v>28</v>
+      </c>
       <c r="B29" s="11"/>
-      <c r="C29" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F29" s="9"/>
+      <c r="C29" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="E29" s="0" t="n">
+        <v>28</v>
+      </c>
       <c r="G29" s="0" t="s">
-        <v>185</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>140</v>
+        <v>205</v>
+      </c>
+      <c r="I29" s="0" t="n">
+        <v>28</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>186</v>
+        <v>206</v>
+      </c>
+      <c r="M29" s="0" t="n">
+        <v>28</v>
       </c>
       <c r="N29" s="11"/>
       <c r="O29" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="R29" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="S29" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="V29" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="W29" s="5" t="s">
-        <v>189</v>
+        <v>207</v>
+      </c>
+      <c r="Q29" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="S29" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="U29" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="W29" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB29" s="0" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="11"/>
-      <c r="C30" s="0" t="s">
-        <v>190</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>140</v>
+      <c r="A30" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E30" s="0" t="n">
+        <v>29</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="J30" s="10"/>
+        <v>212</v>
+      </c>
+      <c r="I30" s="0" t="n">
+        <v>29</v>
+      </c>
       <c r="K30" s="0" t="s">
-        <v>192</v>
+        <v>213</v>
+      </c>
+      <c r="M30" s="0" t="n">
+        <v>29</v>
       </c>
       <c r="N30" s="11"/>
       <c r="O30" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="R30" s="10"/>
-      <c r="S30" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="V30" s="10"/>
-      <c r="W30" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="AB30" s="5"/>
+        <v>214</v>
+      </c>
+      <c r="Q30" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="S30" s="0" t="s">
+        <v>215</v>
+      </c>
+      <c r="U30" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="W30" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB30" s="5" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="11"/>
-      <c r="C31" s="0" t="s">
-        <v>196</v>
-      </c>
-      <c r="F31" s="10"/>
+      <c r="A31" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E31" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="G31" s="0" t="s">
-        <v>197</v>
-      </c>
-      <c r="J31" s="10"/>
+        <v>218</v>
+      </c>
+      <c r="I31" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="K31" s="0" t="s">
-        <v>198</v>
+        <v>219</v>
+      </c>
+      <c r="M31" s="0" t="n">
+        <v>30</v>
       </c>
       <c r="N31" s="11"/>
       <c r="O31" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="R31" s="10"/>
-      <c r="S31" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="V31" s="10"/>
+        <v>220</v>
+      </c>
+      <c r="Q31" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="S31" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="U31" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="W31" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB31" s="5"/>
+        <v>222</v>
+      </c>
+      <c r="AB31" s="5" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11"/>
-      <c r="C32" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="0" t="s">
-        <v>203</v>
-      </c>
-      <c r="J32" s="10"/>
-      <c r="K32" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="N32" s="11"/>
-      <c r="O32" s="0" t="s">
-        <v>205</v>
-      </c>
-      <c r="R32" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="S32" s="0" t="s">
-        <v>206</v>
-      </c>
-      <c r="V32" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="W32" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="AB32" s="5"/>
+      <c r="AB32" s="5" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F33" s="10"/>
-      <c r="G33" s="0" t="s">
-        <v>208</v>
-      </c>
-      <c r="J33" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="K33" s="0" t="s">
-        <v>209</v>
-      </c>
-      <c r="N33" s="11"/>
-      <c r="O33" s="0" t="s">
-        <v>210</v>
-      </c>
-      <c r="R33" s="11"/>
-      <c r="S33" s="0" t="s">
-        <v>211</v>
-      </c>
-      <c r="V33" s="11"/>
-      <c r="W33" s="5" t="s">
-        <v>212</v>
+      <c r="AB33" s="5" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F34" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="G34" s="0" t="s">
-        <v>213</v>
-      </c>
-      <c r="J34" s="11"/>
-      <c r="K34" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="R34" s="11"/>
-      <c r="S34" s="0" t="s">
-        <v>215</v>
-      </c>
-      <c r="V34" s="11"/>
-      <c r="W34" s="5" t="s">
-        <v>216</v>
+      <c r="AB34" s="5" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F35" s="11"/>
-      <c r="G35" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="J35" s="11"/>
-      <c r="K35" s="0" t="s">
-        <v>218</v>
-      </c>
-      <c r="R35" s="11"/>
-      <c r="S35" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="V35" s="11"/>
-      <c r="W35" s="0" t="s">
-        <v>220</v>
+      <c r="AB35" s="5" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F36" s="11"/>
-      <c r="G36" s="0" t="s">
-        <v>221</v>
-      </c>
-      <c r="J36" s="11"/>
-      <c r="K36" s="0" t="s">
-        <v>222</v>
-      </c>
-      <c r="R36" s="11"/>
-      <c r="S36" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="V36" s="11"/>
-      <c r="W36" s="0" t="s">
-        <v>224</v>
+      <c r="AB36" s="5" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F37" s="11"/>
-      <c r="G37" s="0" t="s">
-        <v>225</v>
+      <c r="AB37" s="5" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F38" s="11"/>
-      <c r="G38" s="5" t="s">
-        <v>226</v>
-      </c>
       <c r="S38" s="5"/>
+      <c r="AB38" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB39" s="0" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB40" s="0" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB41" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB42" s="0" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="13"/>
       <c r="H43" s="13"/>
+      <c r="AB43" s="0" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="13"/>
+      <c r="AB44" s="5" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="K45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="O45" s="1"/>
       <c r="R45" s="1" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="S45" s="1"/>
       <c r="V45" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="W45" s="1"/>
+      <c r="AB45" s="5" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <v>1</v>
+      </c>
       <c r="B46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>233</v>
+        <v>244</v>
+      </c>
+      <c r="E46" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>234</v>
+        <v>245</v>
+      </c>
+      <c r="I46" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>235</v>
+        <v>246</v>
+      </c>
+      <c r="M46" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>236</v>
+        <v>247</v>
+      </c>
+      <c r="Q46" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="R46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="S46" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
+      </c>
+      <c r="U46" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="V46" s="4" t="s">
         <v>7</v>
       </c>
       <c r="W46" s="5" t="s">
-        <v>238</v>
+        <v>249</v>
+      </c>
+      <c r="AB46" s="5" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
+        <v>2</v>
+      </c>
       <c r="B47" s="4"/>
       <c r="C47" s="5" t="s">
-        <v>239</v>
+        <v>251</v>
+      </c>
+      <c r="E47" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="5" t="s">
-        <v>240</v>
+        <v>252</v>
+      </c>
+      <c r="I47" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="5" t="s">
-        <v>241</v>
+        <v>253</v>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="5" t="s">
-        <v>242</v>
+        <v>254</v>
+      </c>
+      <c r="Q47" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="5" t="s">
-        <v>243</v>
+        <v>255</v>
+      </c>
+      <c r="U47" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="V47" s="14"/>
       <c r="W47" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="AB47" s="5"/>
+        <v>256</v>
+      </c>
+      <c r="AB47" s="5" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
+        <v>3</v>
+      </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>245</v>
+        <v>258</v>
+      </c>
+      <c r="E48" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="5" t="s">
-        <v>246</v>
+        <v>259</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="N48" s="4"/>
+        <v>260</v>
+      </c>
+      <c r="M48" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>22</v>
+      </c>
       <c r="O48" s="5" t="s">
-        <v>248</v>
+        <v>261</v>
+      </c>
+      <c r="Q48" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="5" t="s">
-        <v>249</v>
+        <v>262</v>
+      </c>
+      <c r="U48" s="0" t="n">
+        <v>3</v>
       </c>
       <c r="V48" s="6" t="s">
         <v>22</v>
       </c>
       <c r="W48" s="5" t="s">
-        <v>250</v>
+        <v>263</v>
+      </c>
+      <c r="AB48" s="5" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="0" t="n">
+        <v>4</v>
+      </c>
       <c r="B49" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="0" t="s">
-        <v>252</v>
+        <v>265</v>
+      </c>
+      <c r="E49" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>22</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>22</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="M49" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="N49" s="6"/>
       <c r="O49" s="5" t="s">
-        <v>254</v>
+        <v>268</v>
+      </c>
+      <c r="Q49" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="R49" s="4"/>
-      <c r="S49" s="5" t="s">
-        <v>255</v>
+      <c r="S49" s="0" t="s">
+        <v>269</v>
+      </c>
+      <c r="U49" s="0" t="n">
+        <v>4</v>
       </c>
       <c r="V49" s="6"/>
       <c r="W49" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y49" s="15"/>
+        <v>270</v>
+      </c>
+      <c r="AB49" s="5" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0" t="n">
+        <v>5</v>
+      </c>
       <c r="B50" s="6"/>
       <c r="C50" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>22</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="E50" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="6"/>
       <c r="G50" s="5" t="s">
-        <v>258</v>
+        <v>273</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="5" t="s">
-        <v>259</v>
+        <v>274</v>
+      </c>
+      <c r="M50" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="N50" s="6"/>
       <c r="O50" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="R50" s="4"/>
-      <c r="S50" s="0" t="s">
-        <v>261</v>
+        <v>275</v>
+      </c>
+      <c r="Q50" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="S50" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="U50" s="0" t="n">
+        <v>5</v>
       </c>
       <c r="V50" s="6"/>
       <c r="W50" s="5" t="s">
-        <v>262</v>
+        <v>277</v>
+      </c>
+      <c r="AB50" s="5" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="0" t="n">
+        <v>6</v>
+      </c>
       <c r="B51" s="6"/>
       <c r="C51" s="0" t="s">
-        <v>263</v>
+        <v>279</v>
+      </c>
+      <c r="E51" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="5" t="s">
-        <v>264</v>
+        <v>280</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51" s="5" t="s">
-        <v>265</v>
+        <v>281</v>
+      </c>
+      <c r="M51" s="0" t="n">
+        <v>6</v>
       </c>
       <c r="N51" s="6"/>
       <c r="O51" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="R51" s="6" t="s">
-        <v>22</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Q51" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="R51" s="6"/>
       <c r="S51" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="V51" s="6"/>
+        <v>283</v>
+      </c>
+      <c r="U51" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="V51" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="W51" s="5" t="s">
-        <v>268</v>
+        <v>284</v>
+      </c>
+      <c r="AB51" s="5" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="0" t="n">
+        <v>7</v>
+      </c>
       <c r="B52" s="6"/>
       <c r="C52" s="5" t="s">
-        <v>269</v>
+        <v>286</v>
+      </c>
+      <c r="E52" s="0" t="n">
+        <v>7</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="5" t="s">
-        <v>270</v>
+        <v>287</v>
+      </c>
+      <c r="I52" s="0" t="n">
+        <v>7</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52" s="5" t="s">
-        <v>271</v>
+        <v>288</v>
+      </c>
+      <c r="M52" s="0" t="n">
+        <v>7</v>
       </c>
       <c r="N52" s="6"/>
       <c r="O52" s="5" t="s">
-        <v>272</v>
+        <v>289</v>
+      </c>
+      <c r="Q52" s="0" t="n">
+        <v>7</v>
       </c>
       <c r="R52" s="6"/>
       <c r="S52" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="V52" s="6"/>
+        <v>290</v>
+      </c>
+      <c r="U52" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="V52" s="7"/>
       <c r="W52" s="5" t="s">
-        <v>274</v>
+        <v>291</v>
+      </c>
+      <c r="AB52" s="0" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="0" t="n">
+        <v>8</v>
+      </c>
       <c r="B53" s="6"/>
       <c r="C53" s="5" t="s">
-        <v>275</v>
+        <v>293</v>
+      </c>
+      <c r="E53" s="0" t="n">
+        <v>8</v>
       </c>
       <c r="F53" s="6"/>
-      <c r="G53" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="J53" s="6"/>
+      <c r="G53" s="0" t="s">
+        <v>294</v>
+      </c>
+      <c r="I53" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="K53" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="N53" s="6"/>
+        <v>295</v>
+      </c>
+      <c r="M53" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="O53" s="5" t="s">
-        <v>278</v>
+        <v>296</v>
+      </c>
+      <c r="Q53" s="0" t="n">
+        <v>8</v>
       </c>
       <c r="R53" s="6"/>
       <c r="S53" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="V53" s="6"/>
+        <v>297</v>
+      </c>
+      <c r="U53" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="V53" s="7"/>
       <c r="W53" s="5" t="s">
-        <v>280</v>
+        <v>298</v>
+      </c>
+      <c r="AB53" s="0" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="6"/>
+      <c r="A54" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="C54" s="5" t="s">
-        <v>281</v>
+        <v>300</v>
+      </c>
+      <c r="E54" s="0" t="n">
+        <v>9</v>
       </c>
       <c r="F54" s="6"/>
-      <c r="G54" s="0" t="s">
-        <v>282</v>
-      </c>
-      <c r="J54" s="6"/>
+      <c r="G54" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="I54" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="J54" s="7"/>
       <c r="K54" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="N54" s="6"/>
+        <v>302</v>
+      </c>
+      <c r="M54" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="N54" s="7"/>
       <c r="O54" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="R54" s="6"/>
+        <v>303</v>
+      </c>
+      <c r="Q54" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="R54" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="S54" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="V54" s="6"/>
+        <v>304</v>
+      </c>
+      <c r="U54" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="V54" s="7"/>
       <c r="W54" s="5" t="s">
-        <v>286</v>
+        <v>305</v>
+      </c>
+      <c r="AB54" s="0" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="6"/>
+      <c r="A55" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B55" s="7"/>
       <c r="C55" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="F55" s="6"/>
+        <v>307</v>
+      </c>
+      <c r="E55" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>45</v>
+      </c>
       <c r="G55" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="J55" s="6"/>
+        <v>308</v>
+      </c>
+      <c r="I55" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J55" s="7"/>
       <c r="K55" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="N55" s="6"/>
+        <v>309</v>
+      </c>
+      <c r="M55" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="N55" s="7"/>
       <c r="O55" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="R55" s="6"/>
+        <v>310</v>
+      </c>
+      <c r="Q55" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="R55" s="7"/>
       <c r="S55" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="V55" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="U55" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="V55" s="7"/>
       <c r="W55" s="5" t="s">
-        <v>292</v>
+        <v>312</v>
+      </c>
+      <c r="AB55" s="5" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="7" t="s">
-        <v>59</v>
-      </c>
+      <c r="A56" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B56" s="7"/>
       <c r="C56" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="F56" s="6"/>
+        <v>314</v>
+      </c>
+      <c r="E56" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="F56" s="7"/>
       <c r="G56" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="I56" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="J56" s="7"/>
       <c r="K56" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="N56" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="M56" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="N56" s="7"/>
       <c r="O56" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="R56" s="6"/>
+        <v>317</v>
+      </c>
+      <c r="Q56" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="R56" s="7"/>
       <c r="S56" s="5" t="s">
-        <v>297</v>
+        <v>318</v>
+      </c>
+      <c r="U56" s="0" t="n">
+        <v>11</v>
       </c>
       <c r="V56" s="7"/>
       <c r="W56" s="5" t="s">
-        <v>298</v>
+        <v>319</v>
+      </c>
+      <c r="AB56" s="5" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="0" t="n">
+        <v>12</v>
+      </c>
       <c r="B57" s="7"/>
       <c r="C57" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="E57" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="F57" s="7"/>
       <c r="G57" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="J57" s="7"/>
+        <v>322</v>
+      </c>
+      <c r="I57" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="K57" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="N57" s="7"/>
+        <v>323</v>
+      </c>
+      <c r="M57" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="N57" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="O57" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="R57" s="6"/>
+        <v>324</v>
+      </c>
+      <c r="Q57" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="R57" s="7"/>
       <c r="S57" s="5" t="s">
-        <v>303</v>
+        <v>325</v>
+      </c>
+      <c r="U57" s="0" t="n">
+        <v>12</v>
       </c>
       <c r="V57" s="7"/>
       <c r="W57" s="5" t="s">
-        <v>304</v>
+        <v>326</v>
+      </c>
+      <c r="AB57" s="5" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="0" t="n">
+        <v>13</v>
+      </c>
       <c r="B58" s="7"/>
       <c r="C58" s="5" t="s">
-        <v>305</v>
+        <v>328</v>
+      </c>
+      <c r="E58" s="0" t="n">
+        <v>13</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="J58" s="7"/>
+        <v>329</v>
+      </c>
+      <c r="I58" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="K58" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="N58" s="7"/>
+        <v>330</v>
+      </c>
+      <c r="M58" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="N58" s="8"/>
       <c r="O58" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="R58" s="7" t="s">
-        <v>59</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="Q58" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="R58" s="7"/>
       <c r="S58" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
+      </c>
+      <c r="U58" s="0" t="n">
+        <v>13</v>
       </c>
       <c r="V58" s="7"/>
       <c r="W58" s="5" t="s">
-        <v>310</v>
+        <v>333</v>
+      </c>
+      <c r="AB58" s="5" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="0" t="n">
+        <v>14</v>
+      </c>
       <c r="B59" s="7"/>
       <c r="C59" s="5" t="s">
-        <v>311</v>
+        <v>335</v>
+      </c>
+      <c r="E59" s="0" t="n">
+        <v>14</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="J59" s="7"/>
+        <v>336</v>
+      </c>
+      <c r="I59" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="J59" s="9"/>
       <c r="K59" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="N59" s="7"/>
+        <v>337</v>
+      </c>
+      <c r="M59" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="N59" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="O59" s="5" t="s">
-        <v>314</v>
+        <v>338</v>
+      </c>
+      <c r="Q59" s="0" t="n">
+        <v>14</v>
       </c>
       <c r="R59" s="7"/>
       <c r="S59" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="V59" s="7"/>
-      <c r="W59" s="5" t="s">
-        <v>316</v>
+        <v>339</v>
+      </c>
+      <c r="U59" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="V59" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="W59" s="0" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB59" s="5" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0" t="n">
+        <v>15</v>
+      </c>
       <c r="B60" s="7"/>
       <c r="C60" s="5" t="s">
-        <v>317</v>
+        <v>342</v>
+      </c>
+      <c r="E60" s="0" t="n">
+        <v>15</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="J60" s="7"/>
+        <v>343</v>
+      </c>
+      <c r="I60" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="J60" s="9"/>
       <c r="K60" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="N60" s="7"/>
+        <v>344</v>
+      </c>
+      <c r="M60" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="N60" s="9"/>
       <c r="O60" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="R60" s="7"/>
+        <v>345</v>
+      </c>
+      <c r="Q60" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="R60" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="S60" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="V60" s="7"/>
-      <c r="W60" s="5" t="s">
-        <v>322</v>
+        <v>346</v>
+      </c>
+      <c r="U60" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="V60" s="8"/>
+      <c r="W60" s="0" t="s">
+        <v>347</v>
+      </c>
+      <c r="AB60" s="5" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="7"/>
+      <c r="A61" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="C61" s="5" t="s">
-        <v>323</v>
+        <v>349</v>
+      </c>
+      <c r="E61" s="0" t="n">
+        <v>16</v>
       </c>
       <c r="F61" s="7"/>
-      <c r="G61" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="J61" s="7"/>
+      <c r="G61" s="0" t="s">
+        <v>350</v>
+      </c>
+      <c r="I61" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="J61" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="K61" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="N61" s="7"/>
-      <c r="O61" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="R61" s="7"/>
+        <v>351</v>
+      </c>
+      <c r="M61" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="N61" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="O61" s="0" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q61" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="R61" s="8"/>
       <c r="S61" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="V61" s="7"/>
-      <c r="W61" s="5" t="s">
-        <v>328</v>
+        <v>353</v>
+      </c>
+      <c r="U61" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="V61" s="8"/>
+      <c r="W61" s="0" t="s">
+        <v>354</v>
+      </c>
+      <c r="AB61" s="5" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="7"/>
+      <c r="A62" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B62" s="8"/>
       <c r="C62" s="5" t="s">
-        <v>329</v>
+        <v>356</v>
+      </c>
+      <c r="E62" s="0" t="n">
+        <v>17</v>
       </c>
       <c r="F62" s="7"/>
-      <c r="G62" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="J62" s="7"/>
+      <c r="G62" s="0" t="s">
+        <v>357</v>
+      </c>
+      <c r="I62" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="J62" s="10"/>
       <c r="K62" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="N62" s="7"/>
-      <c r="O62" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="R62" s="7"/>
+        <v>358</v>
+      </c>
+      <c r="M62" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="N62" s="10"/>
+      <c r="O62" s="0" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q62" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="R62" s="8"/>
       <c r="S62" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="V62" s="7"/>
-      <c r="W62" s="5" t="s">
-        <v>334</v>
+        <v>360</v>
+      </c>
+      <c r="U62" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="V62" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="W62" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB62" s="5" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="7"/>
+      <c r="A63" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="C63" s="0" t="s">
-        <v>335</v>
+        <v>363</v>
+      </c>
+      <c r="E63" s="0" t="n">
+        <v>18</v>
       </c>
       <c r="F63" s="7"/>
-      <c r="G63" s="0" t="s">
-        <v>336</v>
-      </c>
-      <c r="J63" s="8" t="s">
-        <v>102</v>
-      </c>
+      <c r="G63" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="I63" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="J63" s="10"/>
       <c r="K63" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="N63" s="7"/>
-      <c r="O63" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="R63" s="7"/>
+        <v>365</v>
+      </c>
+      <c r="M63" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="N63" s="10"/>
+      <c r="O63" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q63" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="R63" s="9" t="s">
+        <v>111</v>
+      </c>
       <c r="S63" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="V63" s="7"/>
-      <c r="W63" s="5" t="s">
-        <v>340</v>
+        <v>367</v>
+      </c>
+      <c r="U63" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="V63" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="W63" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="AB63" s="5" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="7"/>
+      <c r="A64" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B64" s="9"/>
       <c r="C64" s="5" t="s">
-        <v>341</v>
+        <v>370</v>
+      </c>
+      <c r="E64" s="0" t="n">
+        <v>19</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="0" t="s">
-        <v>342</v>
-      </c>
-      <c r="J64" s="8"/>
+        <v>371</v>
+      </c>
+      <c r="I64" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="J64" s="10"/>
       <c r="K64" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="N64" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="O64" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="R64" s="7"/>
+        <v>372</v>
+      </c>
+      <c r="M64" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="N64" s="10"/>
+      <c r="O64" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q64" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="R64" s="9"/>
       <c r="S64" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="V64" s="7"/>
-      <c r="W64" s="5" t="s">
-        <v>346</v>
+        <v>374</v>
+      </c>
+      <c r="U64" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="V64" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="W64" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="AB64" s="0" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="F65" s="7"/>
+      <c r="A65" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="E65" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="G65" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="J65" s="8"/>
+        <v>378</v>
+      </c>
+      <c r="I65" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" s="10"/>
       <c r="K65" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="N65" s="8"/>
-      <c r="O65" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="R65" s="7"/>
-      <c r="S65" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="V65" s="7"/>
-      <c r="W65" s="5" t="s">
-        <v>352</v>
+        <v>379</v>
+      </c>
+      <c r="M65" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="N65" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="O65" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q65" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="R65" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="S65" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="U65" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="V65" s="11"/>
+      <c r="W65" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="AB65" s="5" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="8"/>
-      <c r="C66" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="F66" s="8" t="s">
-        <v>102</v>
-      </c>
+      <c r="A66" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="E66" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="F66" s="8"/>
       <c r="G66" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="J66" s="9" t="s">
-        <v>121</v>
-      </c>
+        <v>385</v>
+      </c>
+      <c r="I66" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="J66" s="10"/>
       <c r="K66" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="N66" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="O66" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="R66" s="7"/>
-      <c r="S66" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="V66" s="7"/>
-      <c r="W66" s="0" t="s">
-        <v>358</v>
+        <v>386</v>
+      </c>
+      <c r="M66" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="N66" s="11"/>
+      <c r="O66" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q66" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="R66" s="10"/>
+      <c r="S66" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="U66" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="W66" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="AB66" s="0" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="8"/>
+      <c r="A67" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B67" s="10"/>
       <c r="C67" s="0" t="s">
-        <v>359</v>
+        <v>391</v>
+      </c>
+      <c r="E67" s="0" t="n">
+        <v>22</v>
       </c>
       <c r="F67" s="8"/>
-      <c r="G67" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="J67" s="9"/>
-      <c r="K67" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="N67" s="9"/>
-      <c r="O67" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="R67" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="S67" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="V67" s="7"/>
+      <c r="G67" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="I67" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="J67" s="10"/>
+      <c r="K67" s="0" t="s">
+        <v>393</v>
+      </c>
+      <c r="M67" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="N67" s="11"/>
+      <c r="O67" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q67" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="R67" s="10"/>
+      <c r="S67" s="0" t="s">
+        <v>395</v>
+      </c>
+      <c r="U67" s="0" t="n">
+        <v>22</v>
+      </c>
       <c r="W67" s="0" t="s">
-        <v>364</v>
+        <v>396</v>
+      </c>
+      <c r="AB67" s="0" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="A68" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B68" s="10"/>
       <c r="C68" s="0" t="s">
-        <v>365</v>
-      </c>
-      <c r="F68" s="8"/>
-      <c r="G68" s="0" t="s">
-        <v>366</v>
-      </c>
-      <c r="J68" s="9"/>
+        <v>398</v>
+      </c>
+      <c r="E68" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="I68" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="J68" s="11" t="s">
+        <v>148</v>
+      </c>
       <c r="K68" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="N68" s="9"/>
-      <c r="O68" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="R68" s="8"/>
-      <c r="S68" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="V68" s="8" t="s">
-        <v>102</v>
+        <v>400</v>
+      </c>
+      <c r="M68" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="N68" s="11"/>
+      <c r="O68" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="Q68" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="R68" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="S68" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="U68" s="0" t="n">
+        <v>23</v>
       </c>
       <c r="W68" s="0" t="s">
-        <v>370</v>
+        <v>403</v>
+      </c>
+      <c r="AB68" s="5" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="9"/>
-      <c r="C69" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>121</v>
-      </c>
+      <c r="A69" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C69" s="0" t="s">
+        <v>405</v>
+      </c>
+      <c r="E69" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" s="9"/>
       <c r="G69" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="J69" s="10" t="s">
-        <v>140</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="I69" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="J69" s="11"/>
       <c r="K69" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="N69" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="O69" s="0" t="s">
-        <v>374</v>
-      </c>
-      <c r="R69" s="8"/>
-      <c r="S69" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="V69" s="8"/>
+        <v>407</v>
+      </c>
+      <c r="M69" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="O69" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q69" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="R69" s="11"/>
+      <c r="S69" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="U69" s="0" t="n">
+        <v>24</v>
+      </c>
       <c r="W69" s="0" t="s">
-        <v>376</v>
+        <v>410</v>
+      </c>
+      <c r="AB69" s="5" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="9"/>
+      <c r="A70" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B70" s="15"/>
       <c r="C70" s="0" t="s">
-        <v>377</v>
+        <v>412</v>
+      </c>
+      <c r="E70" s="0" t="n">
+        <v>25</v>
       </c>
       <c r="F70" s="9"/>
       <c r="G70" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="J70" s="10"/>
-      <c r="K70" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="N70" s="10"/>
+        <v>413</v>
+      </c>
+      <c r="I70" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J70" s="11"/>
+      <c r="K70" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="M70" s="0" t="n">
+        <v>25</v>
+      </c>
       <c r="O70" s="0" t="s">
-        <v>380</v>
-      </c>
-      <c r="R70" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="S70" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="V70" s="8"/>
+        <v>415</v>
+      </c>
+      <c r="Q70" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="R70" s="11"/>
+      <c r="S70" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="U70" s="0" t="n">
+        <v>25</v>
+      </c>
       <c r="W70" s="0" t="s">
-        <v>382</v>
+        <v>417</v>
+      </c>
+      <c r="AB70" s="5" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="9"/>
+      <c r="A71" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="B71" s="15"/>
       <c r="C71" s="0" t="s">
-        <v>383</v>
-      </c>
-      <c r="F71" s="9"/>
+        <v>419</v>
+      </c>
+      <c r="E71" s="0" t="n">
+        <v>26</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>126</v>
+      </c>
       <c r="G71" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="J71" s="10"/>
+        <v>420</v>
+      </c>
+      <c r="I71" s="0" t="n">
+        <v>26</v>
+      </c>
       <c r="K71" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="N71" s="10"/>
+        <v>421</v>
+      </c>
+      <c r="M71" s="0" t="n">
+        <v>26</v>
+      </c>
       <c r="O71" s="0" t="s">
-        <v>386</v>
-      </c>
-      <c r="R71" s="9"/>
+        <v>422</v>
+      </c>
+      <c r="Q71" s="0" t="n">
+        <v>26</v>
+      </c>
       <c r="S71" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="V71" s="9" t="s">
-        <v>121</v>
+        <v>423</v>
+      </c>
+      <c r="U71" s="0" t="n">
+        <v>26</v>
       </c>
       <c r="W71" s="0" t="s">
-        <v>388</v>
+        <v>424</v>
+      </c>
+      <c r="AB71" s="0" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="9"/>
-      <c r="C72" s="0" t="s">
-        <v>389</v>
-      </c>
-      <c r="F72" s="9"/>
+      <c r="A72" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="B72" s="15"/>
+      <c r="C72" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E72" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="F72" s="10"/>
       <c r="G72" s="0" t="s">
-        <v>390</v>
-      </c>
-      <c r="J72" s="10"/>
-      <c r="K72" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="N72" s="10"/>
+        <v>427</v>
+      </c>
+      <c r="I72" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="K72" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="M72" s="0" t="n">
+        <v>27</v>
+      </c>
       <c r="O72" s="0" t="s">
-        <v>392</v>
-      </c>
-      <c r="R72" s="9"/>
-      <c r="S72" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="V72" s="9"/>
+        <v>429</v>
+      </c>
+      <c r="Q72" s="0" t="n">
+        <v>27</v>
+      </c>
+      <c r="S72" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="U72" s="0" t="n">
+        <v>27</v>
+      </c>
       <c r="W72" s="0" t="s">
-        <v>394</v>
+        <v>431</v>
+      </c>
+      <c r="AB72" s="5" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="C73" s="0" t="s">
-        <v>395</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="J73" s="10"/>
-      <c r="K73" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="N73" s="10"/>
+      <c r="A73" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="E73" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="F73" s="10"/>
+      <c r="G73" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="I73" s="0" t="n">
+        <v>28</v>
+      </c>
+      <c r="K73" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="M73" s="0" t="n">
+        <v>28</v>
+      </c>
       <c r="O73" s="0" t="s">
-        <v>398</v>
-      </c>
-      <c r="R73" s="10" t="s">
-        <v>140</v>
+        <v>436</v>
+      </c>
+      <c r="Q73" s="0" t="n">
+        <v>28</v>
       </c>
       <c r="S73" s="0" t="s">
-        <v>399</v>
-      </c>
-      <c r="V73" s="9"/>
+        <v>437</v>
+      </c>
+      <c r="U73" s="0" t="n">
+        <v>28</v>
+      </c>
       <c r="W73" s="0" t="s">
-        <v>400</v>
+        <v>438</v>
+      </c>
+      <c r="AB73" s="0" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="10"/>
+      <c r="A74" s="0" t="n">
+        <v>29</v>
+      </c>
       <c r="C74" s="0" t="s">
-        <v>401</v>
-      </c>
-      <c r="F74" s="10"/>
-      <c r="G74" s="0" t="s">
-        <v>402</v>
-      </c>
-      <c r="J74" s="10"/>
-      <c r="K74" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="N74" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="O74" s="0" t="s">
-        <v>404</v>
-      </c>
-      <c r="R74" s="10"/>
+        <v>440</v>
+      </c>
+      <c r="E74" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G74" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="I74" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="K74" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="M74" s="0" t="n">
+        <v>29</v>
+      </c>
+      <c r="O74" s="16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Q74" s="0" t="n">
+        <v>29</v>
+      </c>
       <c r="S74" s="0" t="s">
-        <v>405</v>
-      </c>
-      <c r="V74" s="10" t="s">
-        <v>140</v>
+        <v>443</v>
+      </c>
+      <c r="U74" s="0" t="n">
+        <v>29</v>
       </c>
       <c r="W74" s="0" t="s">
-        <v>406</v>
-      </c>
-      <c r="AB74" s="5"/>
+        <v>444</v>
+      </c>
+      <c r="AB74" s="0" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="10"/>
+      <c r="A75" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="C75" s="0" t="s">
-        <v>407</v>
-      </c>
-      <c r="F75" s="10"/>
+        <v>446</v>
+      </c>
+      <c r="E75" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="F75" s="11"/>
       <c r="G75" s="0" t="s">
-        <v>408</v>
-      </c>
-      <c r="J75" s="10"/>
+        <v>447</v>
+      </c>
+      <c r="I75" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="K75" s="0" t="s">
-        <v>409</v>
-      </c>
-      <c r="N75" s="11"/>
-      <c r="O75" s="0" t="s">
-        <v>410</v>
-      </c>
-      <c r="R75" s="10"/>
+        <v>448</v>
+      </c>
+      <c r="M75" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="O75" s="16" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Q75" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="S75" s="0" t="s">
-        <v>411</v>
-      </c>
-      <c r="V75" s="10"/>
+        <v>449</v>
+      </c>
+      <c r="U75" s="0" t="n">
+        <v>30</v>
+      </c>
       <c r="W75" s="0" t="s">
-        <v>412</v>
-      </c>
-      <c r="AB75" s="5"/>
+        <v>450</v>
+      </c>
+      <c r="AB75" s="5" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="10"/>
-      <c r="C76" s="0" t="s">
-        <v>413</v>
-      </c>
-      <c r="F76" s="10"/>
-      <c r="G76" s="0" t="s">
-        <v>414</v>
-      </c>
-      <c r="J76" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="K76" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="N76" s="11"/>
-      <c r="O76" s="0" t="s">
-        <v>416</v>
-      </c>
-      <c r="R76" s="10"/>
-      <c r="S76" s="0" t="s">
-        <v>417</v>
-      </c>
-      <c r="V76" s="10"/>
-      <c r="W76" s="0" t="s">
-        <v>418</v>
-      </c>
-      <c r="AB76" s="5"/>
+      <c r="AB76" s="0" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="C77" s="0" t="s">
-        <v>419</v>
-      </c>
-      <c r="F77" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="J77" s="11"/>
-      <c r="K77" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="N77" s="11"/>
-      <c r="O77" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="R77" s="10"/>
-      <c r="S77" s="0" t="s">
-        <v>423</v>
-      </c>
-      <c r="V77" s="10"/>
-      <c r="W77" s="0" t="s">
-        <v>424</v>
+      <c r="AB77" s="5" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="16"/>
-      <c r="C78" s="0" t="s">
-        <v>425</v>
-      </c>
-      <c r="F78" s="11"/>
-      <c r="G78" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="J78" s="11"/>
-      <c r="K78" s="0" t="s">
-        <v>427</v>
-      </c>
-      <c r="N78" s="11"/>
-      <c r="O78" s="0" t="s">
-        <v>428</v>
-      </c>
-      <c r="R78" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="S78" s="0" t="s">
-        <v>429</v>
-      </c>
-      <c r="V78" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="W78" s="0" t="s">
-        <v>430</v>
+      <c r="AB78" s="0" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="16"/>
-      <c r="C79" s="0" t="s">
-        <v>431</v>
-      </c>
-      <c r="F79" s="11"/>
-      <c r="G79" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="R79" s="11"/>
-      <c r="S79" s="0" t="s">
-        <v>433</v>
-      </c>
-      <c r="V79" s="11"/>
-      <c r="W79" s="0" t="s">
-        <v>434</v>
+      <c r="AB79" s="0" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="16"/>
-      <c r="C80" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="F80" s="11"/>
-      <c r="G80" s="0" t="s">
-        <v>436</v>
-      </c>
-      <c r="R80" s="11"/>
-      <c r="S80" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="V80" s="11"/>
-      <c r="W80" s="0" t="s">
-        <v>438</v>
+      <c r="AB80" s="0" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="16"/>
-      <c r="C81" s="0" t="s">
-        <v>439</v>
-      </c>
-      <c r="F81" s="11"/>
-      <c r="G81" s="0" t="s">
-        <v>440</v>
-      </c>
       <c r="H81" s="13"/>
-      <c r="R81" s="11"/>
-      <c r="S81" s="0" t="s">
-        <v>441</v>
-      </c>
-      <c r="V81" s="11"/>
-      <c r="W81" s="0" t="s">
-        <v>442</v>
+      <c r="AB81" s="0" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F82" s="11"/>
-      <c r="G82" s="0" t="s">
-        <v>443</v>
-      </c>
-      <c r="V82" s="11"/>
-      <c r="W82" s="0" t="s">
-        <v>444</v>
+      <c r="AB82" s="0" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB83" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB84" s="5" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB85" s="5"/>
+      <c r="AB85" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB86" s="0" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB87" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB88" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB89" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB90" s="5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB91" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB92" s="5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB93" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB94" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB95" s="0" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB96" s="0" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB97" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB98" s="5" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB99" s="5"/>
+      <c r="AB99" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB100" s="5" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB101" s="5"/>
+      <c r="AB101" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB102" s="5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB103" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB104" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB105" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB106" s="0" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB107" s="0" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB108" s="0" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB109" s="0" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB110" s="0" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB111" s="0" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB112" s="0" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB113" s="0" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB114" s="0" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB115" s="0" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB116" s="0" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB117" s="5" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AB118" s="5"/>
+      <c r="AB118" s="0" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AB119" s="0" t="s">
+        <v>495</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="32">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="J1:K1"/>
@@ -4481,42 +5678,17 @@
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="N2:N4"/>
     <mergeCell ref="R2:R3"/>
-    <mergeCell ref="V2:V5"/>
     <mergeCell ref="B4:B8"/>
-    <mergeCell ref="F4:F11"/>
-    <mergeCell ref="R4:R11"/>
-    <mergeCell ref="J5:J12"/>
     <mergeCell ref="N5:N9"/>
-    <mergeCell ref="V6:V13"/>
-    <mergeCell ref="B9:B15"/>
-    <mergeCell ref="N10:N16"/>
-    <mergeCell ref="F12:F22"/>
-    <mergeCell ref="R12:R20"/>
-    <mergeCell ref="J13:J23"/>
-    <mergeCell ref="V14:V21"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="N17:N19"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="R21:R24"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="V22:V24"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="N23:N27"/>
-    <mergeCell ref="J24:J26"/>
-    <mergeCell ref="R25:R28"/>
-    <mergeCell ref="V25:V28"/>
-    <mergeCell ref="F27:F29"/>
-    <mergeCell ref="J27:J28"/>
-    <mergeCell ref="N28:N33"/>
-    <mergeCell ref="J29:J32"/>
-    <mergeCell ref="R29:R31"/>
-    <mergeCell ref="V29:V31"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="R32:R36"/>
-    <mergeCell ref="V32:V36"/>
-    <mergeCell ref="J33:J36"/>
-    <mergeCell ref="F34:F38"/>
+    <mergeCell ref="B9:B14"/>
+    <mergeCell ref="N10:N17"/>
+    <mergeCell ref="V14:V16"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="J18:J20"/>
+    <mergeCell ref="N18:N20"/>
+    <mergeCell ref="B21:B25"/>
+    <mergeCell ref="N21:N23"/>
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="F45:G45"/>
     <mergeCell ref="J45:K45"/>
@@ -4524,43 +5696,9 @@
     <mergeCell ref="R45:S45"/>
     <mergeCell ref="V45:W45"/>
     <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F46:F49"/>
     <mergeCell ref="J46:J48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="R46:R50"/>
-    <mergeCell ref="V48:V54"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="J49:J55"/>
-    <mergeCell ref="N49:N55"/>
-    <mergeCell ref="F50:F56"/>
-    <mergeCell ref="R51:R57"/>
-    <mergeCell ref="V55:V67"/>
-    <mergeCell ref="B56:B64"/>
-    <mergeCell ref="J56:J62"/>
-    <mergeCell ref="N56:N63"/>
-    <mergeCell ref="F57:F65"/>
-    <mergeCell ref="R58:R66"/>
-    <mergeCell ref="J63:J65"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="F66:F68"/>
-    <mergeCell ref="J66:J68"/>
-    <mergeCell ref="R67:R69"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="V68:V70"/>
-    <mergeCell ref="F69:F72"/>
-    <mergeCell ref="J69:J75"/>
-    <mergeCell ref="N69:N73"/>
-    <mergeCell ref="R70:R72"/>
-    <mergeCell ref="V71:V73"/>
-    <mergeCell ref="B73:B76"/>
-    <mergeCell ref="R73:R77"/>
-    <mergeCell ref="N74:N78"/>
-    <mergeCell ref="V74:V77"/>
-    <mergeCell ref="J76:J78"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="F77:F82"/>
-    <mergeCell ref="R78:R81"/>
-    <mergeCell ref="V78:V82"/>
+    <mergeCell ref="F65:F67"/>
+    <mergeCell ref="B69:B72"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4589,115 +5727,115 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>445</v>
+        <v>496</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>446</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>447</v>
+        <v>498</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>448</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>449</v>
+        <v>500</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>450</v>
+        <v>501</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>451</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>452</v>
+        <v>503</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>453</v>
+        <v>504</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>451</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>454</v>
+        <v>505</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>455</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>456</v>
+        <v>507</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>457</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>458</v>
+        <v>509</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>459</v>
+        <v>510</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>460</v>
+        <v>511</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>461</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>462</v>
+        <v>513</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>463</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>464</v>
+        <v>515</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>465</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>466</v>
+        <v>517</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>467</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>468</v>
+        <v>519</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>469</v>
+        <v>520</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>451</v>
+        <v>502</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>470</v>
+        <v>521</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>471</v>
+        <v>522</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4759,237 +5897,237 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>503</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>472</v>
+        <v>523</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="19"/>
       <c r="G1" s="1" t="s">
-        <v>473</v>
+        <v>524</v>
       </c>
       <c r="H1" s="1"/>
       <c r="J1" s="1" t="s">
-        <v>474</v>
+        <v>525</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="19"/>
       <c r="M1" s="1" t="s">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="N1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>476</v>
+        <v>527</v>
       </c>
       <c r="Q1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>477</v>
+        <v>211</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>478</v>
+        <v>528</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>479</v>
+        <v>177</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>480</v>
+        <v>529</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>481</v>
+        <v>192</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>482</v>
+        <v>530</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>483</v>
+        <v>212</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>485</v>
+        <v>201</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>486</v>
+        <v>532</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>487</v>
+        <v>188</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>488</v>
+        <v>533</v>
       </c>
       <c r="BG2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>489</v>
+        <v>217</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>490</v>
+        <v>534</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>491</v>
+        <v>184</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>492</v>
+        <v>535</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>493</v>
+        <v>199</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>494</v>
+        <v>536</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>495</v>
+        <v>537</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>496</v>
+        <v>208</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>498</v>
+        <v>195</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>499</v>
+        <v>539</v>
       </c>
       <c r="BG3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="0" t="s">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>501</v>
+        <v>191</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>502</v>
+        <v>541</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>503</v>
+        <v>206</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="K4" s="0" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>506</v>
+        <v>215</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>507</v>
+        <v>543</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>508</v>
+        <v>202</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>509</v>
+        <v>544</v>
       </c>
       <c r="BG4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>511</v>
+        <v>198</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>512</v>
+        <v>546</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>513</v>
+        <v>213</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>514</v>
+        <v>547</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>515</v>
+        <v>548</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>516</v>
+        <v>221</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>517</v>
+        <v>549</v>
+      </c>
+      <c r="P5" s="0" t="s">
+        <v>209</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>518</v>
+        <v>550</v>
       </c>
       <c r="BG5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>519</v>
+        <v>551</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>520</v>
+        <v>205</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>521</v>
+        <v>552</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>522</v>
+        <v>219</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>523</v>
+        <v>553</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>525</v>
+        <v>555</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>526</v>
+        <v>556</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>527</v>
+        <v>205</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>528</v>
+        <v>557</v>
       </c>
       <c r="BG6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>529</v>
+        <v>558</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>483</v>
+        <v>212</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>520</v>
+        <v>559</v>
       </c>
       <c r="BG7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>531</v>
+        <v>218</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>532</v>
+        <v>222</v>
       </c>
       <c r="BG8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>561</v>
+      </c>
       <c r="P9" s="0" t="s">
-        <v>533</v>
+        <v>562</v>
       </c>
       <c r="BG9" s="0"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P10" s="0" t="s">
-        <v>534</v>
-      </c>
       <c r="BG10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5024,252 +6162,252 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="B21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="19"/>
       <c r="G21" s="1" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="H21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>538</v>
+        <v>566</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="19"/>
       <c r="M21" s="1" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="N21" s="1"/>
       <c r="P21" s="1" t="s">
-        <v>540</v>
+        <v>568</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="BG21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>541</v>
+        <v>433</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>569</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>543</v>
+        <v>571</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>544</v>
+        <v>421</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>545</v>
+        <v>572</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>546</v>
+        <v>408</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>547</v>
+        <v>573</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>548</v>
+        <v>423</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>549</v>
+        <v>574</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>550</v>
+        <v>389</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="BG22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>552</v>
+        <v>440</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>576</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>554</v>
+        <v>578</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>555</v>
+        <v>428</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>556</v>
+        <v>579</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>557</v>
+        <v>415</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>558</v>
+        <v>580</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>559</v>
+        <v>430</v>
       </c>
       <c r="N23" s="0" t="s">
-        <v>560</v>
+        <v>581</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>561</v>
+        <v>396</v>
       </c>
       <c r="Q23" s="0" t="s">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="BG23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>563</v>
+        <v>446</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>566</v>
+        <v>435</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>568</v>
+        <v>422</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="M24" s="0" t="s">
-        <v>570</v>
+        <v>437</v>
       </c>
       <c r="N24" s="0" t="s">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="P24" s="0" t="s">
-        <v>572</v>
+        <v>403</v>
       </c>
       <c r="Q24" s="0" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="BG24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>577</v>
+        <v>442</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>579</v>
+        <v>429</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="M25" s="0" t="s">
-        <v>581</v>
+        <v>443</v>
       </c>
       <c r="N25" s="0" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="Q25" s="0" t="s">
-        <v>584</v>
+        <v>410</v>
       </c>
       <c r="BG25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>585</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>588</v>
+        <v>448</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>590</v>
+        <v>436</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>592</v>
+        <v>449</v>
       </c>
       <c r="N26" s="0" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>594</v>
+        <v>417</v>
       </c>
       <c r="Q26" s="0" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="BG26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>596</v>
-      </c>
       <c r="D27" s="5"/>
       <c r="G27" s="5"/>
       <c r="J27" s="5"/>
       <c r="M27" s="5"/>
       <c r="P27" s="0" t="s">
-        <v>597</v>
+        <v>424</v>
       </c>
       <c r="BG27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>598</v>
-      </c>
       <c r="G28" s="5"/>
       <c r="M28" s="5"/>
       <c r="P28" s="0" t="s">
-        <v>599</v>
+        <v>431</v>
       </c>
       <c r="BG28" s="0"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>600</v>
-      </c>
       <c r="G29" s="20"/>
       <c r="M29" s="5"/>
+      <c r="P29" s="0" t="s">
+        <v>438</v>
+      </c>
       <c r="BG29" s="0"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G30" s="20"/>
       <c r="M30" s="5"/>
+      <c r="P30" s="0" t="s">
+        <v>444</v>
+      </c>
       <c r="BG30" s="0"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G31" s="20"/>
+      <c r="P31" s="0" t="s">
+        <v>450</v>
+      </c>
       <c r="BG31" s="0"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5321,7 +6459,7 @@
         <v>1.01</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>604</v>
+        <v>568</v>
       </c>
       <c r="BG37" s="0"/>
       <c r="BH37" s="0"/>
@@ -5336,7 +6474,7 @@
         <v>1.02</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>460</v>
+        <v>511</v>
       </c>
       <c r="BG38" s="0"/>
       <c r="BH38" s="0"/>
@@ -5351,7 +6489,7 @@
         <v>1.03</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="BG39" s="0"/>
       <c r="BH39" s="0"/>
@@ -5366,7 +6504,7 @@
         <v>1.04</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="BG40" s="0"/>
       <c r="BH40" s="0"/>
@@ -5381,7 +6519,7 @@
         <v>1.05</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>445</v>
+        <v>496</v>
       </c>
       <c r="BG41" s="0"/>
       <c r="BH41" s="0"/>
@@ -5396,7 +6534,7 @@
         <v>1.06</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="BG42" s="0"/>
       <c r="BH42" s="0"/>
@@ -5411,7 +6549,7 @@
         <v>1.07</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>468</v>
+        <v>519</v>
       </c>
       <c r="BG43" s="0"/>
       <c r="BH43" s="0"/>
@@ -5426,7 +6564,7 @@
         <v>1.08</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>470</v>
+        <v>521</v>
       </c>
       <c r="BG44" s="0"/>
       <c r="BH44" s="0"/>
@@ -5441,7 +6579,7 @@
         <v>1.09</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>458</v>
+        <v>509</v>
       </c>
       <c r="BG45" s="0"/>
       <c r="BH45" s="0"/>
@@ -5456,7 +6594,7 @@
         <v>1.1</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="BG46" s="0"/>
       <c r="BH46" s="0"/>
@@ -5471,7 +6609,7 @@
         <v>1.11</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>466</v>
+        <v>517</v>
       </c>
       <c r="BG47" s="0"/>
       <c r="BH47" s="0"/>
@@ -5486,7 +6624,7 @@
         <v>1.12</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>452</v>
+        <v>503</v>
       </c>
       <c r="BG48" s="0"/>
       <c r="BH48" s="0"/>
@@ -7166,68 +8304,68 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25"/>
       <c r="B2" s="26" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25"/>
       <c r="B3" s="26" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25"/>
       <c r="B5" s="26" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27"/>
       <c r="B7" s="28" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25"/>
       <c r="B10" s="26" t="s">
-        <v>490</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27"/>
       <c r="B11" s="28" t="s">
-        <v>510</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7236,42 +8374,42 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25"/>
       <c r="B14" s="26" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25"/>
       <c r="B15" s="26" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27"/>
       <c r="B16" s="28" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27"/>
       <c r="B19" s="28" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7280,22 +8418,22 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>474</v>
+        <v>525</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25"/>
       <c r="B22" s="26" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25"/>
       <c r="B23" s="26" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7304,23 +8442,23 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25"/>
       <c r="B26" s="26" t="s">
-        <v>135</v>
+        <v>68</v>
       </c>
       <c r="G26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="27"/>
       <c r="B27" s="28" t="s">
-        <v>142</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7329,15 +8467,15 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>472</v>
+        <v>523</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>294</v>
+        <v>459</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>472</v>
+        <v>523</v>
       </c>
       <c r="B31" s="29" t="n">
         <v>1.12</v>
@@ -7349,36 +8487,36 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>476</v>
+        <v>527</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="27"/>
       <c r="B34" s="28" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25"/>
       <c r="B37" s="30" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25"/>
       <c r="B38" s="30" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7387,14 +8525,151 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>540</v>
+        <v>621</v>
       </c>
       <c r="B40" s="28" t="s">
         <v>622</v>
       </c>
     </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="23" t="s">
+        <v>563</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="E43" s="0"/>
+      <c r="F43" s="0"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="25"/>
+      <c r="B44" s="26" t="s">
+        <v>477</v>
+      </c>
+      <c r="E44" s="0"/>
+      <c r="F44" s="0"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="25"/>
+      <c r="B45" s="30"/>
+      <c r="E45" s="0"/>
+      <c r="F45" s="0"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="27" t="s">
+        <v>621</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>576</v>
+      </c>
+      <c r="E46" s="0"/>
+      <c r="F46" s="0"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E47" s="0"/>
+      <c r="F47" s="0"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="23" t="s">
+        <v>564</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="F48" s="0"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="25"/>
+      <c r="B49" s="26" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="25"/>
+      <c r="B50" s="26" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="25"/>
+      <c r="B51" s="30"/>
+      <c r="E51" s="0"/>
+      <c r="F51" s="0"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="27" t="s">
+        <v>621</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="D52" s="0"/>
+      <c r="E52" s="0"/>
+      <c r="F52" s="0"/>
+      <c r="G52" s="0"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>558</v>
+      </c>
+      <c r="D54" s="0"/>
+      <c r="E54" s="0"/>
+      <c r="F54" s="0"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="25"/>
+      <c r="B55" s="30"/>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
+      <c r="F55" s="0"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="27" t="s">
+        <v>612</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D56" s="0"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D57" s="0"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D58" s="0"/>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D59" s="0"/>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C60" s="0"/>
+      <c r="D60" s="0"/>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C61" s="0"/>
+      <c r="D61" s="0"/>
+      <c r="E61" s="0"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C62" s="0"/>
+      <c r="D62" s="0"/>
+    </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D78" s="15"/>
+      <c r="D78" s="31"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C82" s="0"/>
@@ -7459,36 +8734,36 @@
       <c r="A132" s="0"/>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D135" s="15"/>
+      <c r="D135" s="31"/>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C159" s="15"/>
+      <c r="C159" s="31"/>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D187" s="15"/>
+      <c r="D187" s="31"/>
     </row>
     <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C190" s="15"/>
-      <c r="D190" s="15"/>
+      <c r="C190" s="31"/>
+      <c r="D190" s="31"/>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D216" s="31"/>
+      <c r="D216" s="32"/>
       <c r="E216" s="0"/>
     </row>
     <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D217" s="31"/>
+      <c r="D217" s="32"/>
       <c r="E217" s="0"/>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D218" s="31"/>
+      <c r="D218" s="32"/>
       <c r="E218" s="0"/>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D219" s="31"/>
+      <c r="D219" s="32"/>
       <c r="E219" s="0"/>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D220" s="31"/>
+      <c r="D220" s="32"/>
       <c r="E220" s="0"/>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7528,11 +8803,11 @@
       <c r="E229" s="0"/>
     </row>
     <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D230" s="31"/>
+      <c r="D230" s="32"/>
       <c r="E230" s="0"/>
     </row>
     <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D231" s="31"/>
+      <c r="D231" s="32"/>
       <c r="E231" s="0"/>
     </row>
   </sheetData>
@@ -7559,54 +8834,54 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="33" t="s">
         <v>623</v>
       </c>
-      <c r="B1" s="32"/>
+      <c r="B1" s="33"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="32"/>
-      <c r="B2" s="32"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="32"/>
-      <c r="B3" s="32"/>
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="32"/>
-      <c r="B4" s="32"/>
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="32"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
+      <c r="A12" s="33"/>
+      <c r="B12" s="33"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5"/>

--- a/OffSeason.xlsx
+++ b/OffSeason.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Rosters" sheetId="1" state="visible" r:id="rId2"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="628">
   <si>
     <t xml:space="preserve">No Chubb – John Olson</t>
   </si>
@@ -557,129 +557,155 @@
     <t xml:space="preserve">Will Anderson</t>
   </si>
   <si>
+    <t xml:space="preserve">2025 3 3.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fred Warner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carl Granderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micah McFadden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas Turner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noah Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zack Baun</t>
+  </si>
+  <si>
     <t xml:space="preserve">2025 3 3.09</t>
   </si>
   <si>
-    <t xml:space="preserve">Fred Warner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carl Granderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Micah McFadden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dallas Turner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noah Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zack Baun</t>
+    <t xml:space="preserve">Kaden Ellis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danielle Hunter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lavonte David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A’Shawn Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roquan Smith</t>
   </si>
   <si>
     <t xml:space="preserve">2025 3 3.12</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaden Ellis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danielle Hunter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lavonte David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A’Shawn Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roquan Smith</t>
+    <t xml:space="preserve">2025 1 1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calijah Kancey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alex Anzalone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.09</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">End 26</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">th</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Henry To’oTo’o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ernest Jones</t>
   </si>
   <si>
     <t xml:space="preserve">2025 4 4.12</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 1 1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calijah Kancey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alex Anzalone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henry To’oTo’o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ernest Jones</t>
+    <t xml:space="preserve">2025 2 2.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quay Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quintin Lake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Pace Jr.</t>
   </si>
   <si>
     <t xml:space="preserve">2025 4 4.05</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 2 2.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quay Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quintin Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivan Pace Jr.</t>
+    <t xml:space="preserve">2025 3 3.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foyesade Oluokun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 2 2.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Colson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 1 1.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 5 5.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 4 4.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Logan Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 3 3.08</t>
   </si>
   <si>
     <t xml:space="preserve">2025 4 4.06</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 3.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Foyesade Oluokun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 2 2.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Colson</t>
+    <t xml:space="preserve">Taysom Hill (QB/TE</t>
   </si>
   <si>
     <t xml:space="preserve">2025 1 1.11</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 5 5.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 4 4.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logan Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 3 3.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taysom Hill (QB/TE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025 1 1.07</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025 5 5.12</t>
   </si>
   <si>
@@ -704,6 +730,9 @@
     <t xml:space="preserve">Raheem Mostert</t>
   </si>
   <si>
+    <t xml:space="preserve">issue keepers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trey Sermon</t>
   </si>
   <si>
@@ -1757,9 +1786,6 @@
     <t xml:space="preserve">2026 4 CJ Perry</t>
   </si>
   <si>
-    <t xml:space="preserve">2025 3 3.07</t>
-  </si>
-  <si>
     <t xml:space="preserve">2026 2 Vanja</t>
   </si>
   <si>
@@ -1827,6 +1853,12 @@
   </si>
   <si>
     <t xml:space="preserve">2026 5 CJ Perry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 6.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025 7.3</t>
   </si>
   <si>
     <t xml:space="preserve">2025 picks</t>
@@ -1907,7 +1939,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1942,6 +1974,14 @@
       <b val="true"/>
       <i val="true"/>
       <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -2132,7 +2172,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
@@ -2189,12 +2229,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2205,11 +2245,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2217,7 +2257,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2265,11 +2305,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3666,7 +3706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="n">
         <v>26</v>
       </c>
@@ -3706,8 +3746,11 @@
       <c r="W27" s="5" t="s">
         <v>195</v>
       </c>
+      <c r="X27" s="0" t="s">
+        <v>196</v>
+      </c>
       <c r="AB27" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3716,19 +3759,19 @@
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E28" s="0" t="n">
         <v>27</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I28" s="0" t="n">
         <v>27</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M28" s="0" t="n">
         <v>27</v>
@@ -3737,22 +3780,22 @@
         <v>148</v>
       </c>
       <c r="O28" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q28" s="0" t="n">
         <v>27</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U28" s="0" t="n">
         <v>27</v>
       </c>
       <c r="W28" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AB28" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3761,41 +3804,41 @@
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E29" s="0" t="n">
         <v>28</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I29" s="0" t="n">
         <v>28</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M29" s="0" t="n">
         <v>28</v>
       </c>
       <c r="N29" s="11"/>
       <c r="O29" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q29" s="0" t="n">
         <v>28</v>
       </c>
       <c r="S29" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U29" s="0" t="n">
         <v>28</v>
       </c>
       <c r="W29" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AB29" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3803,41 +3846,41 @@
         <v>29</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E30" s="0" t="n">
         <v>29</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I30" s="0" t="n">
         <v>29</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M30" s="0" t="n">
         <v>29</v>
       </c>
       <c r="N30" s="11"/>
       <c r="O30" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q30" s="0" t="n">
         <v>29</v>
       </c>
       <c r="S30" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U30" s="0" t="n">
         <v>29</v>
       </c>
       <c r="W30" s="0" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="AB30" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3845,139 +3888,142 @@
         <v>30</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E31" s="0" t="n">
         <v>30</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I31" s="0" t="n">
         <v>30</v>
       </c>
       <c r="K31" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M31" s="0" t="n">
         <v>30</v>
       </c>
       <c r="N31" s="11"/>
       <c r="O31" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q31" s="0" t="n">
         <v>30</v>
       </c>
       <c r="S31" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="U31" s="0" t="n">
         <v>30</v>
       </c>
       <c r="W31" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AB31" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB32" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB33" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W34" s="13" t="s">
+        <v>228</v>
+      </c>
       <c r="AB34" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB35" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB36" s="5" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB37" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S38" s="5"/>
       <c r="AB38" s="5" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB39" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB40" s="0" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB41" s="12" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB42" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="13"/>
-      <c r="H43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="H43" s="14"/>
       <c r="AB43" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="13"/>
+      <c r="B44" s="14"/>
       <c r="AB44" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G45" s="1"/>
       <c r="J45" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K45" s="1"/>
       <c r="N45" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="O45" s="1"/>
       <c r="R45" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="S45" s="1"/>
       <c r="V45" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="W45" s="1"/>
       <c r="AB45" s="5" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3988,7 +4034,7 @@
         <v>7</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E46" s="0" t="n">
         <v>1</v>
@@ -3997,7 +4043,7 @@
         <v>7</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I46" s="0" t="n">
         <v>1</v>
@@ -4006,7 +4052,7 @@
         <v>7</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="M46" s="0" t="n">
         <v>1</v>
@@ -4015,7 +4061,7 @@
         <v>7</v>
       </c>
       <c r="O46" s="5" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q46" s="0" t="n">
         <v>1</v>
@@ -4024,7 +4070,7 @@
         <v>7</v>
       </c>
       <c r="S46" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="U46" s="0" t="n">
         <v>1</v>
@@ -4033,10 +4079,10 @@
         <v>7</v>
       </c>
       <c r="W46" s="5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AB46" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4045,45 +4091,45 @@
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="5" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E47" s="0" t="n">
         <v>2</v>
       </c>
       <c r="F47" s="4"/>
       <c r="G47" s="5" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="I47" s="0" t="n">
         <v>2</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="5" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="M47" s="0" t="n">
         <v>2</v>
       </c>
       <c r="N47" s="4"/>
       <c r="O47" s="5" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q47" s="0" t="n">
         <v>2</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="U47" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="V47" s="14"/>
+      <c r="V47" s="13"/>
       <c r="W47" s="5" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AB47" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4092,21 +4138,21 @@
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E48" s="0" t="n">
         <v>3</v>
       </c>
       <c r="F48" s="4"/>
       <c r="G48" s="5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="I48" s="0" t="n">
         <v>3</v>
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="5" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M48" s="0" t="n">
         <v>3</v>
@@ -4115,14 +4161,14 @@
         <v>22</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q48" s="0" t="n">
         <v>3</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="5" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="U48" s="0" t="n">
         <v>3</v>
@@ -4131,10 +4177,10 @@
         <v>22</v>
       </c>
       <c r="W48" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AB48" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4145,7 +4191,7 @@
         <v>22</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E49" s="0" t="n">
         <v>4</v>
@@ -4154,7 +4200,7 @@
         <v>22</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I49" s="0" t="n">
         <v>4</v>
@@ -4163,31 +4209,31 @@
         <v>22</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="M49" s="0" t="n">
         <v>4</v>
       </c>
       <c r="N49" s="6"/>
       <c r="O49" s="5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q49" s="0" t="n">
         <v>4</v>
       </c>
       <c r="R49" s="4"/>
       <c r="S49" s="0" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="U49" s="0" t="n">
         <v>4</v>
       </c>
       <c r="V49" s="6"/>
       <c r="W49" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="AB49" s="5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4196,28 +4242,28 @@
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E50" s="0" t="n">
         <v>5</v>
       </c>
       <c r="F50" s="6"/>
       <c r="G50" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="I50" s="0" t="n">
         <v>5</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M50" s="0" t="n">
         <v>5</v>
       </c>
       <c r="N50" s="6"/>
       <c r="O50" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q50" s="0" t="n">
         <v>5</v>
@@ -4226,17 +4272,17 @@
         <v>22</v>
       </c>
       <c r="S50" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="U50" s="0" t="n">
         <v>5</v>
       </c>
       <c r="V50" s="6"/>
       <c r="W50" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AB50" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4245,35 +4291,35 @@
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="0" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E51" s="0" t="n">
         <v>6</v>
       </c>
       <c r="F51" s="6"/>
       <c r="G51" s="5" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I51" s="0" t="n">
         <v>6</v>
       </c>
       <c r="J51" s="6"/>
       <c r="K51" s="5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="M51" s="0" t="n">
         <v>6</v>
       </c>
       <c r="N51" s="6"/>
       <c r="O51" s="5" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q51" s="0" t="n">
         <v>6</v>
       </c>
       <c r="R51" s="6"/>
       <c r="S51" s="5" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="U51" s="0" t="n">
         <v>6</v>
@@ -4282,10 +4328,10 @@
         <v>45</v>
       </c>
       <c r="W51" s="5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AB51" s="5" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4294,45 +4340,45 @@
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E52" s="0" t="n">
         <v>7</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I52" s="0" t="n">
         <v>7</v>
       </c>
       <c r="J52" s="6"/>
       <c r="K52" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="M52" s="0" t="n">
         <v>7</v>
       </c>
       <c r="N52" s="6"/>
       <c r="O52" s="5" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q52" s="0" t="n">
         <v>7</v>
       </c>
       <c r="R52" s="6"/>
       <c r="S52" s="5" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="U52" s="0" t="n">
         <v>7</v>
       </c>
       <c r="V52" s="7"/>
       <c r="W52" s="5" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AB52" s="0" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4341,14 +4387,14 @@
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="5" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E53" s="0" t="n">
         <v>8</v>
       </c>
       <c r="F53" s="6"/>
       <c r="G53" s="0" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="I53" s="0" t="n">
         <v>8</v>
@@ -4357,7 +4403,7 @@
         <v>45</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M53" s="0" t="n">
         <v>8</v>
@@ -4366,24 +4412,24 @@
         <v>45</v>
       </c>
       <c r="O53" s="5" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q53" s="0" t="n">
         <v>8</v>
       </c>
       <c r="R53" s="6"/>
       <c r="S53" s="5" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="U53" s="0" t="n">
         <v>8</v>
       </c>
       <c r="V53" s="7"/>
       <c r="W53" s="5" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AB53" s="0" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4394,28 +4440,28 @@
         <v>45</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="E54" s="0" t="n">
         <v>9</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="5" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I54" s="0" t="n">
         <v>9</v>
       </c>
       <c r="J54" s="7"/>
       <c r="K54" s="5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M54" s="0" t="n">
         <v>9</v>
       </c>
       <c r="N54" s="7"/>
       <c r="O54" s="5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q54" s="0" t="n">
         <v>9</v>
@@ -4424,17 +4470,17 @@
         <v>45</v>
       </c>
       <c r="S54" s="5" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="U54" s="0" t="n">
         <v>9</v>
       </c>
       <c r="V54" s="7"/>
       <c r="W54" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AB54" s="0" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4443,7 +4489,7 @@
       </c>
       <c r="B55" s="7"/>
       <c r="C55" s="5" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E55" s="0" t="n">
         <v>10</v>
@@ -4452,38 +4498,38 @@
         <v>45</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="I55" s="0" t="n">
         <v>10</v>
       </c>
       <c r="J55" s="7"/>
       <c r="K55" s="5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="M55" s="0" t="n">
         <v>10</v>
       </c>
       <c r="N55" s="7"/>
       <c r="O55" s="5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q55" s="0" t="n">
         <v>10</v>
       </c>
       <c r="R55" s="7"/>
       <c r="S55" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="U55" s="0" t="n">
         <v>10</v>
       </c>
       <c r="V55" s="7"/>
       <c r="W55" s="5" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AB55" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4492,45 +4538,45 @@
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E56" s="0" t="n">
         <v>11</v>
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="5" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="I56" s="0" t="n">
         <v>11</v>
       </c>
       <c r="J56" s="7"/>
       <c r="K56" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="M56" s="0" t="n">
         <v>11</v>
       </c>
       <c r="N56" s="7"/>
       <c r="O56" s="5" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q56" s="0" t="n">
         <v>11</v>
       </c>
       <c r="R56" s="7"/>
       <c r="S56" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="U56" s="0" t="n">
         <v>11</v>
       </c>
       <c r="V56" s="7"/>
       <c r="W56" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AB56" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4539,14 +4585,14 @@
       </c>
       <c r="B57" s="7"/>
       <c r="C57" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E57" s="0" t="n">
         <v>12</v>
       </c>
       <c r="F57" s="7"/>
       <c r="G57" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="I57" s="0" t="n">
         <v>12</v>
@@ -4555,7 +4601,7 @@
         <v>89</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="M57" s="0" t="n">
         <v>12</v>
@@ -4564,24 +4610,24 @@
         <v>89</v>
       </c>
       <c r="O57" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q57" s="0" t="n">
         <v>12</v>
       </c>
       <c r="R57" s="7"/>
       <c r="S57" s="5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="U57" s="0" t="n">
         <v>12</v>
       </c>
       <c r="V57" s="7"/>
       <c r="W57" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AB57" s="5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4590,14 +4636,14 @@
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="5" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E58" s="0" t="n">
         <v>13</v>
       </c>
       <c r="F58" s="7"/>
       <c r="G58" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I58" s="0" t="n">
         <v>13</v>
@@ -4606,31 +4652,31 @@
         <v>111</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M58" s="0" t="n">
         <v>13</v>
       </c>
       <c r="N58" s="8"/>
       <c r="O58" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q58" s="0" t="n">
         <v>13</v>
       </c>
       <c r="R58" s="7"/>
       <c r="S58" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="U58" s="0" t="n">
         <v>13</v>
       </c>
       <c r="V58" s="7"/>
       <c r="W58" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AB58" s="5" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4639,21 +4685,21 @@
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E59" s="0" t="n">
         <v>14</v>
       </c>
       <c r="F59" s="7"/>
       <c r="G59" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="I59" s="0" t="n">
         <v>14</v>
       </c>
       <c r="J59" s="9"/>
       <c r="K59" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M59" s="0" t="n">
         <v>14</v>
@@ -4662,14 +4708,14 @@
         <v>111</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q59" s="0" t="n">
         <v>14</v>
       </c>
       <c r="R59" s="7"/>
       <c r="S59" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="U59" s="0" t="n">
         <v>14</v>
@@ -4678,10 +4724,10 @@
         <v>89</v>
       </c>
       <c r="W59" s="0" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AB59" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4690,28 +4736,28 @@
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E60" s="0" t="n">
         <v>15</v>
       </c>
       <c r="F60" s="7"/>
       <c r="G60" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="I60" s="0" t="n">
         <v>15</v>
       </c>
       <c r="J60" s="9"/>
       <c r="K60" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M60" s="0" t="n">
         <v>15</v>
       </c>
       <c r="N60" s="9"/>
       <c r="O60" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q60" s="0" t="n">
         <v>15</v>
@@ -4720,17 +4766,17 @@
         <v>89</v>
       </c>
       <c r="S60" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="U60" s="0" t="n">
         <v>15</v>
       </c>
       <c r="V60" s="8"/>
       <c r="W60" s="0" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AB60" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4741,14 +4787,14 @@
         <v>89</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="E61" s="0" t="n">
         <v>16</v>
       </c>
       <c r="F61" s="7"/>
       <c r="G61" s="0" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="I61" s="0" t="n">
         <v>16</v>
@@ -4757,7 +4803,7 @@
         <v>126</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="M61" s="0" t="n">
         <v>16</v>
@@ -4766,24 +4812,24 @@
         <v>126</v>
       </c>
       <c r="O61" s="0" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q61" s="0" t="n">
         <v>16</v>
       </c>
       <c r="R61" s="8"/>
       <c r="S61" s="5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="U61" s="0" t="n">
         <v>16</v>
       </c>
       <c r="V61" s="8"/>
       <c r="W61" s="0" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AB61" s="5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4792,35 +4838,35 @@
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E62" s="0" t="n">
         <v>17</v>
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="0" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="I62" s="0" t="n">
         <v>17</v>
       </c>
       <c r="J62" s="10"/>
       <c r="K62" s="5" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="M62" s="0" t="n">
         <v>17</v>
       </c>
       <c r="N62" s="10"/>
       <c r="O62" s="0" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q62" s="0" t="n">
         <v>17</v>
       </c>
       <c r="R62" s="8"/>
       <c r="S62" s="5" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="U62" s="0" t="n">
         <v>17</v>
@@ -4829,10 +4875,10 @@
         <v>111</v>
       </c>
       <c r="W62" s="0" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AB62" s="5" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4843,28 +4889,28 @@
         <v>111</v>
       </c>
       <c r="C63" s="0" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E63" s="0" t="n">
         <v>18</v>
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="5" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I63" s="0" t="n">
         <v>18</v>
       </c>
       <c r="J63" s="10"/>
       <c r="K63" s="5" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M63" s="0" t="n">
         <v>18</v>
       </c>
       <c r="N63" s="10"/>
       <c r="O63" s="0" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q63" s="0" t="n">
         <v>18</v>
@@ -4873,7 +4919,7 @@
         <v>111</v>
       </c>
       <c r="S63" s="5" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="U63" s="0" t="n">
         <v>18</v>
@@ -4882,10 +4928,10 @@
         <v>126</v>
       </c>
       <c r="W63" s="0" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AB63" s="5" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4894,35 +4940,35 @@
       </c>
       <c r="B64" s="9"/>
       <c r="C64" s="5" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="E64" s="0" t="n">
         <v>19</v>
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="0" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="I64" s="0" t="n">
         <v>19</v>
       </c>
       <c r="J64" s="10"/>
       <c r="K64" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M64" s="0" t="n">
         <v>19</v>
       </c>
       <c r="N64" s="10"/>
       <c r="O64" s="0" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="Q64" s="0" t="n">
         <v>19</v>
       </c>
       <c r="R64" s="9"/>
       <c r="S64" s="5" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="U64" s="0" t="n">
         <v>19</v>
@@ -4931,10 +4977,10 @@
         <v>148</v>
       </c>
       <c r="W64" s="0" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AB64" s="0" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4943,7 +4989,7 @@
       </c>
       <c r="B65" s="9"/>
       <c r="C65" s="0" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="E65" s="0" t="n">
         <v>20</v>
@@ -4952,14 +4998,14 @@
         <v>89</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I65" s="0" t="n">
         <v>20</v>
       </c>
       <c r="J65" s="10"/>
       <c r="K65" s="5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M65" s="0" t="n">
         <v>20</v>
@@ -4968,7 +5014,7 @@
         <v>148</v>
       </c>
       <c r="O65" s="0" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="Q65" s="0" t="n">
         <v>20</v>
@@ -4977,17 +5023,17 @@
         <v>126</v>
       </c>
       <c r="S65" s="0" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="U65" s="0" t="n">
         <v>20</v>
       </c>
       <c r="V65" s="11"/>
       <c r="W65" s="0" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AB65" s="5" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4998,44 +5044,44 @@
         <v>126</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E66" s="0" t="n">
         <v>21</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="I66" s="0" t="n">
         <v>21</v>
       </c>
       <c r="J66" s="10"/>
       <c r="K66" s="5" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M66" s="0" t="n">
         <v>21</v>
       </c>
       <c r="N66" s="11"/>
       <c r="O66" s="0" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q66" s="0" t="n">
         <v>21</v>
       </c>
       <c r="R66" s="10"/>
       <c r="S66" s="0" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="U66" s="0" t="n">
         <v>21</v>
       </c>
       <c r="W66" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AB66" s="0" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5044,44 +5090,44 @@
       </c>
       <c r="B67" s="10"/>
       <c r="C67" s="0" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E67" s="0" t="n">
         <v>22</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="0" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="I67" s="0" t="n">
         <v>22</v>
       </c>
       <c r="J67" s="10"/>
       <c r="K67" s="0" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M67" s="0" t="n">
         <v>22</v>
       </c>
       <c r="N67" s="11"/>
       <c r="O67" s="0" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q67" s="0" t="n">
         <v>22</v>
       </c>
       <c r="R67" s="10"/>
       <c r="S67" s="0" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="U67" s="0" t="n">
         <v>22</v>
       </c>
       <c r="W67" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AB67" s="0" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5090,7 +5136,7 @@
       </c>
       <c r="B68" s="10"/>
       <c r="C68" s="0" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E68" s="0" t="n">
         <v>23</v>
@@ -5099,7 +5145,7 @@
         <v>111</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="I68" s="0" t="n">
         <v>23</v>
@@ -5108,14 +5154,14 @@
         <v>148</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M68" s="0" t="n">
         <v>23</v>
       </c>
       <c r="N68" s="11"/>
       <c r="O68" s="0" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="Q68" s="0" t="n">
         <v>23</v>
@@ -5124,16 +5170,16 @@
         <v>148</v>
       </c>
       <c r="S68" s="0" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="U68" s="0" t="n">
         <v>23</v>
       </c>
       <c r="W68" s="0" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AB68" s="5" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5144,43 +5190,43 @@
         <v>148</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E69" s="0" t="n">
         <v>24</v>
       </c>
       <c r="F69" s="9"/>
       <c r="G69" s="5" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="I69" s="0" t="n">
         <v>24</v>
       </c>
       <c r="J69" s="11"/>
       <c r="K69" s="5" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M69" s="0" t="n">
         <v>24</v>
       </c>
       <c r="O69" s="5" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="Q69" s="0" t="n">
         <v>24</v>
       </c>
       <c r="R69" s="11"/>
       <c r="S69" s="0" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="U69" s="0" t="n">
         <v>24</v>
       </c>
       <c r="W69" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AB69" s="5" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5189,43 +5235,43 @@
       </c>
       <c r="B70" s="15"/>
       <c r="C70" s="0" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E70" s="0" t="n">
         <v>25</v>
       </c>
       <c r="F70" s="9"/>
       <c r="G70" s="5" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="I70" s="0" t="n">
         <v>25</v>
       </c>
       <c r="J70" s="11"/>
       <c r="K70" s="0" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="M70" s="0" t="n">
         <v>25</v>
       </c>
       <c r="O70" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="Q70" s="0" t="n">
         <v>25</v>
       </c>
       <c r="R70" s="11"/>
       <c r="S70" s="0" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="U70" s="0" t="n">
         <v>25</v>
       </c>
       <c r="W70" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AB70" s="5" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5234,7 +5280,7 @@
       </c>
       <c r="B71" s="15"/>
       <c r="C71" s="0" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E71" s="0" t="n">
         <v>26</v>
@@ -5243,34 +5289,34 @@
         <v>126</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="I71" s="0" t="n">
         <v>26</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M71" s="0" t="n">
         <v>26</v>
       </c>
       <c r="O71" s="0" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q71" s="0" t="n">
         <v>26</v>
       </c>
       <c r="S71" s="5" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="U71" s="0" t="n">
         <v>26</v>
       </c>
       <c r="W71" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AB71" s="0" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5279,41 +5325,41 @@
       </c>
       <c r="B72" s="15"/>
       <c r="C72" s="5" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E72" s="0" t="n">
         <v>27</v>
       </c>
       <c r="F72" s="10"/>
       <c r="G72" s="0" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="I72" s="0" t="n">
         <v>27</v>
       </c>
       <c r="K72" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M72" s="0" t="n">
         <v>27</v>
       </c>
       <c r="O72" s="0" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="Q72" s="0" t="n">
         <v>27</v>
       </c>
       <c r="S72" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="U72" s="0" t="n">
         <v>27</v>
       </c>
       <c r="W72" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AB72" s="5" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5321,41 +5367,41 @@
         <v>28</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E73" s="0" t="n">
         <v>28</v>
       </c>
       <c r="F73" s="10"/>
       <c r="G73" s="0" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="I73" s="0" t="n">
         <v>28</v>
       </c>
       <c r="K73" s="0" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M73" s="0" t="n">
         <v>28</v>
       </c>
       <c r="O73" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="Q73" s="0" t="n">
         <v>28</v>
       </c>
       <c r="S73" s="0" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="U73" s="0" t="n">
         <v>28</v>
       </c>
       <c r="W73" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AB73" s="0" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5363,7 +5409,7 @@
         <v>29</v>
       </c>
       <c r="C74" s="0" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E74" s="0" t="n">
         <v>29</v>
@@ -5372,13 +5418,13 @@
         <v>148</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="I74" s="0" t="n">
         <v>29</v>
       </c>
       <c r="K74" s="0" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M74" s="0" t="n">
         <v>29</v>
@@ -5390,16 +5436,16 @@
         <v>29</v>
       </c>
       <c r="S74" s="0" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="U74" s="0" t="n">
         <v>29</v>
       </c>
       <c r="W74" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AB74" s="0" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5407,20 +5453,20 @@
         <v>30</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E75" s="0" t="n">
         <v>30</v>
       </c>
       <c r="F75" s="11"/>
       <c r="G75" s="0" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="I75" s="0" t="n">
         <v>30</v>
       </c>
       <c r="K75" s="0" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M75" s="0" t="n">
         <v>30</v>
@@ -5432,237 +5478,237 @@
         <v>30</v>
       </c>
       <c r="S75" s="0" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="U75" s="0" t="n">
         <v>30</v>
       </c>
       <c r="W75" s="0" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AB75" s="5" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB76" s="0" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB77" s="5" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB78" s="0" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB79" s="0" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB80" s="0" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H81" s="13"/>
+      <c r="H81" s="14"/>
       <c r="AB81" s="0" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB82" s="0" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB83" s="5" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB84" s="5" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB85" s="5" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB86" s="0" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB87" s="5" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB88" s="5" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB89" s="5" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB90" s="5" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB91" s="5" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB92" s="5" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB93" s="5" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB94" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB95" s="0" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB96" s="0" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB97" s="5" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB98" s="5" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB99" s="5" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB100" s="5" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB101" s="5" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB102" s="5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB103" s="5" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB104" s="5" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB105" s="0" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB106" s="0" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB107" s="0" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB108" s="0" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB109" s="0" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB110" s="0" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB111" s="0" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB112" s="0" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB113" s="0" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB114" s="0" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB115" s="0" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB116" s="0" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB117" s="5" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB118" s="0" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AB119" s="0" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -5727,115 +5773,115 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5897,233 +5943,233 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E1" s="1"/>
       <c r="F1" s="19"/>
       <c r="G1" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H1" s="1"/>
       <c r="J1" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="19"/>
       <c r="M1" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="N1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="Q1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D2" s="0" t="s">
         <v>177</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>192</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="J2" s="0" t="s">
-        <v>212</v>
+        <v>533</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>213</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="P2" s="5" t="s">
         <v>188</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="BG2" s="0"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D3" s="0" t="s">
         <v>184</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="M3" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N3" s="0" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="P3" s="5" t="s">
         <v>195</v>
       </c>
       <c r="Q3" s="0" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="BG3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="0" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D4" s="0" t="s">
         <v>191</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M4" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N4" s="0" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q4" s="0" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="BG4" s="0"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M5" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="N5" s="0" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="P5" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q5" s="0" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="BG5" s="0"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="M6" s="0" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="N6" s="0" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="P6" s="0" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="Q6" s="0" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="BG6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P7" s="0" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="BG7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="P8" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BG8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="P9" s="0" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="BG9" s="0"/>
     </row>
@@ -6162,228 +6208,230 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B21" s="1"/>
       <c r="D21" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="19"/>
       <c r="G21" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="H21" s="1"/>
       <c r="J21" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="19"/>
       <c r="M21" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N21" s="1"/>
       <c r="P21" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="Q21" s="1"/>
       <c r="BG21" s="0"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="P22" s="5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="Q22" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="BG22" s="0"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>576</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="M23" s="0" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N23" s="0" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P23" s="0" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q23" s="0" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="BG23" s="0"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>585</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>586</v>
+      </c>
+      <c r="G24" s="0" t="s">
+        <v>438</v>
+      </c>
+      <c r="H24" s="0" t="s">
+        <v>587</v>
+      </c>
+      <c r="J24" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="K24" s="0" t="s">
+        <v>588</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="N24" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="P24" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="Q24" s="0" t="s">
+        <v>590</v>
+      </c>
+      <c r="BG24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>592</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="G25" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="H25" s="0" t="s">
+        <v>594</v>
+      </c>
+      <c r="J25" s="0" t="s">
+        <v>432</v>
+      </c>
+      <c r="K25" s="0" t="s">
+        <v>595</v>
+      </c>
+      <c r="M25" s="0" t="s">
         <v>446</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>583</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>584</v>
-      </c>
-      <c r="G24" s="0" t="s">
-        <v>435</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>585</v>
-      </c>
-      <c r="J24" s="0" t="s">
-        <v>422</v>
-      </c>
-      <c r="K24" s="0" t="s">
-        <v>586</v>
-      </c>
-      <c r="M24" s="0" t="s">
-        <v>437</v>
-      </c>
-      <c r="N24" s="0" t="s">
-        <v>587</v>
-      </c>
-      <c r="P24" s="0" t="s">
-        <v>403</v>
-      </c>
-      <c r="Q24" s="0" t="s">
-        <v>588</v>
-      </c>
-      <c r="BG24" s="0"/>
-    </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>589</v>
-      </c>
-      <c r="B25" s="0" t="s">
-        <v>590</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>591</v>
-      </c>
-      <c r="G25" s="0" t="s">
-        <v>442</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>592</v>
-      </c>
-      <c r="J25" s="0" t="s">
-        <v>429</v>
-      </c>
-      <c r="K25" s="0" t="s">
-        <v>593</v>
-      </c>
-      <c r="M25" s="0" t="s">
-        <v>443</v>
-      </c>
       <c r="N25" s="0" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P25" s="0" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="BG25" s="0"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>595</v>
+      <c r="A26" s="20" t="s">
+        <v>597</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M26" s="0" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N26" s="0" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="P26" s="0" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="Q26" s="0" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="BG26" s="0"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="5"/>
       <c r="G27" s="5"/>
-      <c r="J27" s="5"/>
+      <c r="J27" s="0" t="s">
+        <v>603</v>
+      </c>
       <c r="M27" s="5"/>
       <c r="P27" s="0" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="BG27" s="0"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G28" s="5"/>
+      <c r="J28" s="0" t="s">
+        <v>604</v>
+      </c>
       <c r="M28" s="5"/>
       <c r="P28" s="0" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="BG28" s="0"/>
     </row>
@@ -6391,7 +6439,7 @@
       <c r="G29" s="20"/>
       <c r="M29" s="5"/>
       <c r="P29" s="0" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="BG29" s="0"/>
     </row>
@@ -6399,14 +6447,14 @@
       <c r="G30" s="20"/>
       <c r="M30" s="5"/>
       <c r="P30" s="0" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="BG30" s="0"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G31" s="20"/>
       <c r="P31" s="0" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="BG31" s="0"/>
     </row>
@@ -6429,7 +6477,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="BG35" s="0"/>
       <c r="BH35" s="0"/>
@@ -6441,7 +6489,7 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="BG36" s="0"/>
       <c r="BH36" s="0"/>
@@ -6453,13 +6501,13 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E37" s="0" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="F37" s="0" t="n">
         <v>1.01</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="BG37" s="0"/>
       <c r="BH37" s="0"/>
@@ -6474,7 +6522,7 @@
         <v>1.02</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="BG38" s="0"/>
       <c r="BH38" s="0"/>
@@ -6489,7 +6537,7 @@
         <v>1.03</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="BG39" s="0"/>
       <c r="BH39" s="0"/>
@@ -6504,7 +6552,7 @@
         <v>1.04</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="BG40" s="0"/>
       <c r="BH40" s="0"/>
@@ -6519,7 +6567,7 @@
         <v>1.05</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="BG41" s="0"/>
       <c r="BH41" s="0"/>
@@ -6534,7 +6582,7 @@
         <v>1.06</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="BG42" s="0"/>
       <c r="BH42" s="0"/>
@@ -6549,7 +6597,7 @@
         <v>1.07</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="BG43" s="0"/>
       <c r="BH43" s="0"/>
@@ -6564,7 +6612,7 @@
         <v>1.08</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="BG44" s="0"/>
       <c r="BH44" s="0"/>
@@ -6579,7 +6627,7 @@
         <v>1.09</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="BG45" s="0"/>
       <c r="BH45" s="0"/>
@@ -6594,7 +6642,7 @@
         <v>1.1</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="BG46" s="0"/>
       <c r="BH46" s="0"/>
@@ -6609,7 +6657,7 @@
         <v>1.11</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="BG47" s="0"/>
       <c r="BH47" s="0"/>
@@ -6624,7 +6672,7 @@
         <v>1.12</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="BG48" s="0"/>
       <c r="BH48" s="0"/>
@@ -6716,6 +6764,12 @@
       <c r="BM57" s="0"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F58" s="0" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G58" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG58" s="0"/>
       <c r="BH58" s="0"/>
       <c r="BI58" s="0"/>
@@ -6725,6 +6779,12 @@
       <c r="BM58" s="0"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F59" s="0" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G59" s="0" t="s">
+        <v>514</v>
+      </c>
       <c r="BG59" s="0"/>
       <c r="BH59" s="0"/>
       <c r="BI59" s="0"/>
@@ -6734,6 +6794,12 @@
       <c r="BM59" s="0"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F60" s="0" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G60" s="0" t="s">
+        <v>608</v>
+      </c>
       <c r="BG60" s="0"/>
       <c r="BH60" s="0"/>
       <c r="BI60" s="0"/>
@@ -6743,6 +6809,12 @@
       <c r="BM60" s="0"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F61" s="0" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G61" s="0" t="s">
+        <v>609</v>
+      </c>
       <c r="BG61" s="0"/>
       <c r="BH61" s="0"/>
       <c r="BI61" s="0"/>
@@ -6752,6 +6824,12 @@
       <c r="BM61" s="0"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F62" s="0" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G62" s="0" t="s">
+        <v>522</v>
+      </c>
       <c r="BG62" s="0"/>
       <c r="BH62" s="0"/>
       <c r="BI62" s="0"/>
@@ -6761,6 +6839,12 @@
       <c r="BM62" s="0"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F63" s="0" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G63" s="0" t="s">
+        <v>610</v>
+      </c>
       <c r="BG63" s="0"/>
       <c r="BH63" s="0"/>
       <c r="BI63" s="0"/>
@@ -6770,6 +6854,12 @@
       <c r="BM63" s="0"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F64" s="0" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G64" s="0" t="s">
+        <v>506</v>
+      </c>
       <c r="BG64" s="0"/>
       <c r="BH64" s="0"/>
       <c r="BI64" s="0"/>
@@ -6779,6 +6869,12 @@
       <c r="BM64" s="0"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F65" s="0" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G65" s="0" t="s">
+        <v>524</v>
+      </c>
       <c r="BG65" s="0"/>
       <c r="BH65" s="0"/>
       <c r="BI65" s="0"/>
@@ -6788,6 +6884,12 @@
       <c r="BM65" s="0"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F66" s="0" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G66" s="0" t="s">
+        <v>522</v>
+      </c>
       <c r="BG66" s="0"/>
       <c r="BH66" s="0"/>
       <c r="BI66" s="0"/>
@@ -6797,6 +6899,12 @@
       <c r="BM66" s="0"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F67" s="21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G67" s="0" t="s">
+        <v>611</v>
+      </c>
       <c r="BG67" s="0"/>
       <c r="BH67" s="0"/>
       <c r="BI67" s="0"/>
@@ -6806,6 +6914,12 @@
       <c r="BM67" s="0"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F68" s="0" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G68" s="0" t="s">
+        <v>506</v>
+      </c>
       <c r="BG68" s="0"/>
       <c r="BH68" s="0"/>
       <c r="BI68" s="0"/>
@@ -6815,6 +6929,12 @@
       <c r="BM68" s="0"/>
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F69" s="0" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G69" s="0" t="s">
+        <v>522</v>
+      </c>
       <c r="BG69" s="0"/>
       <c r="BH69" s="0"/>
       <c r="BI69" s="0"/>
@@ -6824,6 +6944,12 @@
       <c r="BM69" s="0"/>
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F70" s="0" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G70" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG70" s="0"/>
       <c r="BH70" s="0"/>
       <c r="BI70" s="0"/>
@@ -6833,6 +6959,12 @@
       <c r="BM70" s="0"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F71" s="0" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G71" s="0" t="s">
+        <v>514</v>
+      </c>
       <c r="BG71" s="0"/>
       <c r="BH71" s="0"/>
       <c r="BI71" s="0"/>
@@ -6842,6 +6974,12 @@
       <c r="BM71" s="0"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F72" s="0" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G72" s="0" t="s">
+        <v>608</v>
+      </c>
       <c r="BG72" s="0"/>
       <c r="BH72" s="0"/>
       <c r="BI72" s="0"/>
@@ -6851,6 +6989,12 @@
       <c r="BM72" s="0"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F73" s="0" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G73" s="0" t="s">
+        <v>609</v>
+      </c>
       <c r="BG73" s="0"/>
       <c r="BH73" s="0"/>
       <c r="BI73" s="0"/>
@@ -6860,6 +7004,12 @@
       <c r="BM73" s="0"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F74" s="0" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G74" s="0" t="s">
+        <v>610</v>
+      </c>
       <c r="BG74" s="0"/>
       <c r="BH74" s="0"/>
       <c r="BI74" s="0"/>
@@ -6869,6 +7019,12 @@
       <c r="BM74" s="0"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F75" s="0" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G75" s="0" t="s">
+        <v>610</v>
+      </c>
       <c r="BG75" s="0"/>
       <c r="BH75" s="0"/>
       <c r="BI75" s="0"/>
@@ -6878,6 +7034,12 @@
       <c r="BM75" s="0"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F76" s="0" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G76" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG76" s="0"/>
       <c r="BH76" s="0"/>
       <c r="BI76" s="0"/>
@@ -6887,6 +7049,12 @@
       <c r="BM76" s="0"/>
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F77" s="0" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G77" s="0" t="s">
+        <v>524</v>
+      </c>
       <c r="BG77" s="0"/>
       <c r="BH77" s="0"/>
       <c r="BI77" s="0"/>
@@ -6896,6 +7064,12 @@
       <c r="BM77" s="0"/>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F78" s="0" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G78" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG78" s="0"/>
       <c r="BH78" s="0"/>
       <c r="BI78" s="0"/>
@@ -6905,6 +7079,12 @@
       <c r="BM78" s="0"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F79" s="21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G79" s="0" t="s">
+        <v>611</v>
+      </c>
       <c r="BG79" s="0"/>
       <c r="BH79" s="0"/>
       <c r="BI79" s="0"/>
@@ -6914,6 +7094,12 @@
       <c r="BM79" s="0"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F80" s="0" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G80" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG80" s="0"/>
       <c r="BH80" s="0"/>
       <c r="BI80" s="0"/>
@@ -6923,6 +7109,12 @@
       <c r="BM80" s="0"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F81" s="0" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G81" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG81" s="0"/>
       <c r="BH81" s="0"/>
       <c r="BI81" s="0"/>
@@ -6932,6 +7124,12 @@
       <c r="BM81" s="0"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F82" s="0" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="G82" s="0" t="s">
+        <v>514</v>
+      </c>
       <c r="BG82" s="0"/>
       <c r="BH82" s="0"/>
       <c r="BI82" s="0"/>
@@ -6941,6 +7139,12 @@
       <c r="BM82" s="0"/>
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F83" s="0" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="G83" s="0" t="s">
+        <v>608</v>
+      </c>
       <c r="BG83" s="0"/>
       <c r="BH83" s="0"/>
       <c r="BI83" s="0"/>
@@ -6950,6 +7154,12 @@
       <c r="BM83" s="0"/>
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F84" s="0" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G84" s="0" t="s">
+        <v>609</v>
+      </c>
       <c r="BG84" s="0"/>
       <c r="BH84" s="0"/>
       <c r="BI84" s="0"/>
@@ -6959,6 +7169,12 @@
       <c r="BM84" s="0"/>
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F85" s="0" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="G85" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG85" s="0"/>
       <c r="BH85" s="0"/>
       <c r="BI85" s="0"/>
@@ -6968,6 +7184,12 @@
       <c r="BM85" s="0"/>
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F86" s="0" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G86" s="0" t="s">
+        <v>522</v>
+      </c>
       <c r="BG86" s="0"/>
       <c r="BH86" s="0"/>
       <c r="BI86" s="0"/>
@@ -6977,6 +7199,12 @@
       <c r="BM86" s="0"/>
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F87" s="0" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G87" s="0" t="s">
+        <v>520</v>
+      </c>
       <c r="BG87" s="0"/>
       <c r="BH87" s="0"/>
       <c r="BI87" s="0"/>
@@ -6986,6 +7214,12 @@
       <c r="BM87" s="0"/>
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F88" s="0" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="G88" s="0" t="s">
+        <v>524</v>
+      </c>
       <c r="BG88" s="0"/>
       <c r="BH88" s="0"/>
       <c r="BI88" s="0"/>
@@ -6995,6 +7229,12 @@
       <c r="BM88" s="0"/>
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F89" s="0" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="G89" s="0" t="s">
+        <v>520</v>
+      </c>
       <c r="BG89" s="0"/>
       <c r="BH89" s="0"/>
       <c r="BI89" s="0"/>
@@ -7004,6 +7244,12 @@
       <c r="BM89" s="0"/>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F90" s="0" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="G90" s="0" t="s">
+        <v>611</v>
+      </c>
       <c r="BG90" s="0"/>
       <c r="BH90" s="0"/>
       <c r="BI90" s="0"/>
@@ -7013,6 +7259,12 @@
       <c r="BM90" s="0"/>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F91" s="21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G91" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG91" s="0"/>
       <c r="BH91" s="0"/>
       <c r="BI91" s="0"/>
@@ -7022,6 +7274,12 @@
       <c r="BM91" s="0"/>
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F92" s="0" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="G92" s="0" t="s">
+        <v>520</v>
+      </c>
       <c r="BG92" s="0"/>
       <c r="BH92" s="0"/>
       <c r="BI92" s="0"/>
@@ -7031,6 +7289,12 @@
       <c r="BM92" s="0"/>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F93" s="0" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G93" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG93" s="0"/>
       <c r="BH93" s="0"/>
       <c r="BI93" s="0"/>
@@ -7040,6 +7304,12 @@
       <c r="BM93" s="0"/>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F94" s="0" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="G94" s="0" t="s">
+        <v>514</v>
+      </c>
       <c r="BG94" s="0"/>
       <c r="BH94" s="0"/>
       <c r="BI94" s="0"/>
@@ -7049,6 +7319,12 @@
       <c r="BM94" s="0"/>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F95" s="0" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="G95" s="0" t="s">
+        <v>608</v>
+      </c>
       <c r="BG95" s="0"/>
       <c r="BH95" s="0"/>
       <c r="BI95" s="0"/>
@@ -7058,6 +7334,12 @@
       <c r="BM95" s="0"/>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F96" s="0" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G96" s="0" t="s">
+        <v>609</v>
+      </c>
       <c r="BG96" s="0"/>
       <c r="BH96" s="0"/>
       <c r="BI96" s="0"/>
@@ -7067,6 +7349,12 @@
       <c r="BM96" s="0"/>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F97" s="0" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="G97" s="0" t="s">
+        <v>520</v>
+      </c>
       <c r="BG97" s="0"/>
       <c r="BH97" s="0"/>
       <c r="BI97" s="0"/>
@@ -7076,6 +7364,12 @@
       <c r="BM97" s="0"/>
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F98" s="0" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="G98" s="0" t="s">
+        <v>522</v>
+      </c>
       <c r="BG98" s="0"/>
       <c r="BH98" s="0"/>
       <c r="BI98" s="0"/>
@@ -7085,6 +7379,12 @@
       <c r="BM98" s="0"/>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F99" s="0" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="G99" s="0" t="s">
+        <v>522</v>
+      </c>
       <c r="BG99" s="0"/>
       <c r="BH99" s="0"/>
       <c r="BI99" s="0"/>
@@ -7094,6 +7394,12 @@
       <c r="BM99" s="0"/>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F100" s="0" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="G100" s="0" t="s">
+        <v>524</v>
+      </c>
       <c r="BG100" s="0"/>
       <c r="BH100" s="0"/>
       <c r="BI100" s="0"/>
@@ -7103,6 +7409,12 @@
       <c r="BM100" s="0"/>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F101" s="0" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="G101" s="0" t="s">
+        <v>611</v>
+      </c>
       <c r="BG101" s="0"/>
       <c r="BH101" s="0"/>
       <c r="BI101" s="0"/>
@@ -7112,6 +7424,12 @@
       <c r="BM101" s="0"/>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F102" s="0" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="G102" s="0" t="s">
+        <v>520</v>
+      </c>
       <c r="BG102" s="0"/>
       <c r="BH102" s="0"/>
       <c r="BI102" s="0"/>
@@ -7121,6 +7439,12 @@
       <c r="BM102" s="0"/>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F103" s="21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G103" s="0" t="s">
+        <v>571</v>
+      </c>
       <c r="BG103" s="0"/>
       <c r="BH103" s="0"/>
       <c r="BI103" s="0"/>
@@ -7130,6 +7454,12 @@
       <c r="BM103" s="0"/>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F104" s="0" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="G104" s="0" t="s">
+        <v>514</v>
+      </c>
       <c r="BG104" s="0"/>
       <c r="BH104" s="0"/>
       <c r="BI104" s="0"/>
@@ -7139,6 +7469,12 @@
       <c r="BM104" s="0"/>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F105" s="0" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="G105" s="0" t="s">
+        <v>608</v>
+      </c>
       <c r="BG105" s="0"/>
       <c r="BH105" s="0"/>
       <c r="BI105" s="0"/>
@@ -7148,6 +7484,12 @@
       <c r="BM105" s="0"/>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F106" s="0" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="G106" s="0" t="s">
+        <v>609</v>
+      </c>
       <c r="BG106" s="0"/>
       <c r="BH106" s="0"/>
       <c r="BI106" s="0"/>
@@ -7157,6 +7499,12 @@
       <c r="BM106" s="0"/>
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F107" s="0" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="G107" s="0" t="s">
+        <v>611</v>
+      </c>
       <c r="BG107" s="0"/>
       <c r="BH107" s="0"/>
       <c r="BI107" s="0"/>
@@ -7166,6 +7514,12 @@
       <c r="BM107" s="0"/>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F108" s="0" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="G108" s="0" t="s">
+        <v>520</v>
+      </c>
       <c r="BG108" s="0"/>
       <c r="BH108" s="0"/>
       <c r="BI108" s="0"/>
@@ -7175,6 +7529,12 @@
       <c r="BM108" s="0"/>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F109" s="0" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="G109" s="0" t="s">
+        <v>608</v>
+      </c>
       <c r="BG109" s="0"/>
       <c r="BH109" s="0"/>
       <c r="BI109" s="0"/>
@@ -7184,6 +7544,12 @@
       <c r="BM109" s="0"/>
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F110" s="0" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="G110" s="0" t="s">
+        <v>608</v>
+      </c>
       <c r="BG110" s="0"/>
       <c r="BH110" s="0"/>
       <c r="BI110" s="0"/>
@@ -7229,6 +7595,7 @@
       <c r="BM114" s="0"/>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F115" s="21"/>
       <c r="BG115" s="0"/>
       <c r="BH115" s="0"/>
       <c r="BI115" s="0"/>
@@ -8304,68 +8671,68 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="23" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B1" s="24" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25"/>
       <c r="B2" s="26" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25"/>
       <c r="B3" s="26" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25"/>
       <c r="B5" s="26" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27"/>
       <c r="B7" s="28" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25"/>
       <c r="B10" s="26" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27"/>
       <c r="B11" s="28" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8374,42 +8741,42 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25"/>
       <c r="B14" s="26" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25"/>
       <c r="B15" s="26" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27"/>
       <c r="B16" s="28" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27"/>
       <c r="B19" s="28" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8418,22 +8785,22 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25"/>
       <c r="B22" s="26" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25"/>
       <c r="B23" s="26" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8442,10 +8809,10 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B25" s="24" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8458,7 +8825,7 @@
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="27"/>
       <c r="B27" s="28" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8467,15 +8834,15 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="23" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="B31" s="29" t="n">
         <v>1.12</v>
@@ -8487,7 +8854,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B33" s="30" t="s">
         <v>90</v>
@@ -8496,27 +8863,27 @@
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="27"/>
       <c r="B34" s="28" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="23" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25"/>
       <c r="B37" s="30" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25"/>
       <c r="B38" s="30" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8525,18 +8892,18 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="E43" s="0"/>
       <c r="F43" s="0"/>
@@ -8544,7 +8911,7 @@
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25"/>
       <c r="B44" s="26" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E44" s="0"/>
       <c r="F44" s="0"/>
@@ -8557,10 +8924,10 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="27" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E46" s="0"/>
       <c r="F46" s="0"/>
@@ -8571,23 +8938,23 @@
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F48" s="0"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25"/>
       <c r="B49" s="26" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25"/>
       <c r="B50" s="26" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8598,10 +8965,10 @@
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="27" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B52" s="28" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D52" s="0"/>
       <c r="E52" s="0"/>
@@ -8615,10 +8982,10 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D54" s="0"/>
       <c r="E54" s="0"/>
@@ -8633,7 +9000,7 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="27" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B56" s="28" t="s">
         <v>121</v>
@@ -8835,7 +9202,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="33" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B1" s="33"/>
     </row>

--- a/OffSeason.xlsx
+++ b/OffSeason.xlsx
@@ -1214,424 +1214,427 @@
     <t xml:space="preserve">Derrick Brown</t>
   </si>
   <si>
+    <t xml:space="preserve">Najee Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nnamdi Madubuike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donovan Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tank Bigsby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacoby Brissett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sean Tucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geno Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquired picks: R20 Pace yourself; R28 Smoking Fat Herbs; R29 Smoking Fat Herbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquired picks: R30 Run it back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No pick: R1, R2, R3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No pick: R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jawhar Jordan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy McNichols</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcus Mariota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerome Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-Puka-Lypse Now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Young Guns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Go Pack Go</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Carter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baker Mayfield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.J. Stroud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trevor Lawrence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sam Darnold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donovan Ezeiruaku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Daniels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brock Purdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bryce Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyler Murray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mac Jones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TreVeyon Henderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Cook III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashton Jeanty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emari Demercado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Conner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Rodriguez Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Javonte Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kyle Monangai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Woody Marks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rachaad White</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyjae Spears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jacory Croskey-Merritt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaden Elliss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rico Dowdle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Robinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaleb Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Sampson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germaine Pratt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chuba Hubbard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhayshul Tuten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathon Brooks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luther Burden III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julian Love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devin Singletary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braelon Allen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeVonta Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keon Coleman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nakobe Dean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Michael Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jameson Williams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jayden Reed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alec Pierce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bam Knight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puka Nacua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tre' Harris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chris Olave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylin Noel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamarri Conner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike Evans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garrett Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian Thomas Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tank Dell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mason Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elic Ayomanor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalen McMillan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marvin Harrison Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chig Okonkwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bobby Okereke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parker Washington</t>
+  </si>
+  <si>
     <t xml:space="preserve">Devaughn Vele</t>
   </si>
   <si>
-    <t xml:space="preserve">Najee Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nnamdi Madubuike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donovan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tank Bigsby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacoby Brissett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sean Tucker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geno Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acquired picks: R20 Pace yourself; R28 Smoking Fat Herbs; R29 Smoking Fat Herbs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acquired picks: R30 Run it back</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No pick: R1, R2, R3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No pick: R2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jawhar Jordan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy McNichols</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcus Mariota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerome Ford</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A-Puka-Lypse Now</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Young Guns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Go Pack Go</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Carter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baker Mayfield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C.J. Stroud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trevor Lawrence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Darnold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Donovan Ezeiruaku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Daniels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brock Purdy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bryce Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyler Murray</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TreVeyon Henderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mac Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashton Jeanty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emari Demercado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Conner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Rodriguez Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Cook III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kyle Monangai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Woody Marks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachaad White</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Javonte Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacory Croskey-Merritt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaden Elliss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rico Dowdle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Robinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyjae Spears</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Sampson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germaine Pratt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chuba Hubbard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bhayshul Tuten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaleb Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luther Burden III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julian Love</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devin Singletary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braelon Allen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathon Brooks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keon Coleman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakobe Dean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Michael Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jameson Williams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DeVonta Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alec Pierce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bam Knight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puka Nacua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tre' Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jayden Reed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylin Noel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamarri Conner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mike Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garrett Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chris Olave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tank Dell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mason Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elic Ayomanor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalen McMillan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian Thomas Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chig Okonkwo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bobby Okereke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parker Washington</t>
+    <t xml:space="preserve">Ricky Pearsall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harold Fannin Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coby Bryant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Metchie III</t>
   </si>
   <si>
     <t xml:space="preserve">Michael Mayer</t>
   </si>
   <si>
-    <t xml:space="preserve">Marvin Harrison Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harold Fannin Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coby Bryant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John Metchie III</t>
+    <t xml:space="preserve">Isaiah Bond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xavier Watts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jake Tonges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tory Horton</t>
   </si>
   <si>
     <t xml:space="preserve">Kyle Pitts Sr.</t>
   </si>
   <si>
-    <t xml:space="preserve">Ricky Pearsall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xavier Watts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jake Tonges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tory Horton</t>
+    <t xml:space="preserve">Christian Watson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nick Emmanwori</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alohi Gilman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">George Kittle</t>
   </si>
   <si>
     <t xml:space="preserve">Kyle Hamilton</t>
   </si>
   <si>
-    <t xml:space="preserve">Isaiah Bond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nick Emmanwori</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alohi Gilman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">George Kittle</t>
+    <t xml:space="preserve">Brock Bowers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaquan Brisker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaylinn Hawkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AJ Barner</t>
   </si>
   <si>
     <t xml:space="preserve">Talanoa Hufanga</t>
   </si>
   <si>
-    <t xml:space="preserve">Christian Watson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaquan Brisker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaylinn Hawkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AJ Barner</t>
+    <t xml:space="preserve">Travis Kelce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abdul Carter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taysom Hill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juwan Johnson</t>
   </si>
   <si>
     <t xml:space="preserve">Jalen Thompson</t>
   </si>
   <si>
-    <t xml:space="preserve">Brock Bowers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abdul Carter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taysom Hill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juwan Johnson</t>
+    <t xml:space="preserve">Pat Freiermuth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jalon Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kareem Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colby Parkinson</t>
   </si>
   <si>
     <t xml:space="preserve">Chop Robinson</t>
   </si>
   <si>
-    <t xml:space="preserve">Travis Kelce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jalon Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kareem Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colby Parkinson</t>
+    <t xml:space="preserve">Jeremy Chinn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travon Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaydon Blue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paulson Adebo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CB</t>
   </si>
   <si>
     <t xml:space="preserve">Will McDonald IV</t>
   </si>
   <si>
-    <t xml:space="preserve">Pat Freiermuth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Travon Walker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jaydon Blue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paulson Adebo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CB</t>
+    <t xml:space="preserve">Nick Cross</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demetrius Knight Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lavonte David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jonathon Cooper</t>
   </si>
   <si>
     <t xml:space="preserve">George Karlaftis</t>
   </si>
   <si>
-    <t xml:space="preserve">Jeremy Chinn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demetrius Knight Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lavonte David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonathon Cooper</t>
+    <t xml:space="preserve">Tykee Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ed Oliver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew Van Ginkel</t>
   </si>
   <si>
     <t xml:space="preserve">Nick Bolton</t>
   </si>
   <si>
-    <t xml:space="preserve">Nick Cross</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ed Oliver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew Van Ginkel</t>
+    <t xml:space="preserve">Devin Lloyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joey Bosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osa Odighizuwa</t>
   </si>
   <si>
     <t xml:space="preserve">Terrel Bernard</t>
   </si>
   <si>
-    <t xml:space="preserve">Tykee Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joey Bosa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osa Odighizuwa</t>
+    <t xml:space="preserve">Jack Campbell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troy Franklin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SirVocea Dennis</t>
   </si>
   <si>
     <t xml:space="preserve">Azeez Al-Shaair</t>
   </si>
   <si>
-    <t xml:space="preserve">Devin Lloyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troy Franklin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SirVocea Dennis</t>
+    <t xml:space="preserve">Edgerrin Cooper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tyrone Tracy Jr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kobie Turner</t>
   </si>
   <si>
     <t xml:space="preserve">Byron Young</t>
   </si>
   <si>
-    <t xml:space="preserve">Jack Campbell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tyrone Tracy Jr.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kobie Turner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edgerrin Cooper</t>
+    <t xml:space="preserve">Jihaad Campbell</t>
   </si>
   <si>
     <t xml:space="preserve">Quincy Williams</t>
@@ -1640,16 +1643,13 @@
     <t xml:space="preserve">Jonathan Greenard</t>
   </si>
   <si>
-    <t xml:space="preserve">Jihaad Campbell</t>
+    <t xml:space="preserve">Josh Hines-Allen</t>
   </si>
   <si>
     <t xml:space="preserve">Drake Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">Quentin Lake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Josh Hines-Allen</t>
   </si>
   <si>
     <t xml:space="preserve">Aidan Hutchinson</t>
@@ -3070,7 +3070,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.83"/>
@@ -3268,7 +3268,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -3403,7 +3403,7 @@
         <v>3</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>594</v>
@@ -4055,7 +4055,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -4811,7 +4811,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -5511,7 +5511,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -6276,7 +6276,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -7051,7 +7051,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -7800,7 +7800,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -7815,7 +7815,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -7863,7 +7863,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>146</v>
@@ -7875,7 +7875,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>595</v>
@@ -7895,7 +7895,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>595</v>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>163</v>
@@ -7915,7 +7915,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>595</v>
@@ -7935,7 +7935,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>595</v>
@@ -7955,7 +7955,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>595</v>
@@ -7975,7 +7975,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>595</v>
@@ -7995,7 +7995,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>595</v>
@@ -8015,7 +8015,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>595</v>
@@ -8035,7 +8035,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>595</v>
@@ -8055,7 +8055,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>595</v>
@@ -8063,7 +8063,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B15" s="0" t="s">
         <v>45</v>
@@ -8075,7 +8075,7 @@
         <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>595</v>
@@ -8095,7 +8095,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>595</v>
@@ -8115,7 +8115,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>595</v>
@@ -8135,7 +8135,7 @@
         <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>595</v>
@@ -8155,7 +8155,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>595</v>
@@ -8175,7 +8175,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>595</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>142</v>
@@ -8195,7 +8195,7 @@
         <v>17</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>595</v>
@@ -8215,7 +8215,7 @@
         <v>18</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>595</v>
@@ -8235,7 +8235,7 @@
         <v>19</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>595</v>
@@ -8255,7 +8255,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>595</v>
@@ -8275,7 +8275,7 @@
         <v>21</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>595</v>
@@ -8295,7 +8295,7 @@
         <v>22</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>595</v>
@@ -8315,7 +8315,7 @@
         <v>23</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>595</v>
@@ -8335,7 +8335,7 @@
         <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>595</v>
@@ -8355,7 +8355,7 @@
         <v>25</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>595</v>
@@ -8375,7 +8375,7 @@
         <v>26</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>595</v>
@@ -8395,7 +8395,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>595</v>
@@ -8418,7 +8418,7 @@
         <v>28</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>595</v>
@@ -8438,7 +8438,7 @@
         <v>29</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>595</v>
@@ -8458,7 +8458,7 @@
         <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>595</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B35" s="0" t="s">
         <v>142</v>
@@ -8477,7 +8477,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>142</v>
@@ -8488,7 +8488,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B37" s="0" t="s">
         <v>142</v>
@@ -8526,7 +8526,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B40" s="0" t="s">
         <v>68</v>
@@ -8537,7 +8537,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B41" s="0" t="s">
         <v>48</v>
@@ -8578,7 +8578,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -8593,7 +8593,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8641,7 +8641,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>45</v>
@@ -8653,7 +8653,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>595</v>
@@ -8673,7 +8673,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>595</v>
@@ -8693,7 +8693,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>595</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>105</v>
@@ -8713,7 +8713,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>595</v>
@@ -8733,7 +8733,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>595</v>
@@ -8741,7 +8741,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>131</v>
@@ -8753,7 +8753,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>595</v>
@@ -8773,7 +8773,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>595</v>
@@ -8793,7 +8793,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>595</v>
@@ -8813,7 +8813,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>595</v>
@@ -8833,7 +8833,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>595</v>
@@ -8853,7 +8853,7 @@
         <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>595</v>
@@ -8861,7 +8861,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>161</v>
@@ -8873,7 +8873,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>595</v>
@@ -8881,7 +8881,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>82</v>
@@ -8893,7 +8893,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>595</v>
@@ -8913,7 +8913,7 @@
         <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>595</v>
@@ -8921,7 +8921,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>146</v>
@@ -8933,7 +8933,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>595</v>
@@ -8941,7 +8941,7 @@
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>119</v>
@@ -8953,7 +8953,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>595</v>
@@ -8973,7 +8973,7 @@
         <v>17</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>595</v>
@@ -8981,7 +8981,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>108</v>
@@ -8993,7 +8993,7 @@
         <v>18</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>595</v>
@@ -9001,7 +9001,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>97</v>
@@ -9013,7 +9013,7 @@
         <v>19</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>595</v>
@@ -9021,7 +9021,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>68</v>
@@ -9033,7 +9033,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>595</v>
@@ -9041,7 +9041,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>125</v>
@@ -9053,7 +9053,7 @@
         <v>21</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>595</v>
@@ -9061,7 +9061,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>139</v>
@@ -9073,7 +9073,7 @@
         <v>22</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>595</v>
@@ -9081,7 +9081,7 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>155</v>
@@ -9093,7 +9093,7 @@
         <v>23</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>595</v>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>48</v>
@@ -9113,7 +9113,7 @@
         <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>595</v>
@@ -9121,7 +9121,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>119</v>
@@ -9133,7 +9133,7 @@
         <v>25</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>595</v>
@@ -9141,7 +9141,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>102</v>
@@ -9153,7 +9153,7 @@
         <v>26</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>595</v>
@@ -9161,7 +9161,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>102</v>
@@ -9173,7 +9173,7 @@
         <v>27</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>595</v>
@@ -9181,7 +9181,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>45</v>
@@ -9193,7 +9193,7 @@
         <v>28</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>595</v>
@@ -9201,7 +9201,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>97</v>
@@ -9213,7 +9213,7 @@
         <v>29</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>595</v>
@@ -9221,7 +9221,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>90</v>
@@ -9233,7 +9233,7 @@
         <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>595</v>
@@ -9252,7 +9252,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>95</v>
@@ -9279,7 +9279,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>64</v>
@@ -9293,7 +9293,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>139</v>
@@ -9334,7 +9334,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -9349,7 +9349,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -9397,7 +9397,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>175</v>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>125</v>
@@ -9437,7 +9437,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>90</v>
@@ -9449,7 +9449,7 @@
         <v>4</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>595</v>
@@ -9457,7 +9457,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>113</v>
@@ -9469,7 +9469,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>595</v>
@@ -9477,7 +9477,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>74</v>
@@ -9489,7 +9489,7 @@
         <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>595</v>
@@ -9497,7 +9497,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>68</v>
@@ -9517,7 +9517,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>74</v>
@@ -9529,7 +9529,7 @@
         <v>7</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>595</v>
@@ -9537,7 +9537,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>95</v>
@@ -9549,7 +9549,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>595</v>
@@ -9557,7 +9557,7 @@
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B13" s="0" t="s">
         <v>163</v>
@@ -9569,7 +9569,7 @@
         <v>9</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>595</v>
@@ -9577,7 +9577,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B14" s="0" t="s">
         <v>102</v>
@@ -9589,7 +9589,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>595</v>
@@ -9609,7 +9609,7 @@
         <v>11</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>595</v>
@@ -9617,7 +9617,7 @@
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B16" s="0" t="s">
         <v>136</v>
@@ -9629,7 +9629,7 @@
         <v>12</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>595</v>
@@ -9637,7 +9637,7 @@
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B17" s="0" t="s">
         <v>117</v>
@@ -9649,7 +9649,7 @@
         <v>13</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>595</v>
@@ -9657,7 +9657,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B18" s="0" t="s">
         <v>113</v>
@@ -9669,7 +9669,7 @@
         <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>595</v>
@@ -9677,7 +9677,7 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B19" s="0" t="s">
         <v>161</v>
@@ -9689,7 +9689,7 @@
         <v>15</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>595</v>
@@ -9709,7 +9709,7 @@
         <v>16</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>595</v>
@@ -9717,7 +9717,7 @@
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>82</v>
@@ -9729,7 +9729,7 @@
         <v>17</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>595</v>
@@ -9737,7 +9737,7 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>161</v>
@@ -9749,7 +9749,7 @@
         <v>18</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>595</v>
@@ -9757,7 +9757,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>136</v>
@@ -9769,7 +9769,7 @@
         <v>19</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>595</v>
@@ -9777,7 +9777,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>142</v>
@@ -9789,7 +9789,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>595</v>
@@ -9797,7 +9797,7 @@
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>146</v>
@@ -9809,7 +9809,7 @@
         <v>21</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>595</v>
@@ -9817,7 +9817,7 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>175</v>
@@ -9829,7 +9829,7 @@
         <v>22</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>595</v>
@@ -9849,7 +9849,7 @@
         <v>23</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>595</v>
@@ -9869,7 +9869,7 @@
         <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>595</v>
@@ -9877,7 +9877,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>87</v>
@@ -9889,7 +9889,7 @@
         <v>26</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>595</v>
@@ -9897,7 +9897,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>74</v>
@@ -9909,7 +9909,7 @@
         <v>27</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>595</v>
@@ -9917,7 +9917,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B31" s="0" t="s">
         <v>102</v>
@@ -9929,7 +9929,7 @@
         <v>28</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>595</v>
@@ -9937,7 +9937,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B32" s="0" t="s">
         <v>90</v>
@@ -9969,7 +9969,7 @@
         <v>29</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>595</v>
@@ -9977,7 +9977,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B34" s="0" t="s">
         <v>68</v>
@@ -10008,7 +10008,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B36" s="0" t="s">
         <v>131</v>
@@ -10035,7 +10035,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>136</v>
@@ -10046,7 +10046,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="B39" s="0" t="s">
         <v>131</v>
@@ -10098,7 +10098,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -10161,7 +10161,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>84</v>
@@ -10541,7 +10541,7 @@
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>84</v>
@@ -10716,7 +10716,7 @@
         <v>25</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>594</v>
@@ -10724,7 +10724,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B33" s="0" t="s">
         <v>117</v>
@@ -10802,7 +10802,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B38" s="0" t="s">
         <v>93</v>
@@ -10854,7 +10854,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:U134"/>
-  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28.98"/>
@@ -14261,21 +14261,12 @@
       <c r="M80" s="17" t="n">
         <v>5.1</v>
       </c>
-      <c r="S80" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="T80" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="U80" s="10" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="81" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="9"/>
       <c r="L81" s="10"/>
       <c r="S81" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="T81" s="10" t="s">
         <v>44</v>
@@ -14287,7 +14278,7 @@
     <row r="82" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L82" s="8"/>
       <c r="S82" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="T82" s="10" t="s">
         <v>328</v>
@@ -14299,7 +14290,7 @@
     <row r="83" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L83" s="10"/>
       <c r="S83" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="T83" s="10" t="s">
         <v>44</v>
@@ -14311,7 +14302,7 @@
     <row r="84" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L84" s="8"/>
       <c r="S84" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="T84" s="8" t="s">
         <v>44</v>
@@ -14323,7 +14314,7 @@
     <row r="85" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L85" s="10"/>
       <c r="S85" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="T85" s="10" t="s">
         <v>60</v>
@@ -14335,7 +14326,7 @@
     <row r="86" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L86" s="8"/>
       <c r="S86" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="T86" s="10" t="s">
         <v>44</v>
@@ -14347,7 +14338,7 @@
     <row r="87" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L87" s="10"/>
       <c r="S87" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="T87" s="8" t="s">
         <v>60</v>
@@ -14363,13 +14354,13 @@
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
       <c r="E88" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F88" s="13"/>
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
       <c r="I88" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J88" s="13"/>
       <c r="K88" s="13"/>
@@ -14380,7 +14371,7 @@
       <c r="N88" s="14"/>
       <c r="O88" s="14"/>
       <c r="S88" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="T88" s="8" t="s">
         <v>47</v>
@@ -14396,13 +14387,13 @@
       <c r="C89" s="16"/>
       <c r="D89" s="16"/>
       <c r="E89" s="15" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F89" s="15"/>
       <c r="G89" s="15"/>
       <c r="H89" s="15"/>
       <c r="I89" s="15" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J89" s="15"/>
       <c r="K89" s="15"/>
@@ -14415,7 +14406,7 @@
     </row>
     <row r="90" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S90" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="T90" s="10" t="s">
         <v>44</v>
@@ -14426,7 +14417,7 @@
     </row>
     <row r="91" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S91" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="T91" s="10" t="s">
         <v>44</v>
@@ -14437,7 +14428,7 @@
     </row>
     <row r="92" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S92" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="T92" s="10" t="s">
         <v>60</v>
@@ -14448,7 +14439,7 @@
     </row>
     <row r="93" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="S93" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="T93" s="10" t="s">
         <v>44</v>
@@ -14459,18 +14450,18 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
       <c r="E94" s="11" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F94" s="11"/>
       <c r="G94" s="11"/>
       <c r="H94" s="11"/>
       <c r="I94" s="11" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J94" s="11"/>
       <c r="K94" s="11"/>
@@ -14481,7 +14472,7 @@
       <c r="N94" s="11"/>
       <c r="O94" s="11"/>
       <c r="S94" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="T94" s="10" t="s">
         <v>44</v>
@@ -14530,7 +14521,7 @@
         <v>55</v>
       </c>
       <c r="S95" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="T95" s="10" t="s">
         <v>180</v>
@@ -14544,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>60</v>
@@ -14553,7 +14544,7 @@
         <v>146</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F96" s="10" t="s">
         <v>60</v>
@@ -14565,7 +14556,7 @@
         <v>1</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J96" s="10" t="s">
         <v>60</v>
@@ -14577,7 +14568,7 @@
         <v>1</v>
       </c>
       <c r="M96" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N96" s="10" t="s">
         <v>60</v>
@@ -14586,7 +14577,7 @@
         <v>84</v>
       </c>
       <c r="S96" s="7" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="T96" s="8" t="s">
         <v>197</v>
@@ -14600,7 +14591,7 @@
         <v>2</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>60</v>
@@ -14609,7 +14600,7 @@
         <v>142</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>60</v>
@@ -14621,7 +14612,7 @@
         <v>2</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J97" s="8" t="s">
         <v>60</v>
@@ -14633,13 +14624,22 @@
         <v>2</v>
       </c>
       <c r="M97" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="N97" s="8" t="s">
         <v>60</v>
       </c>
       <c r="O97" s="8" t="s">
         <v>93</v>
+      </c>
+      <c r="S97" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="T97" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="U97" s="10" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14667,14 +14667,14 @@
       <c r="H98" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I98" s="9" t="s">
+      <c r="I98" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="J98" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K98" s="10" t="s">
-        <v>161</v>
+      <c r="J98" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K98" s="8" t="s">
+        <v>125</v>
       </c>
       <c r="L98" s="10" t="n">
         <v>3</v>
@@ -14723,14 +14723,14 @@
       <c r="H99" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I99" s="7" t="s">
+      <c r="I99" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="J99" s="8" t="s">
+      <c r="J99" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="K99" s="8" t="s">
-        <v>125</v>
+      <c r="K99" s="10" t="s">
+        <v>90</v>
       </c>
       <c r="L99" s="10" t="n">
         <v>4</v>
@@ -14786,7 +14786,7 @@
         <v>44</v>
       </c>
       <c r="K100" s="10" t="s">
-        <v>90</v>
+        <v>163</v>
       </c>
       <c r="L100" s="8" t="n">
         <v>5</v>
@@ -14835,14 +14835,14 @@
       <c r="H101" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I101" s="9" t="s">
+      <c r="I101" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="J101" s="10" t="s">
+      <c r="J101" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="K101" s="10" t="s">
-        <v>163</v>
+      <c r="K101" s="8" t="s">
+        <v>113</v>
       </c>
       <c r="L101" s="10" t="n">
         <v>6</v>
@@ -14898,7 +14898,7 @@
         <v>44</v>
       </c>
       <c r="K102" s="8" t="s">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="L102" s="10" t="n">
         <v>7</v>
@@ -14951,10 +14951,10 @@
         <v>449</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K103" s="8" t="s">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="L103" s="8" t="n">
         <v>8</v>
@@ -15003,14 +15003,14 @@
       <c r="H104" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="I104" s="7" t="s">
+      <c r="I104" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="J104" s="8" t="s">
+      <c r="J104" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="K104" s="8" t="s">
-        <v>68</v>
+      <c r="K104" s="10" t="s">
+        <v>74</v>
       </c>
       <c r="L104" s="10" t="n">
         <v>9</v>
@@ -15059,14 +15059,14 @@
       <c r="H105" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="I105" s="9" t="s">
+      <c r="I105" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="J105" s="10" t="s">
+      <c r="J105" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="K105" s="10" t="s">
-        <v>74</v>
+      <c r="K105" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="L105" s="10" t="n">
         <v>10</v>
@@ -15115,14 +15115,14 @@
       <c r="H106" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="I106" s="7" t="s">
+      <c r="I106" s="9" t="s">
         <v>464</v>
       </c>
-      <c r="J106" s="8" t="s">
+      <c r="J106" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="K106" s="8" t="s">
-        <v>95</v>
+      <c r="K106" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="L106" s="8" t="n">
         <v>11</v>
@@ -15178,7 +15178,7 @@
         <v>47</v>
       </c>
       <c r="K107" s="10" t="s">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="L107" s="10" t="n">
         <v>12</v>
@@ -15215,26 +15215,26 @@
       <c r="D108" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="E108" s="7" t="s">
+      <c r="E108" s="9" t="s">
         <v>473</v>
       </c>
-      <c r="F108" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G108" s="8" t="s">
-        <v>131</v>
+      <c r="F108" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>95</v>
       </c>
       <c r="H108" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="I108" s="9" t="s">
+      <c r="I108" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="J108" s="10" t="s">
+      <c r="J108" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="K108" s="10" t="s">
-        <v>82</v>
+      <c r="K108" s="8" t="s">
+        <v>161</v>
       </c>
       <c r="L108" s="10" t="n">
         <v>13</v>
@@ -15278,19 +15278,19 @@
         <v>57</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="H109" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="I109" s="7" t="s">
+      <c r="I109" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="J109" s="8" t="s">
+      <c r="J109" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="K109" s="8" t="s">
-        <v>161</v>
+      <c r="K109" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L109" s="8" t="n">
         <v>14</v>
@@ -15331,10 +15331,10 @@
         <v>483</v>
       </c>
       <c r="F110" s="8" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="H110" s="10" t="n">
         <v>15</v>
@@ -15346,7 +15346,7 @@
         <v>47</v>
       </c>
       <c r="K110" s="10" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="L110" s="10" t="n">
         <v>15</v>
@@ -15383,26 +15383,26 @@
       <c r="D111" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E111" s="9" t="s">
+      <c r="E111" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="F111" s="10" t="s">
+      <c r="F111" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G111" s="10" t="s">
-        <v>155</v>
+      <c r="G111" s="8" t="s">
+        <v>139</v>
       </c>
       <c r="H111" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="I111" s="9" t="s">
+      <c r="I111" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="J111" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="K111" s="10" t="s">
-        <v>74</v>
+      <c r="J111" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="K111" s="8" t="s">
+        <v>131</v>
       </c>
       <c r="L111" s="10" t="n">
         <v>16</v>
@@ -15446,7 +15446,7 @@
         <v>52</v>
       </c>
       <c r="G112" s="10" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="H112" s="8" t="n">
         <v>17</v>
@@ -15458,7 +15458,7 @@
         <v>57</v>
       </c>
       <c r="K112" s="8" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="L112" s="8" t="n">
         <v>17</v>
@@ -15499,10 +15499,10 @@
         <v>498</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>152</v>
+        <v>52</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H113" s="10" t="n">
         <v>18</v>
@@ -15514,7 +15514,7 @@
         <v>57</v>
       </c>
       <c r="K113" s="8" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="L113" s="10" t="n">
         <v>18</v>
@@ -15555,22 +15555,22 @@
         <v>503</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>219</v>
+        <v>152</v>
       </c>
       <c r="G114" s="10" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="H114" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="I114" s="7" t="s">
+      <c r="I114" s="9" t="s">
         <v>504</v>
       </c>
-      <c r="J114" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K114" s="8" t="s">
-        <v>113</v>
+      <c r="J114" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="K114" s="10" t="s">
+        <v>131</v>
       </c>
       <c r="L114" s="10" t="n">
         <v>19</v>
@@ -15607,26 +15607,26 @@
       <c r="D115" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E115" s="7" t="s">
+      <c r="E115" s="9" t="s">
         <v>509</v>
       </c>
-      <c r="F115" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="G115" s="8" t="s">
-        <v>102</v>
+      <c r="F115" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="H115" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="I115" s="9" t="s">
+      <c r="I115" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="J115" s="10" t="s">
+      <c r="J115" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="K115" s="10" t="s">
-        <v>131</v>
+      <c r="K115" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="L115" s="8" t="n">
         <v>20</v>
@@ -15663,26 +15663,26 @@
       <c r="D116" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="E116" s="9" t="s">
+      <c r="E116" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="F116" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="G116" s="10" t="s">
+      <c r="F116" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G116" s="8" t="s">
         <v>102</v>
       </c>
       <c r="H116" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="I116" s="7" t="s">
+      <c r="I116" s="9" t="s">
         <v>515</v>
       </c>
-      <c r="J116" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="K116" s="8" t="s">
-        <v>142</v>
+      <c r="J116" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="K116" s="10" t="s">
+        <v>146</v>
       </c>
       <c r="L116" s="10" t="n">
         <v>21</v>
@@ -15720,7 +15720,7 @@
         <v>124</v>
       </c>
       <c r="G117" s="10" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="H117" s="10" t="n">
         <v>22</v>
@@ -15729,10 +15729,10 @@
         <v>519</v>
       </c>
       <c r="J117" s="10" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="K117" s="10" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L117" s="10" t="n">
         <v>22</v>
@@ -15763,14 +15763,14 @@
       <c r="D118" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E118" s="7" t="s">
+      <c r="E118" s="9" t="s">
         <v>522</v>
       </c>
-      <c r="F118" s="8" t="s">
+      <c r="F118" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="G118" s="8" t="s">
-        <v>45</v>
+      <c r="G118" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="H118" s="8" t="n">
         <v>23</v>
@@ -15782,7 +15782,7 @@
         <v>124</v>
       </c>
       <c r="K118" s="10" t="s">
-        <v>136</v>
+        <v>87</v>
       </c>
       <c r="L118" s="8" t="n">
         <v>23</v>
@@ -15820,19 +15820,19 @@
         <v>124</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H119" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="I119" s="9" t="s">
+      <c r="I119" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="J119" s="10" t="s">
+      <c r="J119" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="K119" s="10" t="s">
-        <v>87</v>
+      <c r="K119" s="8" t="s">
+        <v>74</v>
       </c>
       <c r="L119" s="10" t="n">
         <v>24</v>
@@ -15863,20 +15863,26 @@
       <c r="D120" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E120" s="9" t="n">
-        <v>1.04</v>
+      <c r="E120" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="H120" s="10" t="n">
         <v>25</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="J120" s="8" t="s">
         <v>124</v>
       </c>
       <c r="K120" s="8" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="L120" s="10" t="n">
         <v>25</v>
@@ -15885,7 +15891,7 @@
         <v>2.08</v>
       </c>
       <c r="S120" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="T120" s="10" t="s">
         <v>124</v>
@@ -15899,7 +15905,7 @@
         <v>26</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>197</v>
@@ -15908,19 +15914,19 @@
         <v>68</v>
       </c>
       <c r="E121" s="9" t="n">
-        <v>2.04</v>
+        <v>1.04</v>
       </c>
       <c r="H121" s="8" t="n">
         <v>26</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="J121" s="8" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="K121" s="8" t="s">
-        <v>68</v>
+        <v>175</v>
       </c>
       <c r="L121" s="8" t="n">
         <v>26</v>
@@ -15929,7 +15935,7 @@
         <v>2.12</v>
       </c>
       <c r="S121" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="T121" s="8" t="s">
         <v>124</v>
@@ -15943,7 +15949,7 @@
         <v>27</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>185</v>
@@ -15952,19 +15958,19 @@
         <v>48</v>
       </c>
       <c r="E122" s="9" t="n">
-        <v>3.04</v>
+        <v>2.04</v>
       </c>
       <c r="H122" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="I122" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="J122" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="K122" s="8" t="s">
-        <v>175</v>
+      <c r="I122" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="J122" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="K122" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="L122" s="10" t="n">
         <v>27</v>
@@ -15981,25 +15987,25 @@
         <v>1.05</v>
       </c>
       <c r="E123" s="9" t="n">
-        <v>4.04</v>
+        <v>3.04</v>
       </c>
       <c r="H123" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="I123" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="J123" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="K123" s="10" t="s">
-        <v>87</v>
+      <c r="I123" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="J123" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="K123" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="L123" s="10" t="n">
         <v>28</v>
       </c>
       <c r="M123" s="9" t="n">
-        <v>4.01</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16010,25 +16016,19 @@
         <v>2.05</v>
       </c>
       <c r="E124" s="9" t="n">
-        <v>5.04</v>
+        <v>4.04</v>
       </c>
       <c r="H124" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="I124" s="7" t="s">
-        <v>538</v>
-      </c>
-      <c r="J124" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="K124" s="8" t="s">
-        <v>72</v>
+      <c r="I124" s="0" t="s">
+        <v>539</v>
       </c>
       <c r="L124" s="8" t="n">
         <v>29</v>
       </c>
       <c r="M124" s="9" t="n">
-        <v>5.01</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16038,27 +16038,24 @@
       <c r="B125" s="9" t="n">
         <v>3.05</v>
       </c>
-      <c r="E125" s="0" t="n">
-        <v>6.04</v>
+      <c r="E125" s="9" t="n">
+        <v>5.04</v>
       </c>
       <c r="H125" s="8" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="0" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L125" s="10" t="n">
         <v>30</v>
       </c>
       <c r="M125" s="9" t="n">
-        <v>3.06</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H126" s="10"/>
-      <c r="I126" s="0" t="s">
-        <v>540</v>
-      </c>
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H127" s="8"/>
@@ -16180,7 +16177,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E423"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="30.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.12"/>
@@ -16295,7 +16292,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>175</v>
@@ -20180,10 +20177,10 @@
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B281" s="0" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C281" s="0" t="s">
         <v>146</v>
@@ -20194,7 +20191,7 @@
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B282" s="0" t="s">
         <v>437</v>
@@ -20208,10 +20205,10 @@
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B283" s="0" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C283" s="0" t="s">
         <v>163</v>
@@ -20222,7 +20219,7 @@
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B284" s="0" t="s">
         <v>487</v>
@@ -20236,7 +20233,7 @@
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B285" s="0" t="s">
         <v>452</v>
@@ -20250,7 +20247,7 @@
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B286" s="0" t="s">
         <v>457</v>
@@ -20264,7 +20261,7 @@
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B287" s="0" t="s">
         <v>462</v>
@@ -20278,7 +20275,7 @@
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B288" s="0" t="s">
         <v>432</v>
@@ -20292,7 +20289,7 @@
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B289" s="0" t="s">
         <v>497</v>
@@ -20306,7 +20303,7 @@
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B290" s="0" t="s">
         <v>502</v>
@@ -20320,10 +20317,10 @@
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B291" s="0" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C291" s="0" t="s">
         <v>45</v>
@@ -20334,7 +20331,7 @@
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B292" s="0" t="s">
         <v>442</v>
@@ -20348,7 +20345,7 @@
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B293" s="0" t="s">
         <v>447</v>
@@ -20362,7 +20359,7 @@
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B294" s="0" t="s">
         <v>477</v>
@@ -20376,7 +20373,7 @@
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B295" s="0" t="s">
         <v>492</v>
@@ -20390,7 +20387,7 @@
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B296" s="0" t="s">
         <v>472</v>
@@ -20404,10 +20401,10 @@
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B297" s="0" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C297" s="0" t="s">
         <v>142</v>
@@ -20418,7 +20415,7 @@
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B298" s="0" t="s">
         <v>422</v>
@@ -20432,7 +20429,7 @@
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B299" s="0" t="s">
         <v>467</v>
@@ -20446,7 +20443,7 @@
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B300" s="0" t="s">
         <v>481</v>
@@ -20460,7 +20457,7 @@
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B301" s="0" t="s">
         <v>491</v>
@@ -20474,7 +20471,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B302" s="0" t="s">
         <v>507</v>
@@ -20488,7 +20485,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B303" s="0" t="s">
         <v>486</v>
@@ -20502,7 +20499,7 @@
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B304" s="0" t="s">
         <v>513</v>
@@ -20516,7 +20513,7 @@
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B305" s="0" t="s">
         <v>517</v>
@@ -20530,7 +20527,7 @@
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B306" s="0" t="s">
         <v>521</v>
@@ -20544,7 +20541,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B307" s="0" t="s">
         <v>525</v>
@@ -20558,7 +20555,7 @@
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B308" s="0" t="s">
         <v>471</v>
@@ -20575,7 +20572,7 @@
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B309" s="0" t="s">
         <v>476</v>
@@ -20589,7 +20586,7 @@
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B310" s="0" t="s">
         <v>529</v>
@@ -20603,10 +20600,10 @@
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B311" s="0" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C311" s="0" t="s">
         <v>142</v>
@@ -20617,10 +20614,10 @@
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B312" s="0" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C312" s="0" t="s">
         <v>142</v>
@@ -20631,10 +20628,10 @@
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B313" s="0" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C313" s="0" t="s">
         <v>142</v>
@@ -20645,7 +20642,7 @@
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B314" s="0" t="s">
         <v>482</v>
@@ -20659,7 +20656,7 @@
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B315" s="0" t="s">
         <v>427</v>
@@ -20673,10 +20670,10 @@
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B316" s="0" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C316" s="0" t="s">
         <v>68</v>
@@ -20687,10 +20684,10 @@
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="0" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B317" s="0" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C317" s="0" t="s">
         <v>48</v>
@@ -20701,10 +20698,10 @@
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B318" s="0" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C318" s="0" t="s">
         <v>45</v>
@@ -20715,7 +20712,7 @@
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B319" s="0" t="s">
         <v>423</v>
@@ -20729,7 +20726,7 @@
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B320" s="0" t="s">
         <v>428</v>
@@ -20743,10 +20740,10 @@
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B321" s="0" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C321" s="0" t="s">
         <v>105</v>
@@ -20757,7 +20754,7 @@
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B322" s="0" t="s">
         <v>453</v>
@@ -20771,10 +20768,10 @@
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B323" s="0" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C323" s="0" t="s">
         <v>131</v>
@@ -20785,7 +20782,7 @@
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B324" s="0" t="s">
         <v>383</v>
@@ -20799,7 +20796,7 @@
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B325" s="0" t="s">
         <v>433</v>
@@ -20813,7 +20810,7 @@
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B326" s="0" t="s">
         <v>458</v>
@@ -20827,7 +20824,7 @@
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B327" s="0" t="s">
         <v>385</v>
@@ -20841,7 +20838,7 @@
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B328" s="0" t="s">
         <v>468</v>
@@ -20855,10 +20852,10 @@
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B329" s="0" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C329" s="0" t="s">
         <v>161</v>
@@ -20869,10 +20866,10 @@
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B330" s="0" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C330" s="0" t="s">
         <v>82</v>
@@ -20883,7 +20880,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B331" s="0" t="s">
         <v>387</v>
@@ -20897,10 +20894,10 @@
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B332" s="0" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C332" s="0" t="s">
         <v>146</v>
@@ -20911,10 +20908,10 @@
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B333" s="0" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C333" s="0" t="s">
         <v>119</v>
@@ -20925,7 +20922,7 @@
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B334" s="0" t="s">
         <v>438</v>
@@ -20939,10 +20936,10 @@
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B335" s="0" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C335" s="0" t="s">
         <v>108</v>
@@ -20953,10 +20950,10 @@
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B336" s="0" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C336" s="0" t="s">
         <v>97</v>
@@ -20967,10 +20964,10 @@
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B337" s="0" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C337" s="0" t="s">
         <v>68</v>
@@ -20981,10 +20978,10 @@
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B338" s="0" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C338" s="0" t="s">
         <v>125</v>
@@ -20995,10 +20992,10 @@
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B339" s="0" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="C339" s="0" t="s">
         <v>139</v>
@@ -21009,10 +21006,10 @@
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B340" s="0" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C340" s="0" t="s">
         <v>155</v>
@@ -21023,10 +21020,10 @@
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B341" s="0" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C341" s="0" t="s">
         <v>48</v>
@@ -21037,10 +21034,10 @@
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B342" s="0" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C342" s="0" t="s">
         <v>119</v>
@@ -21051,10 +21048,10 @@
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B343" s="0" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C343" s="0" t="s">
         <v>102</v>
@@ -21065,10 +21062,10 @@
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B344" s="0" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C344" s="0" t="s">
         <v>102</v>
@@ -21079,10 +21076,10 @@
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B345" s="0" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C345" s="0" t="s">
         <v>45</v>
@@ -21093,10 +21090,10 @@
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B346" s="0" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C346" s="0" t="s">
         <v>97</v>
@@ -21107,10 +21104,10 @@
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B347" s="0" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C347" s="0" t="s">
         <v>90</v>
@@ -21121,7 +21118,7 @@
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B348" s="0" t="s">
         <v>389</v>
@@ -21135,10 +21132,10 @@
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B349" s="0" t="s">
-        <v>391</v>
+        <v>473</v>
       </c>
       <c r="C349" s="0" t="s">
         <v>95</v>
@@ -21149,7 +21146,7 @@
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B350" s="0" t="s">
         <v>463</v>
@@ -21163,10 +21160,10 @@
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B351" s="0" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C351" s="0" t="s">
         <v>64</v>
@@ -21180,10 +21177,10 @@
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="0" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B352" s="0" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C352" s="0" t="s">
         <v>139</v>
@@ -21194,10 +21191,10 @@
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B353" s="0" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C353" s="0" t="s">
         <v>175</v>
@@ -21208,10 +21205,10 @@
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B354" s="0" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C354" s="0" t="s">
         <v>125</v>
@@ -21222,10 +21219,10 @@
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B355" s="0" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="C355" s="0" t="s">
         <v>90</v>
@@ -21236,10 +21233,10 @@
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B356" s="0" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C356" s="0" t="s">
         <v>113</v>
@@ -21250,10 +21247,10 @@
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B357" s="0" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C357" s="0" t="s">
         <v>74</v>
@@ -21264,10 +21261,10 @@
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B358" s="0" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C358" s="0" t="s">
         <v>68</v>
@@ -21278,10 +21275,10 @@
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B359" s="0" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C359" s="0" t="s">
         <v>74</v>
@@ -21292,10 +21289,10 @@
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B360" s="0" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C360" s="0" t="s">
         <v>95</v>
@@ -21306,10 +21303,10 @@
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B361" s="0" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C361" s="0" t="s">
         <v>163</v>
@@ -21320,10 +21317,10 @@
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B362" s="0" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C362" s="0" t="s">
         <v>102</v>
@@ -21334,7 +21331,7 @@
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B363" s="0" t="s">
         <v>223</v>
@@ -21348,10 +21345,10 @@
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B364" s="0" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C364" s="0" t="s">
         <v>136</v>
@@ -21362,10 +21359,10 @@
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B365" s="0" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C365" s="0" t="s">
         <v>117</v>
@@ -21376,10 +21373,10 @@
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B366" s="0" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C366" s="0" t="s">
         <v>113</v>
@@ -21390,10 +21387,10 @@
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B367" s="0" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C367" s="0" t="s">
         <v>161</v>
@@ -21404,7 +21401,7 @@
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B368" s="0" t="s">
         <v>250</v>
@@ -21418,10 +21415,10 @@
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B369" s="0" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C369" s="0" t="s">
         <v>82</v>
@@ -21432,10 +21429,10 @@
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B370" s="0" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C370" s="0" t="s">
         <v>161</v>
@@ -21446,10 +21443,10 @@
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B371" s="0" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C371" s="0" t="s">
         <v>136</v>
@@ -21460,10 +21457,10 @@
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B372" s="0" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C372" s="0" t="s">
         <v>142</v>
@@ -21474,10 +21471,10 @@
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B373" s="0" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C373" s="0" t="s">
         <v>146</v>
@@ -21488,10 +21485,10 @@
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B374" s="0" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C374" s="0" t="s">
         <v>175</v>
@@ -21502,7 +21499,7 @@
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B375" s="0" t="s">
         <v>537</v>
@@ -21516,7 +21513,7 @@
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B376" s="0" t="s">
         <v>538</v>
@@ -21530,10 +21527,10 @@
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B377" s="0" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C377" s="0" t="s">
         <v>87</v>
@@ -21544,10 +21541,10 @@
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B378" s="0" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C378" s="0" t="s">
         <v>74</v>
@@ -21558,10 +21555,10 @@
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B379" s="0" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C379" s="0" t="s">
         <v>102</v>
@@ -21572,10 +21569,10 @@
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B380" s="0" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C380" s="0" t="s">
         <v>90</v>
@@ -21586,7 +21583,7 @@
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B381" s="0" t="s">
         <v>244</v>
@@ -21600,10 +21597,10 @@
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B382" s="0" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C382" s="0" t="s">
         <v>68</v>
@@ -21614,7 +21611,7 @@
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B383" s="0" t="s">
         <v>443</v>
@@ -21628,10 +21625,10 @@
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B384" s="0" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C384" s="0" t="s">
         <v>131</v>
@@ -21642,7 +21639,7 @@
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B385" s="0" t="s">
         <v>248</v>
@@ -21656,10 +21653,10 @@
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B386" s="0" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C386" s="0" t="s">
         <v>136</v>
@@ -21670,10 +21667,10 @@
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B387" s="0" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="C387" s="0" t="s">
         <v>131</v>
@@ -21684,7 +21681,7 @@
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="0" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B388" s="0" t="s">
         <v>249</v>
@@ -21701,7 +21698,7 @@
         <v>217</v>
       </c>
       <c r="B389" s="0" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C389" s="0" t="s">
         <v>84</v>
@@ -21967,7 +21964,7 @@
         <v>217</v>
       </c>
       <c r="B408" s="0" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C408" s="0" t="s">
         <v>84</v>
@@ -22096,7 +22093,7 @@
         <v>217</v>
       </c>
       <c r="B417" s="0" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C417" s="0" t="s">
         <v>117</v>
@@ -22166,7 +22163,7 @@
         <v>217</v>
       </c>
       <c r="B422" s="0" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C422" s="0" t="s">
         <v>93</v>
@@ -22209,7 +22206,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="22.69"/>
@@ -22429,7 +22426,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B14" s="10" t="n">
         <v>37</v>
@@ -22449,7 +22446,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B15" s="10" t="n">
         <v>35</v>
@@ -22469,7 +22466,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B16" s="10" t="n">
         <v>36</v>
@@ -22579,7 +22576,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -22789,7 +22786,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E361"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.6"/>
@@ -22824,7 +22821,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>594</v>
@@ -22841,7 +22838,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>594</v>
@@ -23300,7 +23297,7 @@
         <v>30</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>594</v>
@@ -23895,7 +23892,7 @@
         <v>3</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>594</v>
@@ -26898,13 +26895,13 @@
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B242" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>595</v>
@@ -26915,13 +26912,13 @@
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B243" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D243" s="1" t="s">
         <v>595</v>
@@ -26932,13 +26929,13 @@
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B244" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>595</v>
@@ -26949,13 +26946,13 @@
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B245" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D245" s="1" t="s">
         <v>595</v>
@@ -26966,13 +26963,13 @@
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B246" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D246" s="1" t="s">
         <v>595</v>
@@ -26983,13 +26980,13 @@
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B247" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>595</v>
@@ -27000,13 +26997,13 @@
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B248" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>595</v>
@@ -27017,13 +27014,13 @@
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B249" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>595</v>
@@ -27034,13 +27031,13 @@
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B250" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>595</v>
@@ -27051,13 +27048,13 @@
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B251" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D251" s="1" t="s">
         <v>595</v>
@@ -27068,13 +27065,13 @@
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B252" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D252" s="1" t="s">
         <v>595</v>
@@ -27085,13 +27082,13 @@
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B253" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D253" s="1" t="s">
         <v>595</v>
@@ -27102,13 +27099,13 @@
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B254" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D254" s="1" t="s">
         <v>595</v>
@@ -27119,13 +27116,13 @@
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B255" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D255" s="1" t="s">
         <v>595</v>
@@ -27136,13 +27133,13 @@
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B256" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D256" s="1" t="s">
         <v>595</v>
@@ -27153,13 +27150,13 @@
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B257" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D257" s="1" t="s">
         <v>595</v>
@@ -27170,13 +27167,13 @@
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B258" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D258" s="1" t="s">
         <v>595</v>
@@ -27187,13 +27184,13 @@
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B259" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D259" s="1" t="s">
         <v>595</v>
@@ -27204,13 +27201,13 @@
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B260" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D260" s="1" t="s">
         <v>595</v>
@@ -27221,13 +27218,13 @@
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B261" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D261" s="1" t="s">
         <v>595</v>
@@ -27238,13 +27235,13 @@
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B262" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D262" s="1" t="s">
         <v>595</v>
@@ -27255,13 +27252,13 @@
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B263" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D263" s="1" t="s">
         <v>595</v>
@@ -27272,13 +27269,13 @@
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B264" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D264" s="1" t="s">
         <v>595</v>
@@ -27289,13 +27286,13 @@
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B265" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>595</v>
@@ -27306,13 +27303,13 @@
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B266" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>595</v>
@@ -27323,13 +27320,13 @@
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B267" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D267" s="1" t="s">
         <v>595</v>
@@ -27340,13 +27337,13 @@
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B268" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D268" s="1" t="s">
         <v>595</v>
@@ -27357,13 +27354,13 @@
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B269" s="1" t="n">
         <v>28</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D269" s="1" t="s">
         <v>595</v>
@@ -27374,13 +27371,13 @@
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B270" s="1" t="n">
         <v>29</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D270" s="1" t="s">
         <v>595</v>
@@ -27391,13 +27388,13 @@
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B271" s="1" t="n">
         <v>30</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D271" s="1" t="s">
         <v>595</v>
@@ -27408,13 +27405,13 @@
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B272" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D272" s="1" t="s">
         <v>595</v>
@@ -27425,13 +27422,13 @@
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B273" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D273" s="1" t="s">
         <v>595</v>
@@ -27442,13 +27439,13 @@
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B274" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D274" s="1" t="s">
         <v>595</v>
@@ -27459,13 +27456,13 @@
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B275" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D275" s="1" t="s">
         <v>595</v>
@@ -27476,13 +27473,13 @@
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B276" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D276" s="1" t="s">
         <v>595</v>
@@ -27493,13 +27490,13 @@
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B277" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D277" s="1" t="s">
         <v>595</v>
@@ -27510,13 +27507,13 @@
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B278" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D278" s="1" t="s">
         <v>595</v>
@@ -27527,13 +27524,13 @@
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B279" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>595</v>
@@ -27544,13 +27541,13 @@
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B280" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D280" s="1" t="s">
         <v>595</v>
@@ -27561,13 +27558,13 @@
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B281" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D281" s="1" t="s">
         <v>595</v>
@@ -27578,13 +27575,13 @@
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B282" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D282" s="1" t="s">
         <v>595</v>
@@ -27595,13 +27592,13 @@
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B283" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D283" s="1" t="s">
         <v>595</v>
@@ -27612,13 +27609,13 @@
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B284" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D284" s="1" t="s">
         <v>595</v>
@@ -27629,13 +27626,13 @@
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B285" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D285" s="1" t="s">
         <v>595</v>
@@ -27646,13 +27643,13 @@
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B286" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D286" s="1" t="s">
         <v>595</v>
@@ -27663,13 +27660,13 @@
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B287" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D287" s="1" t="s">
         <v>595</v>
@@ -27680,13 +27677,13 @@
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B288" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D288" s="1" t="s">
         <v>595</v>
@@ -27697,13 +27694,13 @@
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B289" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D289" s="1" t="s">
         <v>595</v>
@@ -27714,13 +27711,13 @@
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B290" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D290" s="1" t="s">
         <v>595</v>
@@ -27731,13 +27728,13 @@
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B291" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D291" s="1" t="s">
         <v>595</v>
@@ -27748,13 +27745,13 @@
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B292" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D292" s="1" t="s">
         <v>595</v>
@@ -27765,13 +27762,13 @@
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B293" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D293" s="1" t="s">
         <v>595</v>
@@ -27782,13 +27779,13 @@
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B294" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D294" s="1" t="s">
         <v>595</v>
@@ -27799,13 +27796,13 @@
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B295" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D295" s="1" t="s">
         <v>595</v>
@@ -27816,13 +27813,13 @@
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B296" s="1" t="n">
         <v>25</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D296" s="1" t="s">
         <v>595</v>
@@ -27833,13 +27830,13 @@
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B297" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D297" s="1" t="s">
         <v>595</v>
@@ -27850,13 +27847,13 @@
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B298" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D298" s="1" t="s">
         <v>595</v>
@@ -27867,13 +27864,13 @@
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B299" s="1" t="n">
         <v>28</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D299" s="1" t="s">
         <v>595</v>
@@ -27884,13 +27881,13 @@
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B300" s="1" t="n">
         <v>29</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D300" s="1" t="s">
         <v>595</v>
@@ -27901,13 +27898,13 @@
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B301" s="1" t="n">
         <v>30</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D301" s="1" t="s">
         <v>595</v>
@@ -27918,7 +27915,7 @@
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B302" s="1" t="n">
         <v>1</v>
@@ -27935,7 +27932,7 @@
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B303" s="1" t="n">
         <v>4</v>
@@ -27952,13 +27949,13 @@
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B304" s="1" t="n">
         <v>4</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D304" s="1" t="s">
         <v>595</v>
@@ -27969,13 +27966,13 @@
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B305" s="1" t="n">
         <v>5</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D305" s="1" t="s">
         <v>595</v>
@@ -27986,13 +27983,13 @@
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B306" s="1" t="n">
         <v>6</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D306" s="1" t="s">
         <v>595</v>
@@ -28003,7 +28000,7 @@
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B307" s="1" t="n">
         <v>6</v>
@@ -28020,13 +28017,13 @@
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B308" s="1" t="n">
         <v>7</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D308" s="1" t="s">
         <v>595</v>
@@ -28037,13 +28034,13 @@
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B309" s="1" t="n">
         <v>8</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D309" s="1" t="s">
         <v>595</v>
@@ -28054,13 +28051,13 @@
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B310" s="1" t="n">
         <v>9</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D310" s="1" t="s">
         <v>595</v>
@@ -28071,13 +28068,13 @@
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B311" s="1" t="n">
         <v>10</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D311" s="1" t="s">
         <v>595</v>
@@ -28088,13 +28085,13 @@
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B312" s="1" t="n">
         <v>11</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D312" s="1" t="s">
         <v>595</v>
@@ -28105,13 +28102,13 @@
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B313" s="1" t="n">
         <v>12</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D313" s="1" t="s">
         <v>595</v>
@@ -28122,13 +28119,13 @@
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B314" s="1" t="n">
         <v>13</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D314" s="1" t="s">
         <v>595</v>
@@ -28139,13 +28136,13 @@
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B315" s="1" t="n">
         <v>14</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D315" s="1" t="s">
         <v>595</v>
@@ -28156,13 +28153,13 @@
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B316" s="1" t="n">
         <v>15</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D316" s="1" t="s">
         <v>595</v>
@@ -28173,13 +28170,13 @@
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B317" s="1" t="n">
         <v>16</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D317" s="1" t="s">
         <v>595</v>
@@ -28190,13 +28187,13 @@
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B318" s="1" t="n">
         <v>17</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D318" s="1" t="s">
         <v>595</v>
@@ -28207,13 +28204,13 @@
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B319" s="1" t="n">
         <v>18</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D319" s="1" t="s">
         <v>595</v>
@@ -28224,13 +28221,13 @@
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B320" s="1" t="n">
         <v>19</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D320" s="1" t="s">
         <v>595</v>
@@ -28241,13 +28238,13 @@
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B321" s="1" t="n">
         <v>20</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D321" s="1" t="s">
         <v>595</v>
@@ -28258,13 +28255,13 @@
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B322" s="1" t="n">
         <v>21</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D322" s="1" t="s">
         <v>595</v>
@@ -28275,13 +28272,13 @@
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B323" s="1" t="n">
         <v>22</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D323" s="1" t="s">
         <v>595</v>
@@ -28292,13 +28289,13 @@
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B324" s="1" t="n">
         <v>23</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D324" s="1" t="s">
         <v>595</v>
@@ -28309,13 +28306,13 @@
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B325" s="1" t="n">
         <v>24</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D325" s="1" t="s">
         <v>595</v>
@@ -28326,13 +28323,13 @@
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B326" s="1" t="n">
         <v>26</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D326" s="1" t="s">
         <v>595</v>
@@ -28343,13 +28340,13 @@
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B327" s="1" t="n">
         <v>27</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>595</v>
@@ -28360,13 +28357,13 @@
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B328" s="1" t="n">
         <v>28</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>595</v>
@@ -28377,7 +28374,7 @@
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B329" s="1" t="n">
         <v>29</v>
@@ -28394,13 +28391,13 @@
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B330" s="1" t="n">
         <v>29</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>595</v>
@@ -28411,7 +28408,7 @@
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B331" s="1" t="n">
         <v>30</v>
@@ -28893,7 +28890,7 @@
         <v>25</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>594</v>
@@ -28961,7 +28958,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.83984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.67"/>
@@ -29237,17 +29234,17 @@
       <c r="E12" s="23"/>
       <c r="F12" s="23"/>
       <c r="G12" s="23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="23"/>
       <c r="J12" s="23" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
       <c r="M12" s="23" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="N12" s="23"/>
       <c r="O12" s="23"/>
@@ -29607,7 +29604,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AE31"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="49.87"/>
@@ -29750,7 +29747,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C4" s="26" t="s">
         <v>696</v>
@@ -30507,7 +30504,7 @@
     </row>
     <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B12" s="27" t="s">
         <v>595</v>
@@ -30602,7 +30599,7 @@
     </row>
     <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>595</v>
@@ -30697,7 +30694,7 @@
     </row>
     <row r="14" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>11</v>
@@ -30867,7 +30864,7 @@
         <v>595</v>
       </c>
       <c r="Z15" s="26" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AA15" s="27" t="s">
         <v>595</v>
@@ -31006,7 +31003,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
@@ -31081,7 +31078,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>594</v>
@@ -31101,7 +31098,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>594</v>
@@ -31189,7 +31186,7 @@
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>175</v>
@@ -31647,7 +31644,7 @@
         <v>30</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>594</v>
@@ -31787,7 +31784,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.12"/>
